--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3738" uniqueCount="1133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3746" uniqueCount="1135">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3313,6 +3313,12 @@
   </si>
   <si>
     <t>CASTANHA DE CAJU CARAMELIZADA AÇAÍ</t>
+  </si>
+  <si>
+    <t>castanha-de-caju-caramelizada-ninho</t>
+  </si>
+  <si>
+    <t>CASTANHA DE CAJU CARAM NINHO</t>
   </si>
   <si>
     <t>castanha-de-caju-w1-assada</t>
@@ -3506,7 +3512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3531,6 +3537,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3895,7 +3907,7 @@
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>1076</v>
       </c>
@@ -3918,7 +3930,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>848</v>
       </c>
@@ -3941,7 +3953,7 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>1064</v>
       </c>
@@ -3964,7 +3976,7 @@
         <v>140</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>1064</v>
       </c>
@@ -3987,7 +3999,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>904</v>
       </c>
@@ -4010,7 +4022,7 @@
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>904</v>
       </c>
@@ -4033,7 +4045,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>902</v>
       </c>
@@ -4056,7 +4068,7 @@
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>902</v>
       </c>
@@ -4079,7 +4091,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>878</v>
       </c>
@@ -4102,7 +4114,7 @@
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>878</v>
       </c>
@@ -4125,7 +4137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>720</v>
       </c>
@@ -4148,7 +4160,7 @@
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>722</v>
       </c>
@@ -4171,7 +4183,7 @@
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>546</v>
       </c>
@@ -4194,7 +4206,7 @@
         <v>275</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>556</v>
       </c>
@@ -4217,7 +4229,7 @@
         <v>140</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>520</v>
       </c>
@@ -4240,7 +4252,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>520</v>
       </c>
@@ -4263,7 +4275,7 @@
         <v>373.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>522</v>
       </c>
@@ -4286,7 +4298,7 @@
         <v>312.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>522</v>
       </c>
@@ -4309,7 +4321,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>346</v>
       </c>
@@ -4332,7 +4344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>350</v>
       </c>
@@ -4355,7 +4367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>350</v>
       </c>
@@ -4378,7 +4390,7 @@
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>346</v>
       </c>
@@ -4401,7 +4413,7 @@
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
@@ -4424,7 +4436,7 @@
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
@@ -4447,7 +4459,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
         <v>56</v>
       </c>
@@ -4470,7 +4482,7 @@
         <v>161</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
         <v>56</v>
       </c>
@@ -4493,7 +4505,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
         <v>58</v>
       </c>
@@ -4516,7 +4528,7 @@
         <v>138</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
         <v>58</v>
       </c>
@@ -4539,7 +4551,7 @@
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
@@ -4562,7 +4574,7 @@
         <v>228</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="3" t="s">
         <v>27</v>
       </c>
@@ -4585,7 +4597,7 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
@@ -5357,7 +5369,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="5">
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -5380,7 +5392,7 @@
         <v>158</v>
       </c>
       <c r="G8" s="5">
-        <v>187.5</v>
+        <v>217.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -11998,7 +12010,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="4">
-        <v>210</v>
+        <v>225.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -13436,7 +13448,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -14605,11 +14617,11 @@
       <c r="B51" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="C51" s="4">
-        <v>2442</v>
-      </c>
-      <c r="D51" s="5">
-        <v>11.34</v>
+      <c r="C51" s="10">
+        <v>4691</v>
+      </c>
+      <c r="D51" s="10">
+        <v>11.4</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>29</v>
@@ -14617,8 +14629,8 @@
       <c r="F51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G51" s="5">
-        <v>850.5</v>
+      <c r="G51" s="11">
+        <v>476</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
@@ -14628,10 +14640,10 @@
       <c r="B52" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="C52" s="4">
-        <v>2524</v>
-      </c>
-      <c r="D52" s="4">
+      <c r="C52" s="10">
+        <v>4692</v>
+      </c>
+      <c r="D52" s="10">
         <v>5</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -14640,8 +14652,8 @@
       <c r="F52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="4">
-        <v>378.5</v>
+      <c r="G52" s="11">
+        <v>213.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -14652,7 +14664,7 @@
         <v>1097</v>
       </c>
       <c r="C53" s="4">
-        <v>3441</v>
+        <v>2442</v>
       </c>
       <c r="D53" s="5">
         <v>11.34</v>
@@ -14675,7 +14687,7 @@
         <v>1097</v>
       </c>
       <c r="C54" s="4">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="D54" s="4">
         <v>5</v>
@@ -14698,7 +14710,7 @@
         <v>1099</v>
       </c>
       <c r="C55" s="4">
-        <v>3408</v>
+        <v>3441</v>
       </c>
       <c r="D55" s="5">
         <v>11.34</v>
@@ -14721,42 +14733,42 @@
         <v>1099</v>
       </c>
       <c r="C56" s="4">
-        <v>2273</v>
-      </c>
-      <c r="D56" s="5">
-        <v>22.68</v>
+        <v>2523</v>
+      </c>
+      <c r="D56" s="4">
+        <v>5</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G56" s="4">
-        <v>1701</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C57" s="4">
-        <v>2271</v>
-      </c>
-      <c r="D57" s="4">
-        <v>5</v>
+        <v>3408</v>
+      </c>
+      <c r="D57" s="5">
+        <v>11.34</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" s="4">
-        <v>378.6</v>
+        <v>15</v>
+      </c>
+      <c r="G57" s="5">
+        <v>850.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -14767,10 +14779,10 @@
         <v>1101</v>
       </c>
       <c r="C58" s="4">
-        <v>3409</v>
+        <v>2273</v>
       </c>
       <c r="D58" s="5">
-        <v>11.34</v>
+        <v>22.68</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
@@ -14778,8 +14790,8 @@
       <c r="F58" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="5">
-        <v>850.5</v>
+      <c r="G58" s="4">
+        <v>1701</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -14790,42 +14802,42 @@
         <v>1101</v>
       </c>
       <c r="C59" s="4">
-        <v>459</v>
-      </c>
-      <c r="D59" s="5">
-        <v>22.68</v>
+        <v>2271</v>
+      </c>
+      <c r="D59" s="4">
+        <v>5</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>1701</v>
+        <v>378.6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C60" s="4">
-        <v>285</v>
-      </c>
-      <c r="D60" s="4">
-        <v>5</v>
+        <v>3409</v>
+      </c>
+      <c r="D60" s="5">
+        <v>11.34</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="4">
-        <v>378.5</v>
+        <v>15</v>
+      </c>
+      <c r="G60" s="5">
+        <v>850.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -14836,19 +14848,19 @@
         <v>1103</v>
       </c>
       <c r="C61" s="4">
-        <v>2252</v>
-      </c>
-      <c r="D61" s="4">
-        <v>5</v>
+        <v>459</v>
+      </c>
+      <c r="D61" s="5">
+        <v>22.68</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G61" s="4">
-        <v>458</v>
+        <v>1701</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
@@ -14859,19 +14871,19 @@
         <v>1103</v>
       </c>
       <c r="C62" s="4">
-        <v>2291</v>
+        <v>285</v>
       </c>
       <c r="D62" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>1950</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -14882,19 +14894,19 @@
         <v>1105</v>
       </c>
       <c r="C63" s="4">
-        <v>3534</v>
+        <v>2252</v>
       </c>
       <c r="D63" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G63" s="4">
-        <v>1670</v>
+        <v>458</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -14905,19 +14917,19 @@
         <v>1105</v>
       </c>
       <c r="C64" s="4">
-        <v>2250</v>
+        <v>2291</v>
       </c>
       <c r="D64" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G64" s="4">
-        <v>421</v>
+        <v>1950</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -14928,19 +14940,19 @@
         <v>1107</v>
       </c>
       <c r="C65" s="4">
-        <v>2340</v>
+        <v>3534</v>
       </c>
       <c r="D65" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G65" s="4">
-        <v>398.5</v>
+        <v>1670</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -14951,19 +14963,19 @@
         <v>1107</v>
       </c>
       <c r="C66" s="4">
-        <v>3533</v>
+        <v>2250</v>
       </c>
       <c r="D66" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G66" s="4">
-        <v>1580</v>
+        <v>421</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -14974,19 +14986,19 @@
         <v>1109</v>
       </c>
       <c r="C67" s="4">
-        <v>3532</v>
+        <v>2340</v>
       </c>
       <c r="D67" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G67" s="4">
-        <v>1110</v>
+        <v>398.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -14997,19 +15009,19 @@
         <v>1109</v>
       </c>
       <c r="C68" s="4">
-        <v>2251</v>
+        <v>3533</v>
       </c>
       <c r="D68" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G68" s="4">
-        <v>281</v>
+        <v>1580</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -15020,19 +15032,19 @@
         <v>1111</v>
       </c>
       <c r="C69" s="4">
-        <v>3081</v>
+        <v>3532</v>
       </c>
       <c r="D69" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G69" s="4">
-        <v>145</v>
+        <v>1110</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -15043,7 +15055,7 @@
         <v>1111</v>
       </c>
       <c r="C70" s="4">
-        <v>3818</v>
+        <v>2251</v>
       </c>
       <c r="D70" s="4">
         <v>5</v>
@@ -15054,8 +15066,8 @@
       <c r="F70" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G70" s="5">
-        <v>75.5</v>
+      <c r="G70" s="4">
+        <v>281</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -15066,10 +15078,10 @@
         <v>1113</v>
       </c>
       <c r="C71" s="4">
-        <v>2534</v>
+        <v>3081</v>
       </c>
       <c r="D71" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
@@ -15077,8 +15089,8 @@
       <c r="F71" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G71" s="5">
-        <v>75.5</v>
+      <c r="G71" s="4">
+        <v>145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
@@ -15089,10 +15101,10 @@
         <v>1113</v>
       </c>
       <c r="C72" s="4">
-        <v>2234</v>
+        <v>3818</v>
       </c>
       <c r="D72" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>29</v>
@@ -15100,8 +15112,8 @@
       <c r="F72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="4">
-        <v>145</v>
+      <c r="G72" s="5">
+        <v>75.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -15112,10 +15124,10 @@
         <v>1115</v>
       </c>
       <c r="C73" s="4">
-        <v>2238</v>
+        <v>2534</v>
       </c>
       <c r="D73" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
@@ -15123,8 +15135,8 @@
       <c r="F73" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G73" s="4">
-        <v>145</v>
+      <c r="G73" s="5">
+        <v>75.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -15132,13 +15144,13 @@
         <v>1114</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C74" s="4">
-        <v>2535</v>
+        <v>2234</v>
       </c>
       <c r="D74" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>29</v>
@@ -15146,19 +15158,19 @@
       <c r="F74" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G74" s="5">
-        <v>75.5</v>
+      <c r="G74" s="4">
+        <v>145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>1117</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>1118</v>
-      </c>
       <c r="C75" s="4">
-        <v>2512</v>
+        <v>2238</v>
       </c>
       <c r="D75" s="4">
         <v>10</v>
@@ -15170,18 +15182,18 @@
         <v>10</v>
       </c>
       <c r="G75" s="4">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>1118</v>
       </c>
       <c r="C76" s="4">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="D76" s="4">
         <v>5</v>
@@ -15192,8 +15204,8 @@
       <c r="F76" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G76" s="4">
-        <v>83</v>
+      <c r="G76" s="5">
+        <v>75.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -15204,7 +15216,7 @@
         <v>1120</v>
       </c>
       <c r="C77" s="4">
-        <v>2236</v>
+        <v>2512</v>
       </c>
       <c r="D77" s="4">
         <v>10</v>
@@ -15216,7 +15228,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="4">
-        <v>145</v>
+        <v>166</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -15227,7 +15239,7 @@
         <v>1120</v>
       </c>
       <c r="C78" s="4">
-        <v>2546</v>
+        <v>2537</v>
       </c>
       <c r="D78" s="4">
         <v>5</v>
@@ -15238,8 +15250,8 @@
       <c r="F78" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G78" s="5">
-        <v>75.5</v>
+      <c r="G78" s="4">
+        <v>83</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -15250,7 +15262,7 @@
         <v>1122</v>
       </c>
       <c r="C79" s="4">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="D79" s="4">
         <v>10</v>
@@ -15273,7 +15285,7 @@
         <v>1122</v>
       </c>
       <c r="C80" s="4">
-        <v>2536</v>
+        <v>2546</v>
       </c>
       <c r="D80" s="4">
         <v>5</v>
@@ -15296,10 +15308,10 @@
         <v>1124</v>
       </c>
       <c r="C81" s="4">
-        <v>4021</v>
+        <v>2232</v>
       </c>
       <c r="D81" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
@@ -15308,7 +15320,7 @@
         <v>10</v>
       </c>
       <c r="G81" s="4">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
@@ -15319,19 +15331,19 @@
         <v>1124</v>
       </c>
       <c r="C82" s="4">
-        <v>4135</v>
+        <v>2536</v>
       </c>
       <c r="D82" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" s="4">
-        <v>1250</v>
+        <v>10</v>
+      </c>
+      <c r="G82" s="5">
+        <v>75.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
@@ -15342,10 +15354,10 @@
         <v>1126</v>
       </c>
       <c r="C83" s="4">
-        <v>2852</v>
+        <v>4021</v>
       </c>
       <c r="D83" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
@@ -15354,7 +15366,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="4">
-        <v>325</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -15365,7 +15377,7 @@
         <v>1126</v>
       </c>
       <c r="C84" s="4">
-        <v>3601</v>
+        <v>4135</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -15374,10 +15386,10 @@
         <v>29</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G84" s="4">
-        <v>650</v>
+        <v>1250</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -15388,19 +15400,19 @@
         <v>1128</v>
       </c>
       <c r="C85" s="4">
-        <v>3093</v>
+        <v>2852</v>
       </c>
       <c r="D85" s="4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G85" s="4">
-        <v>583</v>
+        <v>325</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -15411,7 +15423,7 @@
         <v>1128</v>
       </c>
       <c r="C86" s="4">
-        <v>263</v>
+        <v>3601</v>
       </c>
       <c r="D86" s="4">
         <v>10</v>
@@ -15420,33 +15432,33 @@
         <v>29</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G86" s="4">
-        <v>530</v>
+        <v>650</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C87" s="4">
-        <v>2632</v>
+        <v>3093</v>
       </c>
       <c r="D87" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G87" s="4">
-        <v>267</v>
+        <v>583</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -15457,7 +15469,7 @@
         <v>1130</v>
       </c>
       <c r="C88" s="4">
-        <v>2330</v>
+        <v>263</v>
       </c>
       <c r="D88" s="4">
         <v>10</v>
@@ -15469,7 +15481,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="4">
-        <v>480</v>
+        <v>530</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -15480,7 +15492,7 @@
         <v>1130</v>
       </c>
       <c r="C89" s="4">
-        <v>2385</v>
+        <v>2632</v>
       </c>
       <c r="D89" s="4">
         <v>5</v>
@@ -15492,7 +15504,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="4">
-        <v>242</v>
+        <v>267</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -15503,10 +15515,10 @@
         <v>1132</v>
       </c>
       <c r="C90" s="4">
-        <v>2384</v>
+        <v>2330</v>
       </c>
       <c r="D90" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -15514,8 +15526,8 @@
       <c r="F90" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G90" s="5">
-        <v>187.5</v>
+      <c r="G90" s="4">
+        <v>480</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -15526,41 +15538,87 @@
         <v>1132</v>
       </c>
       <c r="C91" s="4">
-        <v>3851</v>
+        <v>2385</v>
       </c>
       <c r="D91" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G91" s="4">
-        <v>75</v>
+        <v>242</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C92" s="4">
+        <v>2384</v>
+      </c>
+      <c r="D92" s="4">
+        <v>25</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="5">
+        <v>187.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+      <c r="A93" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C93" s="4">
+        <v>3851</v>
+      </c>
+      <c r="D93" s="4">
+        <v>10</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G93" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C94" s="4">
         <v>2424</v>
       </c>
-      <c r="D92" s="4">
-        <v>5</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="5">
+      <c r="D94" s="4">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="5">
         <v>39.5</v>
       </c>
     </row>
@@ -22790,7 +22848,7 @@
         <v>4139</v>
       </c>
       <c r="D2" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>29</v>
@@ -22799,7 +22857,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="4">
-        <v>380</v>
+        <v>475</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -22836,7 +22894,7 @@
         <v>4520</v>
       </c>
       <c r="D4" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>29</v>
@@ -22845,7 +22903,7 @@
         <v>158</v>
       </c>
       <c r="G4" s="4">
-        <v>350</v>
+        <v>437.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -23420,7 +23478,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>348</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -23443,7 +23501,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="4">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3443,7 +3443,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3461,6 +3461,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3541,10 +3547,10 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -15044,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="4">
-        <v>1110</v>
+        <v>1240</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -15067,7 +15073,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="4">
-        <v>281</v>
+        <v>313.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -22030,7 +22036,7 @@
         <v>158</v>
       </c>
       <c r="G5" s="4">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -22053,7 +22059,7 @@
         <v>158</v>
       </c>
       <c r="G6" s="4">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -22444,7 +22450,7 @@
         <v>158</v>
       </c>
       <c r="G23" s="4">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -22467,7 +22473,7 @@
         <v>158</v>
       </c>
       <c r="G24" s="4">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -22651,7 +22657,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
@@ -22674,7 +22680,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -22697,7 +22703,7 @@
         <v>158</v>
       </c>
       <c r="G34" s="4">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -22720,7 +22726,7 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -23064,7 +23070,7 @@
         <v>158</v>
       </c>
       <c r="G11" s="5">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -23087,7 +23093,7 @@
         <v>158</v>
       </c>
       <c r="G12" s="4">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3443,7 +3443,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3461,12 +3461,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3518,7 +3512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3545,12 +3539,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -14623,10 +14611,10 @@
       <c r="B51" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="4">
         <v>4691</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="4">
         <v>11.4</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -14635,7 +14623,7 @@
       <c r="F51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="5">
         <v>476</v>
       </c>
     </row>
@@ -14646,10 +14634,10 @@
       <c r="B52" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="4">
         <v>4692</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="4">
         <v>5</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -14658,7 +14646,7 @@
       <c r="F52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="5">
         <v>213.5</v>
       </c>
     </row>
@@ -14958,7 +14946,7 @@
         <v>15</v>
       </c>
       <c r="G65" s="4">
-        <v>1670</v>
+        <v>1780</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -14981,7 +14969,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="4">
-        <v>421</v>
+        <v>448.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -15004,7 +14992,7 @@
         <v>10</v>
       </c>
       <c r="G67" s="4">
-        <v>398.5</v>
+        <v>433.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -15027,7 +15015,7 @@
         <v>15</v>
       </c>
       <c r="G68" s="4">
-        <v>1580</v>
+        <v>1720</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -15050,7 +15038,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="4">
-        <v>1240</v>
+        <v>1460</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -15073,7 +15061,7 @@
         <v>10</v>
       </c>
       <c r="G70" s="4">
-        <v>313.5</v>
+        <v>368.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4220,7 +4220,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="4">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
@@ -5180,7 +5180,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="4">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -14627,7 +14627,7 @@
         <v>476</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
       <c r="A52" s="3" t="s">
         <v>1094</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>213.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
       <c r="A53" s="3" t="s">
         <v>1096</v>
       </c>
@@ -14673,7 +14673,7 @@
         <v>850.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="3" t="s">
         <v>1096</v>
       </c>
@@ -14696,7 +14696,7 @@
         <v>378.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
       <c r="A55" s="3" t="s">
         <v>1098</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>850.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="3" t="s">
         <v>1098</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>378.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="3" t="s">
         <v>1100</v>
       </c>
@@ -14765,7 +14765,7 @@
         <v>850.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
       <c r="A58" s="3" t="s">
         <v>1100</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="3" t="s">
         <v>1100</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>378.6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="3" t="s">
         <v>1102</v>
       </c>
@@ -14834,7 +14834,7 @@
         <v>850.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="3" t="s">
         <v>1102</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="3" t="s">
         <v>1102</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>378.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
       <c r="A63" s="3" t="s">
         <v>1104</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>458</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="3" t="s">
         <v>1104</v>
       </c>
@@ -14926,7 +14926,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="3" t="s">
         <v>1106</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="3" t="s">
         <v>1106</v>
       </c>
@@ -14972,7 +14972,7 @@
         <v>448.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="3" t="s">
         <v>1108</v>
       </c>
@@ -14995,7 +14995,7 @@
         <v>433.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="3" t="s">
         <v>1108</v>
       </c>
@@ -15018,7 +15018,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
       <c r="A69" s="3" t="s">
         <v>1110</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="3" t="s">
         <v>1110</v>
       </c>
@@ -15064,7 +15064,7 @@
         <v>368.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="3" t="s">
         <v>1112</v>
       </c>
@@ -15087,7 +15087,7 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="3" t="s">
         <v>1112</v>
       </c>
@@ -15110,7 +15110,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="3" t="s">
         <v>1114</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="3" t="s">
         <v>1114</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3746" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="1135">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3512,7 +3512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3537,6 +3537,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -19404,7 +19410,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -19427,7 +19433,7 @@
         <v>158</v>
       </c>
       <c r="G59" s="4">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
@@ -21289,7 +21295,7 @@
         <v>158</v>
       </c>
       <c r="G68" s="4">
-        <v>225</v>
+        <v>285</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -21312,7 +21318,7 @@
         <v>10</v>
       </c>
       <c r="G69" s="5">
-        <v>40.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -21900,7 +21906,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -22303,50 +22309,50 @@
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>738</v>
+        <v>388</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="C18" s="4">
-        <v>4048</v>
-      </c>
-      <c r="D18" s="4">
-        <v>20</v>
+        <v>389</v>
+      </c>
+      <c r="C18" s="10">
+        <v>4697</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="4">
-        <v>55</v>
+        <v>10</v>
+      </c>
+      <c r="G18" s="11">
+        <v>14</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C19" s="4">
-        <v>2519</v>
+        <v>4048</v>
       </c>
       <c r="D19" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G19" s="4">
-        <v>530</v>
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -22357,42 +22363,42 @@
         <v>741</v>
       </c>
       <c r="C20" s="4">
-        <v>2525</v>
+        <v>2519</v>
       </c>
       <c r="D20" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G20" s="4">
-        <v>275</v>
+        <v>530</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C21" s="4">
-        <v>3433</v>
+        <v>2525</v>
       </c>
       <c r="D21" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G21" s="4">
-        <v>940</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
@@ -22403,53 +22409,53 @@
         <v>743</v>
       </c>
       <c r="C22" s="4">
-        <v>3394</v>
+        <v>3433</v>
       </c>
       <c r="D22" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G22" s="4">
-        <v>237</v>
+        <v>940</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C23" s="4">
-        <v>47</v>
+        <v>3394</v>
       </c>
       <c r="D23" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G23" s="4">
-        <v>139</v>
+        <v>237</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C24" s="4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="4">
         <v>25</v>
@@ -22461,21 +22467,21 @@
         <v>158</v>
       </c>
       <c r="G24" s="4">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C25" s="4">
-        <v>3100</v>
+        <v>46</v>
       </c>
       <c r="D25" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>29</v>
@@ -22484,21 +22490,21 @@
         <v>158</v>
       </c>
       <c r="G25" s="4">
-        <v>209</v>
+        <v>135</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C26" s="4">
-        <v>3746</v>
+        <v>3100</v>
       </c>
       <c r="D26" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>29</v>
@@ -22507,18 +22513,18 @@
         <v>158</v>
       </c>
       <c r="G26" s="4">
-        <v>119</v>
+        <v>209</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C27" s="4">
-        <v>3639</v>
+        <v>3746</v>
       </c>
       <c r="D27" s="4">
         <v>15</v>
@@ -22535,16 +22541,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C28" s="4">
-        <v>2415</v>
+        <v>3639</v>
       </c>
       <c r="D28" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>29</v>
@@ -22552,42 +22558,42 @@
       <c r="F28" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G28" s="5">
-        <v>158.5</v>
+      <c r="G28" s="4">
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2415</v>
+      </c>
+      <c r="D29" s="4">
+        <v>20</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G29" s="5">
+        <v>158.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
+      <c r="A30" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C30" s="4">
         <v>3747</v>
-      </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="4">
-        <v>119</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="C30" s="4">
-        <v>3640</v>
       </c>
       <c r="D30" s="4">
         <v>15</v>
@@ -22604,16 +22610,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C31" s="4">
-        <v>2416</v>
+        <v>3640</v>
       </c>
       <c r="D31" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>29</v>
@@ -22621,22 +22627,22 @@
       <c r="F31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G31" s="5">
-        <v>158.5</v>
+      <c r="G31" s="4">
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C32" s="4">
-        <v>50</v>
+        <v>2416</v>
       </c>
       <c r="D32" s="4">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -22644,8 +22650,8 @@
       <c r="F32" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G32" s="4">
-        <v>170</v>
+      <c r="G32" s="5">
+        <v>158.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
@@ -22656,42 +22662,42 @@
         <v>763</v>
       </c>
       <c r="C33" s="4">
-        <v>2533</v>
+        <v>50</v>
       </c>
       <c r="D33" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G33" s="4">
-        <v>37</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C34" s="4">
-        <v>52</v>
+        <v>2533</v>
       </c>
       <c r="D34" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>170</v>
+        <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -22702,53 +22708,53 @@
         <v>765</v>
       </c>
       <c r="C35" s="4">
-        <v>2470</v>
+        <v>52</v>
       </c>
       <c r="D35" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G35" s="4">
-        <v>37</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C36" s="4">
-        <v>4671</v>
+        <v>2470</v>
       </c>
       <c r="D36" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G36" s="4">
-        <v>164</v>
+        <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C37" s="4">
-        <v>53</v>
+        <v>4671</v>
       </c>
       <c r="D37" s="4">
         <v>25</v>
@@ -22760,7 +22766,7 @@
         <v>158</v>
       </c>
       <c r="G37" s="4">
-        <v>118</v>
+        <v>164</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
@@ -22771,19 +22777,42 @@
         <v>769</v>
       </c>
       <c r="C38" s="4">
+        <v>53</v>
+      </c>
+      <c r="D38" s="4">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G38" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C39" s="4">
         <v>2435</v>
       </c>
-      <c r="D38" s="4">
-        <v>5</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="5">
-        <v>25.5</v>
+      <c r="D39" s="4">
+        <v>5</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="5">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3750" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3746" uniqueCount="1135">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3443,7 +3443,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3461,6 +3461,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3541,10 +3547,10 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -13448,7 +13454,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -15446,10 +15452,10 @@
         <v>1130</v>
       </c>
       <c r="C87" s="4">
-        <v>3093</v>
+        <v>263</v>
       </c>
       <c r="D87" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
@@ -15458,7 +15464,7 @@
         <v>15</v>
       </c>
       <c r="G87" s="4">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -15469,42 +15475,42 @@
         <v>1130</v>
       </c>
       <c r="C88" s="4">
-        <v>263</v>
+        <v>2632</v>
       </c>
       <c r="D88" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G88" s="4">
-        <v>530</v>
+        <v>293.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C89" s="4">
-        <v>2632</v>
+        <v>2330</v>
       </c>
       <c r="D89" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G89" s="4">
-        <v>267</v>
+        <v>480</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -15515,42 +15521,42 @@
         <v>1132</v>
       </c>
       <c r="C90" s="4">
-        <v>2330</v>
+        <v>2385</v>
       </c>
       <c r="D90" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G90" s="4">
-        <v>480</v>
+        <v>242</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C91" s="4">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="D91" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="4">
-        <v>242</v>
+        <v>15</v>
+      </c>
+      <c r="G91" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -15561,19 +15567,19 @@
         <v>1134</v>
       </c>
       <c r="C92" s="4">
-        <v>2384</v>
+        <v>3851</v>
       </c>
       <c r="D92" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" s="5">
-        <v>187.5</v>
+        <v>158</v>
+      </c>
+      <c r="G92" s="4">
+        <v>75</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -15584,41 +15590,18 @@
         <v>1134</v>
       </c>
       <c r="C93" s="4">
-        <v>3851</v>
+        <v>2424</v>
       </c>
       <c r="D93" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G93" s="4">
-        <v>75</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="3" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C94" s="4">
-        <v>2424</v>
-      </c>
-      <c r="D94" s="4">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="5">
+        <v>10</v>
+      </c>
+      <c r="G93" s="5">
         <v>39.5</v>
       </c>
     </row>
@@ -21283,10 +21266,10 @@
         <v>833</v>
       </c>
       <c r="C68" s="4">
-        <v>3670</v>
+        <v>3740</v>
       </c>
       <c r="D68" s="4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
@@ -21295,7 +21278,7 @@
         <v>158</v>
       </c>
       <c r="G68" s="4">
-        <v>285</v>
+        <v>237.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -21918,7 +21901,7 @@
     <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21941,7 +21924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
         <v>716</v>
       </c>
@@ -21964,7 +21947,7 @@
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>718</v>
       </c>
@@ -21987,7 +21970,7 @@
         <v>186</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>718</v>
       </c>
@@ -22010,7 +21993,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>720</v>
       </c>
@@ -22033,7 +22016,7 @@
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>722</v>
       </c>
@@ -22056,7 +22039,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>724</v>
       </c>
@@ -22079,7 +22062,7 @@
         <v>310</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>724</v>
       </c>
@@ -22102,7 +22085,7 @@
         <v>158</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>726</v>
       </c>
@@ -22125,7 +22108,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
         <v>728</v>
       </c>
@@ -22148,7 +22131,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
         <v>730</v>
       </c>
@@ -22171,7 +22154,7 @@
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
         <v>730</v>
       </c>
@@ -22194,7 +22177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="3" t="s">
         <v>732</v>
       </c>
@@ -22217,7 +22200,7 @@
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="3" t="s">
         <v>732</v>
       </c>
@@ -22240,7 +22223,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="3" t="s">
         <v>734</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3461,7 +3461,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3479,6 +3479,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3553,7 +3559,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -4695,7 +4701,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="4">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -5040,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="4">
-        <v>850</v>
+        <v>675</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -5063,7 +5069,7 @@
         <v>10</v>
       </c>
       <c r="G18" s="5">
-        <v>425</v>
+        <v>337.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
@@ -5453,7 +5459,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="4">
-        <v>108.5</v>
+        <v>103.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -5476,7 +5482,7 @@
         <v>158</v>
       </c>
       <c r="G10" s="4">
-        <v>525</v>
+        <v>500</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -5683,7 +5689,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="5">
-        <v>202.5</v>
+        <v>162.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -5706,7 +5712,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="4">
-        <v>405</v>
+        <v>325</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -5959,7 +5965,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="4">
-        <v>1850</v>
+        <v>1725</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -5982,7 +5988,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>373.5</v>
+        <v>348.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -6064,7 +6070,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -6510,7 +6516,7 @@
         <v>158</v>
       </c>
       <c r="G19" s="4">
-        <v>575</v>
+        <v>450</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -6533,7 +6539,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -6602,7 +6608,7 @@
         <v>158</v>
       </c>
       <c r="G23" s="4">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -6625,7 +6631,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>260</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -6740,7 +6746,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>595</v>
+        <v>627.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -8097,7 +8103,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="5">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -8120,30 +8126,30 @@
         <v>158</v>
       </c>
       <c r="G89" s="4">
-        <v>310</v>
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C90" s="4">
-        <v>4225</v>
+        <v>4378</v>
       </c>
       <c r="D90" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>775</v>
+        <v>430</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -8154,10 +8160,10 @@
         <v>448</v>
       </c>
       <c r="C91" s="4">
-        <v>4378</v>
+        <v>4379</v>
       </c>
       <c r="D91" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
@@ -8166,30 +8172,30 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>430</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C92" s="4">
-        <v>4379</v>
+        <v>3524</v>
       </c>
       <c r="D92" s="4">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="G92" s="4">
-        <v>43</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -8200,10 +8206,10 @@
         <v>450</v>
       </c>
       <c r="C93" s="4">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="D93" s="4">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>29</v>
@@ -8212,30 +8218,30 @@
         <v>9</v>
       </c>
       <c r="G93" s="4">
-        <v>350</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C94" s="4">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="D94" s="4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>29</v>
+        <v>453</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G94" s="4">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
@@ -8246,53 +8252,53 @@
         <v>452</v>
       </c>
       <c r="C95" s="4">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="D95" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>453</v>
+        <v>74</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G95" s="4">
-        <v>158</v>
+      <c r="G95" s="5">
+        <v>216.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C96" s="4">
-        <v>3522</v>
+        <v>64</v>
       </c>
       <c r="D96" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G96" s="5">
-        <v>216.5</v>
+      <c r="G96" s="4">
+        <v>132</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C97" s="4">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D97" s="4">
         <v>8</v>
@@ -8309,25 +8315,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C98" s="4">
-        <v>90</v>
+        <v>3637</v>
       </c>
       <c r="D98" s="4">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="G98" s="4">
-        <v>132</v>
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
@@ -8338,10 +8344,10 @@
         <v>459</v>
       </c>
       <c r="C99" s="4">
-        <v>3637</v>
+        <v>2805</v>
       </c>
       <c r="D99" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>29</v>
@@ -8350,7 +8356,7 @@
         <v>158</v>
       </c>
       <c r="G99" s="4">
-        <v>375</v>
+        <v>150</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
@@ -8361,42 +8367,42 @@
         <v>459</v>
       </c>
       <c r="C100" s="4">
-        <v>2805</v>
+        <v>2427</v>
       </c>
       <c r="D100" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G100" s="4">
-        <v>150</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C101" s="4">
-        <v>2427</v>
+        <v>3437</v>
       </c>
       <c r="D101" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G101" s="4">
-        <v>46</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
@@ -8407,53 +8413,53 @@
         <v>461</v>
       </c>
       <c r="C102" s="4">
-        <v>3437</v>
+        <v>3396</v>
       </c>
       <c r="D102" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G102" s="4">
-        <v>350</v>
+        <v>178.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C103" s="4">
-        <v>3396</v>
+        <v>3395</v>
       </c>
       <c r="D103" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>29</v>
+        <v>464</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G103" s="4">
-        <v>178.5</v>
+        <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C104" s="4">
-        <v>3395</v>
+        <v>3490</v>
       </c>
       <c r="D104" s="4">
         <v>12</v>
@@ -8465,41 +8471,41 @@
         <v>15</v>
       </c>
       <c r="G104" s="4">
-        <v>54</v>
+        <v>169</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C105" s="4">
-        <v>3490</v>
+        <v>458</v>
       </c>
       <c r="D105" s="4">
         <v>12</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>464</v>
+        <v>314</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G105" s="4">
-        <v>169</v>
+      <c r="G105" s="5">
+        <v>269.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C106" s="4">
-        <v>458</v>
+        <v>2641</v>
       </c>
       <c r="D106" s="4">
         <v>12</v>
@@ -8510,19 +8516,19 @@
       <c r="F106" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G106" s="5">
-        <v>269.5</v>
+      <c r="G106" s="4">
+        <v>222</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C107" s="4">
-        <v>2641</v>
+        <v>4293</v>
       </c>
       <c r="D107" s="4">
         <v>12</v>
@@ -8534,30 +8540,30 @@
         <v>15</v>
       </c>
       <c r="G107" s="4">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C108" s="4">
-        <v>4293</v>
+        <v>2396</v>
       </c>
       <c r="D108" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>314</v>
+        <v>29</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="G108" s="4">
-        <v>210</v>
+        <v>575</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -8568,33 +8574,33 @@
         <v>474</v>
       </c>
       <c r="C109" s="4">
-        <v>2396</v>
+        <v>2426</v>
       </c>
       <c r="D109" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G109" s="4">
-        <v>675</v>
+        <v>118.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C110" s="4">
-        <v>2426</v>
+        <v>4335</v>
       </c>
       <c r="D110" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>29</v>
@@ -8603,18 +8609,18 @@
         <v>10</v>
       </c>
       <c r="G110" s="4">
-        <v>137</v>
+        <v>510</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C111" s="4">
-        <v>4335</v>
+        <v>4477</v>
       </c>
       <c r="D111" s="4">
         <v>3</v>
@@ -8626,18 +8632,18 @@
         <v>10</v>
       </c>
       <c r="G111" s="4">
-        <v>510</v>
+        <v>252</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C112" s="4">
-        <v>4477</v>
+        <v>4479</v>
       </c>
       <c r="D112" s="4">
         <v>3</v>
@@ -8654,13 +8660,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C113" s="4">
-        <v>4479</v>
+        <v>4478</v>
       </c>
       <c r="D113" s="4">
         <v>3</v>
@@ -8677,25 +8683,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C114" s="4">
-        <v>4478</v>
+        <v>2646</v>
       </c>
       <c r="D114" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>29</v>
+        <v>485</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G114" s="4">
-        <v>252</v>
+        <v>53</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
@@ -8706,19 +8712,19 @@
         <v>484</v>
       </c>
       <c r="C115" s="4">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="D115" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G115" s="4">
-        <v>53</v>
+      <c r="G115" s="5">
+        <v>81.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
@@ -8729,110 +8735,87 @@
         <v>484</v>
       </c>
       <c r="C116" s="4">
-        <v>2645</v>
+        <v>2638</v>
       </c>
       <c r="D116" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G116" s="5">
-        <v>81.5</v>
+      <c r="G116" s="4">
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C117" s="4">
-        <v>2638</v>
+        <v>4294</v>
       </c>
       <c r="D117" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G117" s="4">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C118" s="4">
-        <v>4294</v>
+        <v>4314</v>
       </c>
       <c r="D118" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>490</v>
+        <v>74</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G118" s="4">
-        <v>150</v>
+        <v>252</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C119" s="4">
-        <v>4314</v>
+        <v>4315</v>
       </c>
       <c r="D119" s="4">
         <v>15</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>74</v>
+        <v>495</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G119" s="4">
-        <v>252</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
-      <c r="A120" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C120" s="4">
-        <v>4315</v>
-      </c>
-      <c r="D120" s="4">
-        <v>15</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G120" s="4">
         <v>450</v>
       </c>
     </row>
@@ -14438,7 +14421,7 @@
         <v>158</v>
       </c>
       <c r="G40" s="4">
-        <v>215</v>
+        <v>195</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -14461,7 +14444,7 @@
         <v>10</v>
       </c>
       <c r="G41" s="4">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
@@ -14484,7 +14467,7 @@
         <v>10</v>
       </c>
       <c r="G42" s="4">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
@@ -14507,7 +14490,7 @@
         <v>158</v>
       </c>
       <c r="G43" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
@@ -14530,7 +14513,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -14553,7 +14536,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="4">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
@@ -14576,7 +14559,7 @@
         <v>158</v>
       </c>
       <c r="G46" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -14599,7 +14582,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="4">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
@@ -14829,7 +14812,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="5">
-        <v>850.5</v>
+        <v>833.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
@@ -14852,7 +14835,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="4">
-        <v>1701</v>
+        <v>1667</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -14875,7 +14858,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>378.6</v>
+        <v>371</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
@@ -14898,7 +14881,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="5">
-        <v>850.5</v>
+        <v>833.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
@@ -14921,7 +14904,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="4">
-        <v>1701</v>
+        <v>1667</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
@@ -14944,7 +14927,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>378.5</v>
+        <v>371</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
@@ -18128,7 +18111,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -18712,7 +18695,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="4">
-        <v>330</v>
+        <v>270</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
@@ -18735,7 +18718,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="4">
-        <v>165</v>
+        <v>138.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
@@ -18804,7 +18787,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>925</v>
+        <v>675</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -18815,10 +18798,10 @@
         <v>893</v>
       </c>
       <c r="C30" s="4">
-        <v>4163</v>
+        <v>4676</v>
       </c>
       <c r="D30" s="4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>29</v>
@@ -18827,7 +18810,7 @@
         <v>158</v>
       </c>
       <c r="G30" s="4">
-        <v>370</v>
+        <v>337.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -18838,33 +18821,33 @@
         <v>893</v>
       </c>
       <c r="C31" s="4">
-        <v>4117</v>
+        <v>4163</v>
       </c>
       <c r="D31" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G31" s="4">
-        <v>187</v>
+        <v>270</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C32" s="4">
-        <v>3738</v>
+        <v>4117</v>
       </c>
       <c r="D32" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -18873,7 +18856,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="4">
-        <v>100</v>
+        <v>138.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
@@ -18884,10 +18867,10 @@
         <v>895</v>
       </c>
       <c r="C33" s="4">
-        <v>4317</v>
+        <v>3738</v>
       </c>
       <c r="D33" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
@@ -18896,21 +18879,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="4">
-        <v>52</v>
+        <v>100</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C34" s="4">
-        <v>2924</v>
+        <v>4317</v>
       </c>
       <c r="D34" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
@@ -18919,7 +18902,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>168</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -18930,10 +18913,10 @@
         <v>897</v>
       </c>
       <c r="C35" s="4">
-        <v>3078</v>
+        <v>2924</v>
       </c>
       <c r="D35" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>29</v>
@@ -18942,30 +18925,30 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>86</v>
+        <v>168</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C36" s="4">
-        <v>2348</v>
+        <v>3078</v>
       </c>
       <c r="D36" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G36" s="4">
-        <v>140</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
@@ -18976,10 +18959,10 @@
         <v>899</v>
       </c>
       <c r="C37" s="4">
-        <v>2538</v>
+        <v>2348</v>
       </c>
       <c r="D37" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>29</v>
@@ -18988,18 +18971,18 @@
         <v>158</v>
       </c>
       <c r="G37" s="4">
-        <v>30</v>
+        <v>160</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C38" s="4">
-        <v>2811</v>
+        <v>2538</v>
       </c>
       <c r="D38" s="4">
         <v>5</v>
@@ -19008,10 +18991,10 @@
         <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="5">
-        <v>104.5</v>
+        <v>158</v>
+      </c>
+      <c r="G38" s="4">
+        <v>35</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
@@ -19022,10 +19005,10 @@
         <v>901</v>
       </c>
       <c r="C39" s="4">
-        <v>2820</v>
+        <v>2811</v>
       </c>
       <c r="D39" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>29</v>
@@ -19033,22 +19016,22 @@
       <c r="F39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="4">
-        <v>205</v>
+      <c r="G39" s="5">
+        <v>104.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C40" s="4">
-        <v>3722</v>
+        <v>2820</v>
       </c>
       <c r="D40" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>29</v>
@@ -19057,7 +19040,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="4">
-        <v>66</v>
+        <v>205</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -19068,30 +19051,30 @@
         <v>903</v>
       </c>
       <c r="C41" s="4">
-        <v>4050</v>
+        <v>3722</v>
       </c>
       <c r="D41" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G41" s="4">
-        <v>128</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C42" s="4">
-        <v>415</v>
+        <v>4050</v>
       </c>
       <c r="D42" s="4">
         <v>10</v>
@@ -19100,21 +19083,21 @@
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G42" s="4">
-        <v>105</v>
+        <v>128</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C43" s="4">
-        <v>93</v>
+        <v>415</v>
       </c>
       <c r="D43" s="4">
         <v>10</v>
@@ -19126,30 +19109,30 @@
         <v>10</v>
       </c>
       <c r="G43" s="4">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C44" s="4">
-        <v>261</v>
+        <v>93</v>
       </c>
       <c r="D44" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G44" s="4">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -19160,42 +19143,42 @@
         <v>909</v>
       </c>
       <c r="C45" s="4">
-        <v>2475</v>
+        <v>261</v>
       </c>
       <c r="D45" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="5">
-        <v>18.5</v>
+        <v>158</v>
+      </c>
+      <c r="G45" s="4">
+        <v>83</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C46" s="4">
-        <v>92</v>
+        <v>2475</v>
       </c>
       <c r="D46" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G46" s="4">
-        <v>67</v>
+        <v>10</v>
+      </c>
+      <c r="G46" s="5">
+        <v>18.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -19206,42 +19189,42 @@
         <v>911</v>
       </c>
       <c r="C47" s="4">
-        <v>2476</v>
+        <v>92</v>
       </c>
       <c r="D47" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="5">
-        <v>11.5</v>
+        <v>158</v>
+      </c>
+      <c r="G47" s="4">
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C48" s="4">
-        <v>18</v>
+        <v>2476</v>
       </c>
       <c r="D48" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G48" s="4">
-        <v>96</v>
+        <v>10</v>
+      </c>
+      <c r="G48" s="5">
+        <v>11.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -19252,42 +19235,42 @@
         <v>913</v>
       </c>
       <c r="C49" s="4">
-        <v>2477</v>
+        <v>18</v>
       </c>
       <c r="D49" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G49" s="4">
-        <v>22.5</v>
+        <v>96</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C50" s="4">
-        <v>4164</v>
+        <v>2477</v>
       </c>
       <c r="D50" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G50" s="4">
-        <v>180</v>
+        <v>22.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -19298,42 +19281,42 @@
         <v>915</v>
       </c>
       <c r="C51" s="4">
-        <v>3706</v>
+        <v>4164</v>
       </c>
       <c r="D51" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G51" s="4">
-        <v>92</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C52" s="4">
-        <v>19</v>
+        <v>3706</v>
       </c>
       <c r="D52" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G52" s="4">
-        <v>168</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -19344,19 +19327,19 @@
         <v>917</v>
       </c>
       <c r="C53" s="4">
-        <v>2246</v>
+        <v>19</v>
       </c>
       <c r="D53" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>344</v>
+        <v>29</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="G53" s="4">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
@@ -19367,42 +19350,42 @@
         <v>917</v>
       </c>
       <c r="C54" s="4">
-        <v>575</v>
+        <v>2246</v>
       </c>
       <c r="D54" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G54" s="4">
-        <v>48</v>
+        <v>192</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C55" s="4">
-        <v>221</v>
+        <v>575</v>
       </c>
       <c r="D55" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G55" s="4">
-        <v>300</v>
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -19413,19 +19396,19 @@
         <v>919</v>
       </c>
       <c r="C56" s="4">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="D56" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>344</v>
+        <v>29</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="G56" s="4">
-        <v>324</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -19436,30 +19419,30 @@
         <v>919</v>
       </c>
       <c r="C57" s="4">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="D57" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G57" s="4">
-        <v>77</v>
+        <v>324</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C58" s="4">
-        <v>2520</v>
+        <v>20</v>
       </c>
       <c r="D58" s="4">
         <v>5</v>
@@ -19471,7 +19454,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="4">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -19482,30 +19465,30 @@
         <v>921</v>
       </c>
       <c r="C59" s="4">
-        <v>4089</v>
+        <v>2520</v>
       </c>
       <c r="D59" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>130</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C60" s="4">
-        <v>21</v>
+        <v>4089</v>
       </c>
       <c r="D60" s="4">
         <v>25</v>
@@ -19517,18 +19500,18 @@
         <v>158</v>
       </c>
       <c r="G60" s="4">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C61" s="4">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="D61" s="4">
         <v>25</v>
@@ -19540,7 +19523,7 @@
         <v>158</v>
       </c>
       <c r="G61" s="4">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
@@ -19551,42 +19534,42 @@
         <v>925</v>
       </c>
       <c r="C62" s="4">
-        <v>2513</v>
+        <v>262</v>
       </c>
       <c r="D62" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G62" s="4">
-        <v>26</v>
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C63" s="4">
-        <v>16</v>
+        <v>2513</v>
       </c>
       <c r="D63" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G63" s="4">
-        <v>180</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -19597,65 +19580,65 @@
         <v>927</v>
       </c>
       <c r="C64" s="4">
-        <v>3114</v>
+        <v>16</v>
       </c>
       <c r="D64" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G64" s="4">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C65" s="4">
-        <v>4086</v>
+        <v>3114</v>
       </c>
       <c r="D65" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="4">
         <v>38</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G65" s="4">
-        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C66" s="4">
-        <v>15</v>
+        <v>4086</v>
       </c>
       <c r="D66" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G66" s="4">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -19666,42 +19649,42 @@
         <v>931</v>
       </c>
       <c r="C67" s="4">
-        <v>3115</v>
+        <v>15</v>
       </c>
       <c r="D67" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G67" s="4">
-        <v>40</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C68" s="4">
-        <v>4165</v>
+        <v>3115</v>
       </c>
       <c r="D68" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>280</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -19712,42 +19695,42 @@
         <v>933</v>
       </c>
       <c r="C69" s="4">
-        <v>4100</v>
+        <v>4165</v>
       </c>
       <c r="D69" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G69" s="4">
-        <v>143.5</v>
+        <v>240</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C70" s="4">
-        <v>4280</v>
+        <v>4100</v>
       </c>
       <c r="D70" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G70" s="4">
-        <v>360</v>
+        <v>123.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -19758,18 +19741,41 @@
         <v>935</v>
       </c>
       <c r="C71" s="4">
+        <v>4280</v>
+      </c>
+      <c r="D71" s="4">
+        <v>10</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G71" s="4">
+        <v>360</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="A72" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="C72" s="4">
         <v>4281</v>
       </c>
-      <c r="D71" s="4">
-        <v>5</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G71" s="4">
+      <c r="D72" s="4">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G72" s="4">
         <v>183.5</v>
       </c>
     </row>
@@ -19884,7 +19890,7 @@
         <v>158</v>
       </c>
       <c r="G4" s="4">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -19907,7 +19913,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>24</v>
+        <v>24.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -20298,7 +20304,7 @@
         <v>158</v>
       </c>
       <c r="G22" s="4">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
@@ -20321,7 +20327,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="4">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -20344,7 +20350,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -20367,7 +20373,7 @@
         <v>158</v>
       </c>
       <c r="G25" s="4">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
@@ -20390,7 +20396,7 @@
         <v>158</v>
       </c>
       <c r="G26" s="4">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
@@ -20413,7 +20419,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="4">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
@@ -20436,7 +20442,7 @@
         <v>158</v>
       </c>
       <c r="G28" s="4">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
@@ -20459,7 +20465,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="4">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -21103,7 +21109,7 @@
         <v>158</v>
       </c>
       <c r="G57" s="4">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
@@ -21126,7 +21132,7 @@
         <v>158</v>
       </c>
       <c r="G58" s="4">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -21149,7 +21155,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>31</v>
+        <v>30.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
@@ -21540,7 +21546,7 @@
         <v>158</v>
       </c>
       <c r="G76" s="5">
-        <v>187.5</v>
+        <v>179</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -21563,7 +21569,7 @@
         <v>158</v>
       </c>
       <c r="G77" s="4">
-        <v>375</v>
+        <v>358</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -21586,7 +21592,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="5">
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -21862,7 +21868,7 @@
         <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -21885,7 +21891,7 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -22022,7 +22028,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="4">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -22370,7 +22376,7 @@
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>391</v>
       </c>
@@ -22941,7 +22947,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="4">
-        <v>475</v>
+        <v>412.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -22964,7 +22970,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -23355,7 +23361,7 @@
         <v>158</v>
       </c>
       <c r="G20" s="4">
-        <v>1875</v>
+        <v>1750</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -23378,7 +23384,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="4">
-        <v>375</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
@@ -23608,7 +23614,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="5">
-        <v>77.5</v>
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -23631,7 +23637,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="6"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1141">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -4701,7 +4701,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="4">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -5046,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="4">
-        <v>675</v>
+        <v>850</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -5069,7 +5069,7 @@
         <v>10</v>
       </c>
       <c r="G18" s="5">
-        <v>337.5</v>
+        <v>425</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
@@ -5459,7 +5459,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="4">
-        <v>103.5</v>
+        <v>108.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -5482,7 +5482,7 @@
         <v>158</v>
       </c>
       <c r="G10" s="4">
-        <v>500</v>
+        <v>525</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -5689,7 +5689,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="5">
-        <v>162.5</v>
+        <v>202.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -5712,7 +5712,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="4">
-        <v>325</v>
+        <v>405</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -5965,7 +5965,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="4">
-        <v>1725</v>
+        <v>1850</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -5988,7 +5988,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>348.5</v>
+        <v>373.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -6070,7 +6070,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -6516,7 +6516,7 @@
         <v>158</v>
       </c>
       <c r="G19" s="4">
-        <v>450</v>
+        <v>575</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -6539,7 +6539,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -6608,7 +6608,7 @@
         <v>158</v>
       </c>
       <c r="G23" s="4">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -6631,7 +6631,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>200</v>
+        <v>260</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -6746,7 +6746,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>627.5</v>
+        <v>595</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -8103,7 +8103,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="5">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -8126,30 +8126,30 @@
         <v>158</v>
       </c>
       <c r="G89" s="4">
-        <v>280</v>
+        <v>310</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C90" s="4">
-        <v>4378</v>
+        <v>4225</v>
       </c>
       <c r="D90" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G90" s="4">
-        <v>430</v>
+        <v>775</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -8160,10 +8160,10 @@
         <v>448</v>
       </c>
       <c r="C91" s="4">
-        <v>4379</v>
+        <v>4378</v>
       </c>
       <c r="D91" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
@@ -8172,30 +8172,30 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>43</v>
+        <v>430</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C92" s="4">
-        <v>3524</v>
+        <v>4379</v>
       </c>
       <c r="D92" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>9</v>
+        <v>158</v>
       </c>
       <c r="G92" s="4">
-        <v>350</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -8206,10 +8206,10 @@
         <v>450</v>
       </c>
       <c r="C93" s="4">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="D93" s="4">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>29</v>
@@ -8218,30 +8218,30 @@
         <v>9</v>
       </c>
       <c r="G93" s="4">
-        <v>72</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C94" s="4">
-        <v>3521</v>
+        <v>3523</v>
       </c>
       <c r="D94" s="4">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>453</v>
+        <v>29</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G94" s="4">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
@@ -8252,53 +8252,53 @@
         <v>452</v>
       </c>
       <c r="C95" s="4">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="D95" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>74</v>
+        <v>453</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G95" s="5">
-        <v>216.5</v>
+      <c r="G95" s="4">
+        <v>158</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C96" s="4">
-        <v>64</v>
+        <v>3522</v>
       </c>
       <c r="D96" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G96" s="4">
-        <v>132</v>
+      <c r="G96" s="5">
+        <v>216.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C97" s="4">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D97" s="4">
         <v>8</v>
@@ -8315,25 +8315,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C98" s="4">
-        <v>3637</v>
+        <v>90</v>
       </c>
       <c r="D98" s="4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G98" s="4">
-        <v>375</v>
+        <v>132</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
@@ -8344,10 +8344,10 @@
         <v>459</v>
       </c>
       <c r="C99" s="4">
-        <v>2805</v>
+        <v>3637</v>
       </c>
       <c r="D99" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>29</v>
@@ -8356,7 +8356,7 @@
         <v>158</v>
       </c>
       <c r="G99" s="4">
-        <v>150</v>
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
@@ -8367,42 +8367,42 @@
         <v>459</v>
       </c>
       <c r="C100" s="4">
-        <v>2427</v>
+        <v>2805</v>
       </c>
       <c r="D100" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G100" s="4">
-        <v>46</v>
+        <v>150</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C101" s="4">
-        <v>3437</v>
+        <v>2427</v>
       </c>
       <c r="D101" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G101" s="4">
-        <v>350</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
@@ -8413,53 +8413,53 @@
         <v>461</v>
       </c>
       <c r="C102" s="4">
-        <v>3396</v>
+        <v>3437</v>
       </c>
       <c r="D102" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G102" s="4">
-        <v>178.5</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C103" s="4">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="D103" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>464</v>
+        <v>29</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G103" s="4">
-        <v>54</v>
+        <v>178.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C104" s="4">
-        <v>3490</v>
+        <v>3395</v>
       </c>
       <c r="D104" s="4">
         <v>12</v>
@@ -8471,41 +8471,41 @@
         <v>15</v>
       </c>
       <c r="G104" s="4">
-        <v>169</v>
+        <v>54</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C105" s="4">
-        <v>458</v>
+        <v>3490</v>
       </c>
       <c r="D105" s="4">
         <v>12</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>314</v>
+        <v>464</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G105" s="5">
-        <v>269.5</v>
+      <c r="G105" s="4">
+        <v>169</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C106" s="4">
-        <v>2641</v>
+        <v>458</v>
       </c>
       <c r="D106" s="4">
         <v>12</v>
@@ -8516,19 +8516,19 @@
       <c r="F106" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G106" s="4">
-        <v>222</v>
+      <c r="G106" s="5">
+        <v>269.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C107" s="4">
-        <v>4293</v>
+        <v>2641</v>
       </c>
       <c r="D107" s="4">
         <v>12</v>
@@ -8540,30 +8540,30 @@
         <v>15</v>
       </c>
       <c r="G107" s="4">
-        <v>210</v>
+        <v>222</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C108" s="4">
-        <v>2396</v>
+        <v>4293</v>
       </c>
       <c r="D108" s="4">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>29</v>
+        <v>314</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G108" s="4">
-        <v>575</v>
+        <v>210</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
@@ -8574,33 +8574,33 @@
         <v>474</v>
       </c>
       <c r="C109" s="4">
-        <v>2426</v>
+        <v>2396</v>
       </c>
       <c r="D109" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G109" s="4">
-        <v>118.5</v>
+        <v>675</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C110" s="4">
-        <v>4335</v>
+        <v>2426</v>
       </c>
       <c r="D110" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>29</v>
@@ -8609,18 +8609,18 @@
         <v>10</v>
       </c>
       <c r="G110" s="4">
-        <v>510</v>
+        <v>137</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C111" s="4">
-        <v>4477</v>
+        <v>4335</v>
       </c>
       <c r="D111" s="4">
         <v>3</v>
@@ -8632,18 +8632,18 @@
         <v>10</v>
       </c>
       <c r="G111" s="4">
-        <v>252</v>
+        <v>510</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C112" s="4">
-        <v>4479</v>
+        <v>4477</v>
       </c>
       <c r="D112" s="4">
         <v>3</v>
@@ -8660,13 +8660,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C113" s="4">
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="D113" s="4">
         <v>3</v>
@@ -8683,25 +8683,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C114" s="4">
-        <v>2646</v>
+        <v>4478</v>
       </c>
       <c r="D114" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>485</v>
+        <v>29</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G114" s="4">
-        <v>53</v>
+        <v>252</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
@@ -8712,19 +8712,19 @@
         <v>484</v>
       </c>
       <c r="C115" s="4">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="D115" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G115" s="5">
-        <v>81.5</v>
+      <c r="G115" s="4">
+        <v>53</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
@@ -8735,87 +8735,110 @@
         <v>484</v>
       </c>
       <c r="C116" s="4">
-        <v>2638</v>
+        <v>2645</v>
       </c>
       <c r="D116" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G116" s="4">
-        <v>70</v>
+      <c r="G116" s="5">
+        <v>81.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C117" s="4">
-        <v>4294</v>
+        <v>2638</v>
       </c>
       <c r="D117" s="4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G117" s="4">
-        <v>150</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C118" s="4">
-        <v>4314</v>
+        <v>4294</v>
       </c>
       <c r="D118" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>74</v>
+        <v>490</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G118" s="4">
-        <v>252</v>
+        <v>150</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C119" s="4">
-        <v>4315</v>
+        <v>4314</v>
       </c>
       <c r="D119" s="4">
         <v>15</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>495</v>
+        <v>74</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G119" s="4">
+        <v>252</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+      <c r="A120" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C120" s="4">
+        <v>4315</v>
+      </c>
+      <c r="D120" s="4">
+        <v>15</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" s="4">
         <v>450</v>
       </c>
     </row>
@@ -10113,7 +10136,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -12272,30 +12295,30 @@
         <v>187</v>
       </c>
       <c r="C94" s="4">
-        <v>4629</v>
+        <v>4643</v>
       </c>
       <c r="D94" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>165</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G94" s="4">
-        <v>195</v>
+        <v>188</v>
+      </c>
+      <c r="G94" s="5">
+        <v>97.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C95" s="4">
-        <v>4643</v>
+        <v>4687</v>
       </c>
       <c r="D95" s="4">
         <v>6</v>
@@ -12304,90 +12327,90 @@
         <v>165</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="G95" s="5">
-        <v>97.5</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C96" s="4">
-        <v>4630</v>
+        <v>4644</v>
       </c>
       <c r="D96" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>165</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" s="5">
-        <v>127.5</v>
+        <v>149</v>
+      </c>
+      <c r="G96" s="4">
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C97" s="4">
-        <v>4687</v>
+        <v>4104</v>
       </c>
       <c r="D97" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>165</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G97" s="5">
-        <v>64</v>
+        <v>49</v>
+      </c>
+      <c r="G97" s="4">
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C98" s="4">
-        <v>4644</v>
+        <v>4101</v>
       </c>
       <c r="D98" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>165</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="G98" s="4">
-        <v>113</v>
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C99" s="4">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="D99" s="4">
         <v>10</v>
@@ -12404,36 +12427,36 @@
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C100" s="4">
-        <v>4101</v>
+        <v>3705</v>
       </c>
       <c r="D100" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G100" s="4">
-        <v>77</v>
+      <c r="G100" s="5">
+        <v>123.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C101" s="4">
-        <v>4105</v>
+        <v>3823</v>
       </c>
       <c r="D101" s="4">
         <v>10</v>
@@ -12442,7 +12465,7 @@
         <v>165</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="G101" s="4">
         <v>77</v>
@@ -12450,197 +12473,197 @@
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C102" s="4">
-        <v>3705</v>
+        <v>4641</v>
       </c>
       <c r="D102" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G102" s="5">
-        <v>123.5</v>
+        <v>10</v>
+      </c>
+      <c r="G102" s="4">
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C103" s="4">
-        <v>3823</v>
+        <v>4583</v>
       </c>
       <c r="D103" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>165</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G103" s="4">
-        <v>77</v>
+        <v>144</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C104" s="4">
-        <v>4641</v>
+        <v>4308</v>
       </c>
       <c r="D104" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G104" s="4">
-        <v>72</v>
+      <c r="G104" s="5">
+        <v>68.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C105" s="4">
-        <v>4583</v>
+        <v>4309</v>
       </c>
       <c r="D105" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G105" s="4">
-        <v>144</v>
+        <v>149</v>
+      </c>
+      <c r="G105" s="5">
+        <v>68.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C106" s="4">
-        <v>4308</v>
+        <v>4635</v>
       </c>
       <c r="D106" s="4">
         <v>10</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>209</v>
+        <v>74</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" s="5">
-        <v>68.5</v>
+        <v>149</v>
+      </c>
+      <c r="G106" s="4">
+        <v>177</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C107" s="4">
-        <v>4309</v>
-      </c>
-      <c r="D107" s="4">
-        <v>10</v>
+        <v>4412</v>
+      </c>
+      <c r="D107" s="5">
+        <v>2.5</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>149</v>
       </c>
       <c r="G107" s="5">
-        <v>68.5</v>
+        <v>75.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C108" s="4">
-        <v>4635</v>
+        <v>4413</v>
       </c>
       <c r="D108" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="G108" s="4">
-        <v>177</v>
+        <v>496</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C109" s="4">
-        <v>4412</v>
-      </c>
-      <c r="D109" s="5">
-        <v>2.5</v>
+        <v>4414</v>
+      </c>
+      <c r="D109" s="4">
+        <v>5</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G109" s="5">
-        <v>75.5</v>
+        <v>10</v>
+      </c>
+      <c r="G109" s="4">
+        <v>101</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C110" s="4">
-        <v>4413</v>
+        <v>4415</v>
       </c>
       <c r="D110" s="4">
         <v>25</v>
@@ -12652,18 +12675,18 @@
         <v>10</v>
       </c>
       <c r="G110" s="4">
-        <v>496</v>
+        <v>424</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C111" s="4">
-        <v>4414</v>
+        <v>4416</v>
       </c>
       <c r="D111" s="4">
         <v>5</v>
@@ -12675,87 +12698,87 @@
         <v>10</v>
       </c>
       <c r="G111" s="4">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C112" s="4">
-        <v>4415</v>
+        <v>4475</v>
       </c>
       <c r="D112" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="4">
-        <v>424</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C113" s="4">
-        <v>4416</v>
+        <v>4354</v>
       </c>
       <c r="D113" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G113" s="4">
-        <v>88</v>
+        <v>9</v>
+      </c>
+      <c r="G113" s="5">
+        <v>79.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C114" s="4">
-        <v>4475</v>
+        <v>4445</v>
       </c>
       <c r="D114" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>222</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" s="4">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="G114" s="5">
+        <v>79.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C115" s="4">
-        <v>4354</v>
+        <v>4353</v>
       </c>
       <c r="D115" s="4">
         <v>12</v>
@@ -12764,7 +12787,7 @@
         <v>222</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G115" s="5">
         <v>79.5</v>
@@ -12772,13 +12795,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C116" s="4">
-        <v>4445</v>
+        <v>4350</v>
       </c>
       <c r="D116" s="4">
         <v>12</v>
@@ -12795,13 +12818,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C117" s="4">
-        <v>4353</v>
+        <v>4352</v>
       </c>
       <c r="D117" s="4">
         <v>12</v>
@@ -12818,13 +12841,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C118" s="4">
-        <v>4350</v>
+        <v>4349</v>
       </c>
       <c r="D118" s="4">
         <v>12</v>
@@ -12841,13 +12864,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C119" s="4">
-        <v>4352</v>
+        <v>4351</v>
       </c>
       <c r="D119" s="4">
         <v>12</v>
@@ -12864,13 +12887,13 @@
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C120" s="4">
-        <v>4349</v>
+        <v>4581</v>
       </c>
       <c r="D120" s="4">
         <v>12</v>
@@ -12887,231 +12910,185 @@
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C121" s="4">
-        <v>4351</v>
+        <v>4096</v>
       </c>
       <c r="D121" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G121" s="5">
-        <v>79.5</v>
+        <v>10</v>
+      </c>
+      <c r="G121" s="4">
+        <v>79</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C122" s="4">
-        <v>4581</v>
+        <v>4582</v>
       </c>
       <c r="D122" s="4">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G122" s="5">
-        <v>79.5</v>
+        <v>10</v>
+      </c>
+      <c r="G122" s="4">
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C123" s="4">
-        <v>4096</v>
+        <v>4123</v>
       </c>
       <c r="D123" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>29</v>
+        <v>201</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="4">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C124" s="4">
-        <v>4582</v>
+        <v>4306</v>
       </c>
       <c r="D124" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="G124" s="4">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C125" s="4">
-        <v>4123</v>
+        <v>4307</v>
       </c>
       <c r="D125" s="4">
         <v>10</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="G125" s="4">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C126" s="4">
-        <v>4306</v>
+        <v>2659</v>
       </c>
       <c r="D126" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="G126" s="4">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C127" s="4">
-        <v>4307</v>
+        <v>2621</v>
       </c>
       <c r="D127" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>165</v>
+        <v>253</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G127" s="4">
-        <v>81</v>
+        <v>49</v>
+      </c>
+      <c r="G127" s="5">
+        <v>25.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C128" s="4">
-        <v>2659</v>
+        <v>3656</v>
       </c>
       <c r="D128" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>252</v>
+        <v>165</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G128" s="4">
-        <v>30</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
-      <c r="A129" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C129" s="4">
-        <v>2621</v>
-      </c>
-      <c r="D129" s="4">
-        <v>5</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G129" s="5">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
-      <c r="A130" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C130" s="4">
-        <v>3656</v>
-      </c>
-      <c r="D130" s="4">
-        <v>5</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G130" s="4">
         <v>27</v>
       </c>
     </row>
@@ -14421,7 +14398,7 @@
         <v>158</v>
       </c>
       <c r="G40" s="4">
-        <v>195</v>
+        <v>215</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -14444,7 +14421,7 @@
         <v>10</v>
       </c>
       <c r="G41" s="4">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
@@ -14467,7 +14444,7 @@
         <v>10</v>
       </c>
       <c r="G42" s="4">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
@@ -14490,7 +14467,7 @@
         <v>158</v>
       </c>
       <c r="G43" s="4">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
@@ -14513,7 +14490,7 @@
         <v>10</v>
       </c>
       <c r="G44" s="4">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -14536,7 +14513,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="4">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
@@ -14559,7 +14536,7 @@
         <v>158</v>
       </c>
       <c r="G46" s="4">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -14582,7 +14559,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="4">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
@@ -14812,7 +14789,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="5">
-        <v>833.5</v>
+        <v>850.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
@@ -14835,7 +14812,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="4">
-        <v>1667</v>
+        <v>1701</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -14858,7 +14835,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>371</v>
+        <v>378.6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
@@ -14881,7 +14858,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="5">
-        <v>833.5</v>
+        <v>850.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
@@ -14904,7 +14881,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="4">
-        <v>1667</v>
+        <v>1701</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
@@ -14927,7 +14904,7 @@
         <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>371</v>
+        <v>378.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
@@ -18111,7 +18088,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -18695,7 +18672,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="4">
-        <v>270</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
@@ -18718,7 +18695,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="4">
-        <v>138.5</v>
+        <v>165</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
@@ -18787,7 +18764,7 @@
         <v>158</v>
       </c>
       <c r="G29" s="4">
-        <v>675</v>
+        <v>925</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -18798,10 +18775,10 @@
         <v>893</v>
       </c>
       <c r="C30" s="4">
-        <v>4676</v>
+        <v>4163</v>
       </c>
       <c r="D30" s="4">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>29</v>
@@ -18810,7 +18787,7 @@
         <v>158</v>
       </c>
       <c r="G30" s="4">
-        <v>337.5</v>
+        <v>370</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -18821,33 +18798,33 @@
         <v>893</v>
       </c>
       <c r="C31" s="4">
-        <v>4163</v>
+        <v>4117</v>
       </c>
       <c r="D31" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G31" s="4">
-        <v>270</v>
+        <v>187</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C32" s="4">
-        <v>4117</v>
+        <v>3738</v>
       </c>
       <c r="D32" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>29</v>
@@ -18856,7 +18833,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="4">
-        <v>138.5</v>
+        <v>100</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
@@ -18867,10 +18844,10 @@
         <v>895</v>
       </c>
       <c r="C33" s="4">
-        <v>3738</v>
+        <v>4317</v>
       </c>
       <c r="D33" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>29</v>
@@ -18879,21 +18856,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="4">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C34" s="4">
-        <v>4317</v>
+        <v>2924</v>
       </c>
       <c r="D34" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>29</v>
@@ -18902,7 +18879,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>52</v>
+        <v>168</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -18913,10 +18890,10 @@
         <v>897</v>
       </c>
       <c r="C35" s="4">
-        <v>2924</v>
+        <v>3078</v>
       </c>
       <c r="D35" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>29</v>
@@ -18925,30 +18902,30 @@
         <v>10</v>
       </c>
       <c r="G35" s="4">
-        <v>168</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C36" s="4">
-        <v>3078</v>
+        <v>2348</v>
       </c>
       <c r="D36" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G36" s="4">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
@@ -18959,10 +18936,10 @@
         <v>899</v>
       </c>
       <c r="C37" s="4">
-        <v>2348</v>
+        <v>2538</v>
       </c>
       <c r="D37" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>29</v>
@@ -18971,18 +18948,18 @@
         <v>158</v>
       </c>
       <c r="G37" s="4">
-        <v>160</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C38" s="4">
-        <v>2538</v>
+        <v>2811</v>
       </c>
       <c r="D38" s="4">
         <v>5</v>
@@ -18991,10 +18968,10 @@
         <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G38" s="4">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="G38" s="5">
+        <v>104.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
@@ -19005,10 +18982,10 @@
         <v>901</v>
       </c>
       <c r="C39" s="4">
-        <v>2811</v>
+        <v>2820</v>
       </c>
       <c r="D39" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>29</v>
@@ -19016,22 +18993,22 @@
       <c r="F39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="5">
-        <v>104.5</v>
+      <c r="G39" s="4">
+        <v>205</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C40" s="4">
-        <v>2820</v>
+        <v>3722</v>
       </c>
       <c r="D40" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>29</v>
@@ -19040,7 +19017,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="4">
-        <v>205</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -19051,30 +19028,30 @@
         <v>903</v>
       </c>
       <c r="C41" s="4">
-        <v>3722</v>
+        <v>4050</v>
       </c>
       <c r="D41" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G41" s="4">
-        <v>66</v>
+        <v>128</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C42" s="4">
-        <v>4050</v>
+        <v>415</v>
       </c>
       <c r="D42" s="4">
         <v>10</v>
@@ -19083,21 +19060,21 @@
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G42" s="4">
-        <v>128</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C43" s="4">
-        <v>415</v>
+        <v>93</v>
       </c>
       <c r="D43" s="4">
         <v>10</v>
@@ -19109,30 +19086,30 @@
         <v>10</v>
       </c>
       <c r="G43" s="4">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C44" s="4">
-        <v>93</v>
+        <v>261</v>
       </c>
       <c r="D44" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G44" s="4">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
@@ -19143,42 +19120,42 @@
         <v>909</v>
       </c>
       <c r="C45" s="4">
-        <v>261</v>
+        <v>2475</v>
       </c>
       <c r="D45" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G45" s="4">
-        <v>83</v>
+        <v>10</v>
+      </c>
+      <c r="G45" s="5">
+        <v>18.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C46" s="4">
-        <v>2475</v>
+        <v>92</v>
       </c>
       <c r="D46" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="5">
-        <v>18.5</v>
+        <v>158</v>
+      </c>
+      <c r="G46" s="4">
+        <v>67</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -19189,42 +19166,42 @@
         <v>911</v>
       </c>
       <c r="C47" s="4">
-        <v>92</v>
+        <v>2476</v>
       </c>
       <c r="D47" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G47" s="4">
-        <v>67</v>
+        <v>10</v>
+      </c>
+      <c r="G47" s="5">
+        <v>11.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C48" s="4">
-        <v>2476</v>
+        <v>18</v>
       </c>
       <c r="D48" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="5">
-        <v>11.5</v>
+        <v>158</v>
+      </c>
+      <c r="G48" s="4">
+        <v>96</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
@@ -19235,42 +19212,42 @@
         <v>913</v>
       </c>
       <c r="C49" s="4">
-        <v>18</v>
+        <v>2477</v>
       </c>
       <c r="D49" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G49" s="4">
-        <v>96</v>
+        <v>22.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C50" s="4">
-        <v>2477</v>
+        <v>4164</v>
       </c>
       <c r="D50" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G50" s="4">
-        <v>22.5</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -19281,42 +19258,42 @@
         <v>915</v>
       </c>
       <c r="C51" s="4">
-        <v>4164</v>
+        <v>3706</v>
       </c>
       <c r="D51" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G51" s="4">
-        <v>170</v>
+        <v>92</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C52" s="4">
-        <v>3706</v>
+        <v>19</v>
       </c>
       <c r="D52" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G52" s="4">
-        <v>88</v>
+        <v>168</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -19327,19 +19304,19 @@
         <v>917</v>
       </c>
       <c r="C53" s="4">
-        <v>19</v>
+        <v>2246</v>
       </c>
       <c r="D53" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G53" s="4">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
@@ -19350,42 +19327,42 @@
         <v>917</v>
       </c>
       <c r="C54" s="4">
-        <v>2246</v>
+        <v>575</v>
       </c>
       <c r="D54" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>344</v>
+        <v>29</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G54" s="4">
-        <v>192</v>
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="3" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C55" s="4">
-        <v>575</v>
+        <v>221</v>
       </c>
       <c r="D55" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G55" s="4">
-        <v>48</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -19396,19 +19373,19 @@
         <v>919</v>
       </c>
       <c r="C56" s="4">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="D56" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="G56" s="4">
-        <v>300</v>
+        <v>324</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
@@ -19419,30 +19396,30 @@
         <v>919</v>
       </c>
       <c r="C57" s="4">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="D57" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>344</v>
+        <v>29</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G57" s="4">
-        <v>324</v>
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C58" s="4">
-        <v>20</v>
+        <v>2520</v>
       </c>
       <c r="D58" s="4">
         <v>5</v>
@@ -19454,7 +19431,7 @@
         <v>10</v>
       </c>
       <c r="G58" s="4">
-        <v>77</v>
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -19465,30 +19442,30 @@
         <v>921</v>
       </c>
       <c r="C59" s="4">
-        <v>2520</v>
+        <v>4089</v>
       </c>
       <c r="D59" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4">
-        <v>29</v>
+        <v>130</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C60" s="4">
-        <v>4089</v>
+        <v>21</v>
       </c>
       <c r="D60" s="4">
         <v>25</v>
@@ -19500,18 +19477,18 @@
         <v>158</v>
       </c>
       <c r="G60" s="4">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="3" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C61" s="4">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="D61" s="4">
         <v>25</v>
@@ -19523,7 +19500,7 @@
         <v>158</v>
       </c>
       <c r="G61" s="4">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
@@ -19534,42 +19511,42 @@
         <v>925</v>
       </c>
       <c r="C62" s="4">
-        <v>262</v>
+        <v>2513</v>
       </c>
       <c r="D62" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>119</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C63" s="4">
-        <v>2513</v>
+        <v>16</v>
       </c>
       <c r="D63" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G63" s="4">
-        <v>26</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
@@ -19580,65 +19557,65 @@
         <v>927</v>
       </c>
       <c r="C64" s="4">
-        <v>16</v>
+        <v>3114</v>
       </c>
       <c r="D64" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G64" s="4">
-        <v>180</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C65" s="4">
-        <v>3114</v>
+        <v>4086</v>
       </c>
       <c r="D65" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G65" s="4">
-        <v>38</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C66" s="4">
-        <v>4086</v>
+        <v>15</v>
       </c>
       <c r="D66" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="G66" s="4">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -19649,42 +19626,42 @@
         <v>931</v>
       </c>
       <c r="C67" s="4">
-        <v>15</v>
+        <v>3115</v>
       </c>
       <c r="D67" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G67" s="4">
-        <v>190</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C68" s="4">
-        <v>3115</v>
+        <v>4165</v>
       </c>
       <c r="D68" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G68" s="4">
-        <v>40</v>
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -19695,42 +19672,42 @@
         <v>933</v>
       </c>
       <c r="C69" s="4">
-        <v>4165</v>
+        <v>4100</v>
       </c>
       <c r="D69" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G69" s="4">
-        <v>240</v>
+        <v>143.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C70" s="4">
-        <v>4100</v>
+        <v>4280</v>
       </c>
       <c r="D70" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G70" s="4">
-        <v>123.5</v>
+        <v>360</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -19741,10 +19718,10 @@
         <v>935</v>
       </c>
       <c r="C71" s="4">
-        <v>4280</v>
+        <v>4281</v>
       </c>
       <c r="D71" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
@@ -19753,29 +19730,6 @@
         <v>158</v>
       </c>
       <c r="G71" s="4">
-        <v>360</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="C72" s="4">
-        <v>4281</v>
-      </c>
-      <c r="D72" s="4">
-        <v>5</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G72" s="4">
         <v>183.5</v>
       </c>
     </row>
@@ -19890,7 +19844,7 @@
         <v>158</v>
       </c>
       <c r="G4" s="4">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -19913,7 +19867,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>24.5</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -20304,7 +20258,7 @@
         <v>158</v>
       </c>
       <c r="G22" s="4">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
@@ -20327,7 +20281,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -20350,7 +20304,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -20373,7 +20327,7 @@
         <v>158</v>
       </c>
       <c r="G25" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
@@ -20396,7 +20350,7 @@
         <v>158</v>
       </c>
       <c r="G26" s="4">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
@@ -20419,7 +20373,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
@@ -20442,7 +20396,7 @@
         <v>158</v>
       </c>
       <c r="G28" s="4">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
@@ -20465,7 +20419,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
@@ -21109,7 +21063,7 @@
         <v>158</v>
       </c>
       <c r="G57" s="4">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
@@ -21132,7 +21086,7 @@
         <v>158</v>
       </c>
       <c r="G58" s="4">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -21155,7 +21109,7 @@
         <v>10</v>
       </c>
       <c r="G59" s="4">
-        <v>30.5</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
@@ -21546,7 +21500,7 @@
         <v>158</v>
       </c>
       <c r="G76" s="5">
-        <v>179</v>
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -21569,7 +21523,7 @@
         <v>158</v>
       </c>
       <c r="G77" s="4">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -21592,7 +21546,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="5">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -21868,7 +21822,7 @@
         <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -21891,7 +21845,7 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -22028,7 +21982,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="4">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -22376,7 +22330,7 @@
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
         <v>391</v>
       </c>
@@ -22947,7 +22901,7 @@
         <v>158</v>
       </c>
       <c r="G2" s="4">
-        <v>412.5</v>
+        <v>475</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -22970,7 +22924,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="4">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -23361,7 +23315,7 @@
         <v>158</v>
       </c>
       <c r="G20" s="4">
-        <v>1750</v>
+        <v>1875</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -23384,7 +23338,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="4">
-        <v>350</v>
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
@@ -23614,7 +23568,7 @@
         <v>158</v>
       </c>
       <c r="G31" s="5">
-        <v>73</v>
+        <v>77.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -23637,7 +23591,7 @@
         <v>158</v>
       </c>
       <c r="G32" s="4">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -24925,7 +24879,7 @@
         <v>158</v>
       </c>
       <c r="G88" s="4">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -24948,7 +24902,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="5">
-        <v>38.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="16"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1142">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3430,6 +3430,9 @@
   </si>
   <si>
     <t>MACADAMIA TORRADA S/SAL</t>
+  </si>
+  <si>
+    <t>x1.1KG</t>
   </si>
   <si>
     <t>mix-de-castanhas</t>
@@ -3461,7 +3464,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3479,12 +3482,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3536,7 +3533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3557,9 +3554,6 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -4178,7 +4172,7 @@
         <v>158</v>
       </c>
       <c r="G13" s="4">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -4201,7 +4195,7 @@
         <v>158</v>
       </c>
       <c r="G14" s="4">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -5079,10 +5073,10 @@
       <c r="B19" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="4">
         <v>4700</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="4">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -5091,7 +5085,7 @@
       <c r="F19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="4">
         <v>280</v>
       </c>
     </row>
@@ -9113,7 +9107,7 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -9135,7 +9129,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -12271,10 +12265,10 @@
       <c r="B93" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="4">
         <v>4699</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="4">
         <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
@@ -12283,7 +12277,7 @@
       <c r="F93" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="4">
         <v>30</v>
       </c>
     </row>
@@ -13478,7 +13472,7 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -13500,7 +13494,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -15378,7 +15372,7 @@
         <v>4021</v>
       </c>
       <c r="D83" s="4">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
@@ -15387,7 +15381,7 @@
         <v>10</v>
       </c>
       <c r="G83" s="4">
-        <v>125</v>
+        <v>116.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -15401,24 +15395,24 @@
         <v>4135</v>
       </c>
       <c r="D84" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>29</v>
+        <v>1133</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G84" s="4">
-        <v>1250</v>
+        <v>1398</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C85" s="4">
         <v>2852</v>
@@ -15438,10 +15432,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C86" s="4">
         <v>3601</v>
@@ -15461,10 +15455,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C87" s="4">
         <v>263</v>
@@ -15484,10 +15478,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C88" s="4">
         <v>2632</v>
@@ -15507,10 +15501,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C89" s="4">
         <v>2330</v>
@@ -15530,10 +15524,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C90" s="4">
         <v>2385</v>
@@ -15553,10 +15547,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C91" s="4">
         <v>2384</v>
@@ -15576,10 +15570,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C92" s="4">
         <v>3851</v>
@@ -15599,10 +15593,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C93" s="4">
         <v>2424</v>
@@ -21457,7 +21451,7 @@
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="3" t="s">
         <v>844</v>
       </c>
@@ -21480,7 +21474,7 @@
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="3" t="s">
         <v>846</v>
       </c>
@@ -21503,7 +21497,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="3" t="s">
         <v>846</v>
       </c>
@@ -21526,7 +21520,7 @@
         <v>375</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="3" t="s">
         <v>846</v>
       </c>
@@ -21549,7 +21543,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="3" t="s">
         <v>848</v>
       </c>
@@ -21572,7 +21566,7 @@
         <v>544</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="3" t="s">
         <v>848</v>
       </c>
@@ -21595,7 +21589,7 @@
         <v>272</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="3" t="s">
         <v>848</v>
       </c>
@@ -21618,7 +21612,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="3" t="s">
         <v>850</v>
       </c>
@@ -21641,7 +21635,7 @@
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="3" t="s">
         <v>852</v>
       </c>
@@ -21664,7 +21658,7 @@
         <v>182</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="3" t="s">
         <v>852</v>
       </c>
@@ -21687,7 +21681,7 @@
         <v>350</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
       <c r="A85" s="3" t="s">
         <v>852</v>
       </c>
@@ -21710,7 +21704,7 @@
         <v>700</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="3" t="s">
         <v>852</v>
       </c>
@@ -21733,7 +21727,7 @@
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="3" t="s">
         <v>854</v>
       </c>
@@ -21756,7 +21750,7 @@
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="3" t="s">
         <v>856</v>
       </c>
@@ -21779,7 +21773,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="3" t="s">
         <v>858</v>
       </c>
@@ -21802,7 +21796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="3" t="s">
         <v>860</v>
       </c>
@@ -21825,7 +21819,7 @@
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
       <c r="A91" s="3" t="s">
         <v>860</v>
       </c>
@@ -21848,7 +21842,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
       <c r="A92" s="3" t="s">
         <v>860</v>
       </c>
@@ -21871,7 +21865,7 @@
         <v>228</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
       <c r="A93" s="3" t="s">
         <v>862</v>
       </c>
@@ -21894,7 +21888,7 @@
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
       <c r="A94" s="3" t="s">
         <v>862</v>
       </c>
@@ -21936,7 +21930,7 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -21958,7 +21952,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -8649,7 +8649,7 @@
         <v>10</v>
       </c>
       <c r="G112" s="4">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
@@ -8672,7 +8672,7 @@
         <v>10</v>
       </c>
       <c r="G113" s="4">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
@@ -8695,7 +8695,7 @@
         <v>10</v>
       </c>
       <c r="G114" s="4">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
@@ -11959,7 +11959,7 @@
         <v>124</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="3" t="s">
         <v>154</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>195</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="3" t="s">
         <v>156</v>
       </c>
@@ -12005,7 +12005,7 @@
         <v>880</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="3" t="s">
         <v>156</v>
       </c>
@@ -12028,7 +12028,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="3" t="s">
         <v>159</v>
       </c>
@@ -12051,7 +12051,7 @@
         <v>225.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="3" t="s">
         <v>161</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
       <c r="A85" s="3" t="s">
         <v>163</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="3" t="s">
         <v>166</v>
       </c>
@@ -12120,7 +12120,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="3" t="s">
         <v>168</v>
       </c>
@@ -12143,7 +12143,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="3" t="s">
         <v>170</v>
       </c>
@@ -12166,7 +12166,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="3" t="s">
         <v>173</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="3" t="s">
         <v>176</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
       <c r="A91" s="3" t="s">
         <v>179</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
       <c r="A92" s="3" t="s">
         <v>181</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
       <c r="A93" s="3" t="s">
         <v>183</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
       <c r="A94" s="3" t="s">
         <v>186</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
         <v>189</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="19.5">
       <c r="A96" s="3" t="s">
         <v>191</v>
       </c>
@@ -12350,7 +12350,7 @@
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="19.5">
       <c r="A97" s="3" t="s">
         <v>193</v>
       </c>
@@ -12373,7 +12373,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="19.5">
       <c r="A98" s="3" t="s">
         <v>195</v>
       </c>
@@ -12396,7 +12396,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="19.5">
       <c r="A99" s="3" t="s">
         <v>197</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="19.5">
       <c r="A100" s="3" t="s">
         <v>199</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>123.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
       <c r="A101" s="3" t="s">
         <v>202</v>
       </c>
@@ -12465,7 +12465,7 @@
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="19.5">
       <c r="A102" s="3" t="s">
         <v>204</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="19.5">
       <c r="A103" s="3" t="s">
         <v>204</v>
       </c>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="1144">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3451,6 +3451,12 @@
   </si>
   <si>
     <t>NOZES QUARTOS</t>
+  </si>
+  <si>
+    <t>nozes-moscada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOZ MOSCADA EM PÓ </t>
   </si>
   <si>
     <t>xerem-de-amendoim</t>
@@ -3533,7 +3539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3558,6 +3564,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -13463,7 +13475,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -15552,65 +15564,88 @@
       <c r="B91" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="C91" s="4">
-        <v>2384</v>
-      </c>
-      <c r="D91" s="4">
-        <v>25</v>
+      <c r="C91" s="10">
+        <v>4540</v>
+      </c>
+      <c r="D91" s="10">
+        <v>10</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G91" s="5">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="G91" s="11">
+        <v>650</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C92" s="4">
-        <v>3851</v>
+        <v>2384</v>
       </c>
       <c r="D92" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G92" s="4">
-        <v>75</v>
+        <v>15</v>
+      </c>
+      <c r="G92" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C93" s="4">
+        <v>3851</v>
+      </c>
+      <c r="D93" s="4">
+        <v>10</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G93" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C94" s="4">
         <v>2424</v>
       </c>
-      <c r="D93" s="4">
-        <v>5</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="5">
+      <c r="D94" s="4">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="5">
         <v>39.5</v>
       </c>
     </row>
@@ -16643,7 +16678,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="4">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
@@ -16666,7 +16701,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -16781,7 +16816,7 @@
         <v>158</v>
       </c>
       <c r="G22" s="4">
-        <v>530</v>
+        <v>440</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
@@ -16804,7 +16839,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="4">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
@@ -17356,7 +17391,7 @@
         <v>158</v>
       </c>
       <c r="G47" s="4">
-        <v>625</v>
+        <v>600</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
@@ -17379,7 +17414,7 @@
         <v>158</v>
       </c>
       <c r="G48" s="4">
-        <v>520</v>
+        <v>480</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -17402,7 +17437,7 @@
         <v>10</v>
       </c>
       <c r="G49" s="4">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
@@ -19737,7 +19772,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -20784,7 +20819,7 @@
         <v>330</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
         <v>818</v>
       </c>
@@ -20792,10 +20827,10 @@
         <v>819</v>
       </c>
       <c r="C46" s="4">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D46" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>29</v>
@@ -20804,7 +20839,7 @@
         <v>158</v>
       </c>
       <c r="G46" s="5">
-        <v>115</v>
+        <v>138</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
@@ -20815,10 +20850,10 @@
         <v>819</v>
       </c>
       <c r="C47" s="4">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D47" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>29</v>
@@ -20826,22 +20861,22 @@
       <c r="F47" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G47" s="4">
-        <v>26</v>
+      <c r="G47" s="5">
+        <v>115</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C48" s="4">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D48" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>29</v>
@@ -20850,7 +20885,7 @@
         <v>158</v>
       </c>
       <c r="G48" s="4">
-        <v>170</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -20861,42 +20896,42 @@
         <v>821</v>
       </c>
       <c r="C49" s="4">
+        <v>3025</v>
+      </c>
+      <c r="D49" s="4">
+        <v>30</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G49" s="4">
+        <v>170</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
+      <c r="A50" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="C50" s="4">
         <v>2543</v>
       </c>
-      <c r="D49" s="4">
-        <v>5</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="5">
+      <c r="D50" s="4">
+        <v>5</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="5">
         <v>31.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C50" s="4">
-        <v>98</v>
-      </c>
-      <c r="D50" s="4">
-        <v>30</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G50" s="4">
-        <v>320</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -20907,42 +20942,42 @@
         <v>823</v>
       </c>
       <c r="C51" s="4">
+        <v>98</v>
+      </c>
+      <c r="D51" s="4">
+        <v>30</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" s="4">
+        <v>320</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+      <c r="A52" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C52" s="4">
         <v>35</v>
       </c>
-      <c r="D51" s="4">
-        <v>5</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G51" s="5">
+      <c r="D52" s="4">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G52" s="5">
         <v>55.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="19.5">
-      <c r="A52" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="C52" s="4">
-        <v>2353</v>
-      </c>
-      <c r="D52" s="4">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G52" s="5">
-        <v>362.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="19.5">
@@ -20953,42 +20988,42 @@
         <v>825</v>
       </c>
       <c r="C53" s="4">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D53" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G53" s="5">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="19.5">
       <c r="A54" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C54" s="4">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D54" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G54" s="4">
-        <v>255</v>
+        <v>10</v>
+      </c>
+      <c r="G54" s="5">
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="19.5">
@@ -20999,10 +21034,10 @@
         <v>827</v>
       </c>
       <c r="C55" s="4">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D55" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>29</v>
@@ -21010,8 +21045,8 @@
       <c r="F55" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G55" s="5">
-        <v>212.5</v>
+      <c r="G55" s="4">
+        <v>255</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
@@ -21022,42 +21057,42 @@
         <v>827</v>
       </c>
       <c r="C56" s="4">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D56" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G56" s="5">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C57" s="4">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D57" s="4">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G57" s="4">
-        <v>350</v>
+        <v>10</v>
+      </c>
+      <c r="G57" s="5">
+        <v>44.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
@@ -21068,10 +21103,10 @@
         <v>829</v>
       </c>
       <c r="C58" s="4">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D58" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>29</v>
@@ -21080,7 +21115,7 @@
         <v>158</v>
       </c>
       <c r="G58" s="4">
-        <v>175</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
@@ -21091,42 +21126,42 @@
         <v>829</v>
       </c>
       <c r="C59" s="4">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D59" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4">
-        <v>32</v>
+        <v>175</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C60" s="4">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D60" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G60" s="4">
-        <v>275</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
@@ -21137,42 +21172,42 @@
         <v>831</v>
       </c>
       <c r="C61" s="4">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D61" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G61" s="4">
-        <v>57</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C62" s="4">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D62" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G62" s="4">
-        <v>280</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
@@ -21183,10 +21218,10 @@
         <v>833</v>
       </c>
       <c r="C63" s="4">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D63" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>29</v>
@@ -21194,22 +21229,22 @@
       <c r="F63" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G63" s="5">
-        <v>48.5</v>
+      <c r="G63" s="4">
+        <v>280</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C64" s="4">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D64" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>29</v>
@@ -21217,8 +21252,8 @@
       <c r="F64" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G64" s="4">
-        <v>375</v>
+      <c r="G64" s="5">
+        <v>48.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
@@ -21229,42 +21264,42 @@
         <v>835</v>
       </c>
       <c r="C65" s="4">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D65" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="5">
-        <v>64.5</v>
+        <v>158</v>
+      </c>
+      <c r="G65" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C66" s="4">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D66" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G66" s="4">
-        <v>330</v>
+        <v>10</v>
+      </c>
+      <c r="G66" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
@@ -21275,42 +21310,42 @@
         <v>837</v>
       </c>
       <c r="C67" s="4">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D67" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G67" s="4">
-        <v>57</v>
+        <v>330</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C68" s="4">
-        <v>3740</v>
+        <v>2468</v>
       </c>
       <c r="D68" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>237.5</v>
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
@@ -21321,42 +21356,42 @@
         <v>839</v>
       </c>
       <c r="C69" s="4">
-        <v>2469</v>
+        <v>3740</v>
       </c>
       <c r="D69" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="5">
-        <v>50.5</v>
+        <v>158</v>
+      </c>
+      <c r="G69" s="4">
+        <v>237.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C70" s="4">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D70" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G70" s="5">
-        <v>312.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
@@ -21367,42 +21402,42 @@
         <v>841</v>
       </c>
       <c r="C71" s="4">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D71" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G71" s="5">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C72" s="4">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D72" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G72" s="4">
-        <v>300</v>
+        <v>10</v>
+      </c>
+      <c r="G72" s="5">
+        <v>64.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
@@ -21413,42 +21448,42 @@
         <v>843</v>
       </c>
       <c r="C73" s="4">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D73" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G73" s="4">
-        <v>62</v>
+        <v>300</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C74" s="4">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D74" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G74" s="4">
-        <v>180</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
@@ -21459,42 +21494,42 @@
         <v>845</v>
       </c>
       <c r="C75" s="4">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D75" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G75" s="4">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C76" s="4">
-        <v>211</v>
-      </c>
-      <c r="D76" s="5">
-        <v>22.68</v>
+        <v>2321</v>
+      </c>
+      <c r="D76" s="4">
+        <v>5</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G76" s="5">
-        <v>187.5</v>
+        <v>10</v>
+      </c>
+      <c r="G76" s="4">
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
@@ -21505,10 +21540,10 @@
         <v>847</v>
       </c>
       <c r="C77" s="4">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D77" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>29</v>
@@ -21516,8 +21551,8 @@
       <c r="F77" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G77" s="4">
-        <v>375</v>
+      <c r="G77" s="5">
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
@@ -21528,42 +21563,42 @@
         <v>847</v>
       </c>
       <c r="C78" s="4">
-        <v>2322</v>
-      </c>
-      <c r="D78" s="4">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="D78" s="5">
+        <v>45.36</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="5">
-        <v>43.5</v>
+        <v>158</v>
+      </c>
+      <c r="G78" s="4">
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C79" s="4">
-        <v>67</v>
-      </c>
-      <c r="D79" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D79" s="4">
+        <v>5</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G79" s="4">
-        <v>544</v>
+        <v>10</v>
+      </c>
+      <c r="G79" s="5">
+        <v>43.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
@@ -21574,10 +21609,10 @@
         <v>849</v>
       </c>
       <c r="C80" s="4">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D80" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>29</v>
@@ -21586,7 +21621,7 @@
         <v>158</v>
       </c>
       <c r="G80" s="4">
-        <v>272</v>
+        <v>544</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
@@ -21597,65 +21632,65 @@
         <v>849</v>
       </c>
       <c r="C81" s="4">
-        <v>2488</v>
-      </c>
-      <c r="D81" s="4">
-        <v>5</v>
+        <v>2244</v>
+      </c>
+      <c r="D81" s="5">
+        <v>22.68</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G81" s="4">
-        <v>63</v>
+        <v>272</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C82" s="4">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D82" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G82" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C83" s="4">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D83" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G83" s="4">
-        <v>182</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
@@ -21666,19 +21701,19 @@
         <v>853</v>
       </c>
       <c r="C84" s="4">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D84" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G84" s="4">
-        <v>350</v>
+        <v>182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
@@ -21689,10 +21724,10 @@
         <v>853</v>
       </c>
       <c r="C85" s="4">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D85" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>29</v>
@@ -21701,7 +21736,7 @@
         <v>158</v>
       </c>
       <c r="G85" s="4">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
@@ -21712,56 +21747,56 @@
         <v>853</v>
       </c>
       <c r="C86" s="4">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D86" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="G86" s="4">
-        <v>106</v>
+        <v>700</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C87" s="4">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D87" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>158</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C88" s="4">
-        <v>135</v>
-      </c>
-      <c r="D88" s="5">
-        <v>22.68</v>
+        <v>3110</v>
+      </c>
+      <c r="D88" s="4">
+        <v>25</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
@@ -21770,21 +21805,21 @@
         <v>158</v>
       </c>
       <c r="G88" s="4">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C89" s="4">
-        <v>2463</v>
-      </c>
-      <c r="D89" s="4">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="D89" s="5">
+        <v>22.68</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>29</v>
@@ -21793,21 +21828,21 @@
         <v>158</v>
       </c>
       <c r="G89" s="4">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C90" s="4">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D90" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>29</v>
@@ -21816,7 +21851,7 @@
         <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>114</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="19.5">
@@ -21827,10 +21862,10 @@
         <v>861</v>
       </c>
       <c r="C91" s="4">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D91" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>29</v>
@@ -21839,7 +21874,7 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>27</v>
+        <v>114</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
@@ -21850,10 +21885,10 @@
         <v>861</v>
       </c>
       <c r="C92" s="4">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D92" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>29</v>
@@ -21862,21 +21897,21 @@
         <v>158</v>
       </c>
       <c r="G92" s="4">
-        <v>228</v>
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
       <c r="A93" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C93" s="4">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D93" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>29</v>
@@ -21885,7 +21920,7 @@
         <v>158</v>
       </c>
       <c r="G93" s="4">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
@@ -21896,18 +21931,41 @@
         <v>863</v>
       </c>
       <c r="C94" s="4">
+        <v>4223</v>
+      </c>
+      <c r="D94" s="4">
+        <v>25</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G94" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
+      <c r="A95" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="C95" s="4">
         <v>4224</v>
       </c>
-      <c r="D94" s="4">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" s="4">
+      <c r="D95" s="4">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="4">
         <v>27</v>
       </c>
     </row>
@@ -22068,7 +22126,7 @@
         <v>158</v>
       </c>
       <c r="G6" s="4">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -22482,7 +22540,7 @@
         <v>158</v>
       </c>
       <c r="G24" s="4">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
@@ -22505,7 +22563,7 @@
         <v>158</v>
       </c>
       <c r="G25" s="4">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
@@ -22689,7 +22747,7 @@
         <v>158</v>
       </c>
       <c r="G33" s="4">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -22712,7 +22770,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>37</v>
+        <v>38.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -22735,7 +22793,7 @@
         <v>158</v>
       </c>
       <c r="G35" s="4">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -22758,7 +22816,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="4">
-        <v>37</v>
+        <v>38.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
@@ -23171,7 +23229,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="4">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -23194,7 +23252,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="4">
-        <v>490</v>
+        <v>470</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3470,7 +3470,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3488,6 +3488,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3568,10 +3574,10 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -5373,7 +5379,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="5">
-        <v>64.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -5396,7 +5402,7 @@
         <v>158</v>
       </c>
       <c r="G6" s="5">
-        <v>312.5</v>
+        <v>322.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -15189,7 +15195,7 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="3" t="s">
         <v>1122</v>
       </c>
@@ -15212,7 +15218,7 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="3" t="s">
         <v>1122</v>
       </c>
@@ -15235,7 +15241,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="3" t="s">
         <v>1125</v>
       </c>
@@ -15258,7 +15264,7 @@
         <v>166</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="3" t="s">
         <v>1125</v>
       </c>
@@ -15281,7 +15287,7 @@
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="3" t="s">
         <v>1127</v>
       </c>
@@ -15304,7 +15310,7 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="19.5">
       <c r="A80" s="3" t="s">
         <v>1127</v>
       </c>
@@ -15327,7 +15333,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="19.5">
       <c r="A81" s="3" t="s">
         <v>1129</v>
       </c>
@@ -15350,7 +15356,7 @@
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="19.5">
       <c r="A82" s="3" t="s">
         <v>1129</v>
       </c>
@@ -15373,7 +15379,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="19.5">
       <c r="A83" s="3" t="s">
         <v>1131</v>
       </c>
@@ -15396,7 +15402,7 @@
         <v>116.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="19.5">
       <c r="A84" s="3" t="s">
         <v>1131</v>
       </c>
@@ -15419,7 +15425,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="19.5">
       <c r="A85" s="3" t="s">
         <v>1134</v>
       </c>
@@ -15442,7 +15448,7 @@
         <v>325</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="19.5">
       <c r="A86" s="3" t="s">
         <v>1134</v>
       </c>
@@ -15465,7 +15471,7 @@
         <v>650</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
       <c r="A87" s="3" t="s">
         <v>1136</v>
       </c>
@@ -15488,7 +15494,7 @@
         <v>580</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="3" t="s">
         <v>1136</v>
       </c>
@@ -15511,7 +15517,7 @@
         <v>293.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
       <c r="A89" s="3" t="s">
         <v>1138</v>
       </c>
@@ -15534,7 +15540,7 @@
         <v>480</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
       <c r="A90" s="3" t="s">
         <v>1138</v>
       </c>
@@ -15580,7 +15586,7 @@
         <v>650</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
       <c r="A92" s="3" t="s">
         <v>1142</v>
       </c>
@@ -15603,7 +15609,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">
       <c r="A93" s="3" t="s">
         <v>1142</v>
       </c>
@@ -15626,7 +15632,7 @@
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="19.5">
       <c r="A94" s="3" t="s">
         <v>1142</v>
       </c>
@@ -16678,7 +16684,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
@@ -16701,7 +16707,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -19873,7 +19879,7 @@
         <v>158</v>
       </c>
       <c r="G4" s="4">
-        <v>126</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -19896,7 +19902,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="4">
-        <v>24</v>
+        <v>31.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -21874,7 +21880,7 @@
         <v>158</v>
       </c>
       <c r="G91" s="4">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
@@ -21897,7 +21903,7 @@
         <v>158</v>
       </c>
       <c r="G92" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3470,7 +3470,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3488,12 +3488,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3545,7 +3539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3572,12 +3566,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -5747,7 +5735,7 @@
         <v>158</v>
       </c>
       <c r="G21" s="4">
-        <v>95</v>
+        <v>122.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
@@ -5770,7 +5758,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="4">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
@@ -6023,7 +6011,7 @@
         <v>158</v>
       </c>
       <c r="G33" s="4">
-        <v>312.5</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -6046,7 +6034,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>66.5</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
@@ -15570,10 +15558,10 @@
       <c r="B91" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="4">
         <v>4540</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91" s="4">
         <v>10</v>
       </c>
       <c r="E91" s="3" t="s">
@@ -15582,7 +15570,7 @@
       <c r="F91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G91" s="11">
+      <c r="G91" s="5">
         <v>650</v>
       </c>
     </row>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -12169,7 +12169,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="4">
-        <v>48</v>
+        <v>52.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="19.5">
@@ -12192,7 +12192,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="4">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="19.5">
@@ -12238,7 +12238,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="4">
-        <v>48</v>
+        <v>52.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="19.5">
@@ -12261,7 +12261,7 @@
         <v>10</v>
       </c>
       <c r="G92" s="4">
-        <v>48</v>
+        <v>52.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="16"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -11781,7 +11781,7 @@
         <v>166</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="3" t="s">
         <v>137</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="3" t="s">
         <v>139</v>
       </c>
@@ -11827,7 +11827,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="3" t="s">
         <v>141</v>
       </c>
@@ -11850,7 +11850,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="3" t="s">
         <v>143</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="3" t="s">
         <v>146</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="3" t="s">
         <v>150</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="3" t="s">
         <v>152</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>372</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="3" t="s">
         <v>152</v>
       </c>
@@ -16879,7 +16879,7 @@
         <v>158</v>
       </c>
       <c r="G25" s="4">
-        <v>300</v>
+        <v>375</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
@@ -16902,7 +16902,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4201,7 +4201,7 @@
         <v>158</v>
       </c>
       <c r="G14" s="4">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -4316,7 +4316,7 @@
         <v>158</v>
       </c>
       <c r="G19" s="4">
-        <v>312.5</v>
+        <v>275</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -4339,7 +4339,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="4">
-        <v>66.5</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -16928,7 +16928,7 @@
         <v>660</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
         <v>962</v>
       </c>
@@ -21454,7 +21454,7 @@
         <v>158</v>
       </c>
       <c r="G73" s="4">
-        <v>300</v>
+        <v>262.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
@@ -21477,7 +21477,7 @@
         <v>10</v>
       </c>
       <c r="G74" s="4">
-        <v>62</v>
+        <v>55.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
@@ -21500,7 +21500,7 @@
         <v>158</v>
       </c>
       <c r="G75" s="4">
-        <v>180</v>
+        <v>162.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
@@ -21523,7 +21523,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="4">
-        <v>38</v>
+        <v>35.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1142">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2178,31 +2178,25 @@
     <t>farofa-flocada-torresmo</t>
   </si>
   <si>
-    <t>FAROFA FLOCADA TORRESMO</t>
+    <t>FAROFA SABOR PICANHA C/ALHO</t>
   </si>
   <si>
     <t>farofa-flocada-gourmet</t>
   </si>
   <si>
-    <t>FAROFA FLOCADA GOURMET</t>
+    <t>FAROFA SABOR TORRESMO</t>
+  </si>
+  <si>
+    <t>farofa-com-pimenta</t>
+  </si>
+  <si>
+    <t>FAROFA COM PIMENTA</t>
   </si>
   <si>
     <t>farofa-fina-tradicional</t>
   </si>
   <si>
-    <t>FAROFA FINA TRADICIONAL</t>
-  </si>
-  <si>
-    <t>farofa-fina-c-pimenta</t>
-  </si>
-  <si>
-    <t>FAROFA FINA C/ PIMENTA</t>
-  </si>
-  <si>
-    <t>farofa-com-pimenta</t>
-  </si>
-  <si>
-    <t>FAROFA COM PIMENTA</t>
+    <t>FAROFA TRADICIONAL</t>
   </si>
   <si>
     <t>granola-c-castanha-martigran</t>
@@ -5697,7 +5691,7 @@
         <v>11</v>
       </c>
       <c r="G19" s="4">
-        <v>202.5</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5720,7 +5714,7 @@
         <v>28</v>
       </c>
       <c r="G20" s="4">
-        <v>405</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6076,7 +6070,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -7005,7 +6999,7 @@
         <v>11</v>
       </c>
       <c r="G40" s="4">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7028,7 +7022,7 @@
         <v>11</v>
       </c>
       <c r="G41" s="4">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7039,7 +7033,7 @@
         <v>720</v>
       </c>
       <c r="C42" s="4">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="D42" s="4">
         <v>3</v>
@@ -7051,7 +7045,7 @@
         <v>11</v>
       </c>
       <c r="G42" s="4">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7062,7 +7056,7 @@
         <v>722</v>
       </c>
       <c r="C43" s="4">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="D43" s="4">
         <v>3</v>
@@ -7074,79 +7068,79 @@
         <v>11</v>
       </c>
       <c r="G43" s="4">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>723</v>
+        <v>425</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>724</v>
+        <v>426</v>
       </c>
       <c r="C44" s="4">
-        <v>2657</v>
+        <v>4640</v>
       </c>
       <c r="D44" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G44" s="4">
-        <v>65</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C45" s="4">
-        <v>2658</v>
+        <v>3537</v>
       </c>
       <c r="D45" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G45" s="4">
-        <v>65</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>425</v>
+        <v>725</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>426</v>
+        <v>726</v>
       </c>
       <c r="C46" s="4">
-        <v>4640</v>
+        <v>2732</v>
       </c>
       <c r="D46" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G46" s="4">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="47" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>725</v>
       </c>
@@ -7154,22 +7148,22 @@
         <v>726</v>
       </c>
       <c r="C47" s="4">
-        <v>3537</v>
+        <v>2733</v>
       </c>
       <c r="D47" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G47" s="4">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>727</v>
       </c>
@@ -7177,7 +7171,7 @@
         <v>728</v>
       </c>
       <c r="C48" s="4">
-        <v>2732</v>
+        <v>2584</v>
       </c>
       <c r="D48" s="4">
         <v>10</v>
@@ -7189,7 +7183,7 @@
         <v>28</v>
       </c>
       <c r="G48" s="4">
-        <v>189</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7200,7 +7194,7 @@
         <v>728</v>
       </c>
       <c r="C49" s="4">
-        <v>2733</v>
+        <v>2677</v>
       </c>
       <c r="D49" s="4">
         <v>5</v>
@@ -7212,7 +7206,7 @@
         <v>11</v>
       </c>
       <c r="G49" s="4">
-        <v>96.5</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7223,7 +7217,7 @@
         <v>730</v>
       </c>
       <c r="C50" s="4">
-        <v>2584</v>
+        <v>2495</v>
       </c>
       <c r="D50" s="4">
         <v>10</v>
@@ -7235,7 +7229,7 @@
         <v>28</v>
       </c>
       <c r="G50" s="4">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7246,7 +7240,7 @@
         <v>730</v>
       </c>
       <c r="C51" s="4">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="D51" s="4">
         <v>5</v>
@@ -7258,7 +7252,7 @@
         <v>11</v>
       </c>
       <c r="G51" s="4">
-        <v>113.5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7269,30 +7263,30 @@
         <v>732</v>
       </c>
       <c r="C52" s="4">
-        <v>2495</v>
+        <v>4498</v>
       </c>
       <c r="D52" s="4">
         <v>10</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>28</v>
+        <v>272</v>
       </c>
       <c r="G52" s="4">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C53" s="4">
-        <v>2678</v>
+        <v>4253</v>
       </c>
       <c r="D53" s="4">
         <v>5</v>
@@ -7301,7 +7295,7 @@
         <v>9</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>11</v>
+        <v>272</v>
       </c>
       <c r="G53" s="4">
         <v>112</v>
@@ -7315,59 +7309,59 @@
         <v>734</v>
       </c>
       <c r="C54" s="4">
-        <v>4498</v>
+        <v>4500</v>
       </c>
       <c r="D54" s="4">
         <v>10</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>272</v>
       </c>
       <c r="G54" s="4">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C55" s="4">
-        <v>4253</v>
+        <v>4249</v>
       </c>
       <c r="D55" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>272</v>
       </c>
       <c r="G55" s="4">
-        <v>112</v>
+        <v>230</v>
       </c>
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C56" s="4">
-        <v>4500</v>
+        <v>3724</v>
       </c>
       <c r="D56" s="4">
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>272</v>
@@ -7384,30 +7378,30 @@
         <v>736</v>
       </c>
       <c r="C57" s="4">
-        <v>4249</v>
+        <v>3736</v>
       </c>
       <c r="D57" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="G57" s="4">
-        <v>230</v>
+        <v>162</v>
       </c>
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C58" s="4">
-        <v>3724</v>
+        <v>4499</v>
       </c>
       <c r="D58" s="4">
         <v>10</v>
@@ -7419,18 +7413,18 @@
         <v>272</v>
       </c>
       <c r="G58" s="4">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C59" s="4">
-        <v>3736</v>
+        <v>3536</v>
       </c>
       <c r="D59" s="4">
         <v>12</v>
@@ -7447,25 +7441,25 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C60" s="4">
-        <v>4499</v>
+        <v>2494</v>
       </c>
       <c r="D60" s="4">
         <v>10</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="G60" s="4">
-        <v>240</v>
+        <v>188.5</v>
       </c>
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7476,19 +7470,19 @@
         <v>742</v>
       </c>
       <c r="C61" s="4">
-        <v>3536</v>
+        <v>2679</v>
       </c>
       <c r="D61" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G61" s="4">
-        <v>162</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7499,88 +7493,88 @@
         <v>744</v>
       </c>
       <c r="C62" s="4">
-        <v>2494</v>
+        <v>4497</v>
       </c>
       <c r="D62" s="4">
         <v>10</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>28</v>
+        <v>272</v>
       </c>
       <c r="G62" s="4">
-        <v>188.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C63" s="4">
-        <v>2679</v>
+        <v>2493</v>
       </c>
       <c r="D63" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G63" s="4">
-        <v>96</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C64" s="4">
-        <v>4497</v>
+        <v>3535</v>
       </c>
       <c r="D64" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>269</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="G64" s="4">
-        <v>240</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C65" s="4">
-        <v>2493</v>
+        <v>2498</v>
       </c>
       <c r="D65" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G65" s="4">
-        <v>180</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7591,30 +7585,30 @@
         <v>750</v>
       </c>
       <c r="C66" s="4">
-        <v>3535</v>
+        <v>2806</v>
       </c>
       <c r="D66" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>28</v>
+        <v>272</v>
       </c>
       <c r="G66" s="4">
-        <v>162</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C67" s="4">
-        <v>2498</v>
+        <v>2807</v>
       </c>
       <c r="D67" s="4">
         <v>5</v>
@@ -7623,10 +7617,10 @@
         <v>9</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G67" s="4">
-        <v>92</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7637,19 +7631,19 @@
         <v>752</v>
       </c>
       <c r="C68" s="4">
-        <v>2806</v>
+        <v>4556</v>
       </c>
       <c r="D68" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>272</v>
+        <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>472.5</v>
+        <v>900</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7660,7 +7654,7 @@
         <v>752</v>
       </c>
       <c r="C69" s="4">
-        <v>2807</v>
+        <v>4557</v>
       </c>
       <c r="D69" s="4">
         <v>5</v>
@@ -7669,10 +7663,10 @@
         <v>9</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G69" s="4">
-        <v>159.5</v>
+        <v>182</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7683,19 +7677,19 @@
         <v>754</v>
       </c>
       <c r="C70" s="4">
-        <v>4556</v>
+        <v>4018</v>
       </c>
       <c r="D70" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G70" s="4">
-        <v>900</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7706,7 +7700,7 @@
         <v>754</v>
       </c>
       <c r="C71" s="4">
-        <v>4557</v>
+        <v>2652</v>
       </c>
       <c r="D71" s="4">
         <v>5</v>
@@ -7718,7 +7712,7 @@
         <v>11</v>
       </c>
       <c r="G71" s="4">
-        <v>182</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7729,7 +7723,7 @@
         <v>756</v>
       </c>
       <c r="C72" s="4">
-        <v>4018</v>
+        <v>4049</v>
       </c>
       <c r="D72" s="4">
         <v>10</v>
@@ -7741,7 +7735,7 @@
         <v>11</v>
       </c>
       <c r="G72" s="4">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7752,7 +7746,7 @@
         <v>756</v>
       </c>
       <c r="C73" s="4">
-        <v>2652</v>
+        <v>3737</v>
       </c>
       <c r="D73" s="4">
         <v>5</v>
@@ -7764,7 +7758,7 @@
         <v>11</v>
       </c>
       <c r="G73" s="4">
-        <v>103.5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7775,10 +7769,10 @@
         <v>758</v>
       </c>
       <c r="C74" s="4">
-        <v>4049</v>
+        <v>4301</v>
       </c>
       <c r="D74" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>9</v>
@@ -7787,18 +7781,18 @@
         <v>11</v>
       </c>
       <c r="G74" s="4">
-        <v>180</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C75" s="4">
-        <v>3737</v>
+        <v>4334</v>
       </c>
       <c r="D75" s="4">
         <v>5</v>
@@ -7810,30 +7804,30 @@
         <v>11</v>
       </c>
       <c r="G75" s="4">
-        <v>93</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C76" s="4">
-        <v>4301</v>
+        <v>195</v>
       </c>
       <c r="D76" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G76" s="4">
-        <v>235</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7844,7 +7838,7 @@
         <v>762</v>
       </c>
       <c r="C77" s="4">
-        <v>4334</v>
+        <v>54</v>
       </c>
       <c r="D77" s="4">
         <v>5</v>
@@ -7856,7 +7850,7 @@
         <v>11</v>
       </c>
       <c r="G77" s="4">
-        <v>376.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7867,7 +7861,7 @@
         <v>764</v>
       </c>
       <c r="C78" s="4">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="D78" s="4">
         <v>25</v>
@@ -7879,7 +7873,7 @@
         <v>10</v>
       </c>
       <c r="G78" s="4">
-        <v>300</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7890,7 +7884,7 @@
         <v>764</v>
       </c>
       <c r="C79" s="4">
-        <v>54</v>
+        <v>2483</v>
       </c>
       <c r="D79" s="4">
         <v>5</v>
@@ -7902,7 +7896,7 @@
         <v>11</v>
       </c>
       <c r="G79" s="4">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7913,10 +7907,10 @@
         <v>766</v>
       </c>
       <c r="C80" s="4">
-        <v>63</v>
+        <v>2974</v>
       </c>
       <c r="D80" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>9</v>
@@ -7925,7 +7919,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="4">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7936,7 +7930,7 @@
         <v>766</v>
       </c>
       <c r="C81" s="4">
-        <v>2483</v>
+        <v>2831</v>
       </c>
       <c r="D81" s="4">
         <v>5</v>
@@ -7948,7 +7942,7 @@
         <v>11</v>
       </c>
       <c r="G81" s="4">
-        <v>53</v>
+        <v>127</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7959,33 +7953,33 @@
         <v>768</v>
       </c>
       <c r="C82" s="4">
-        <v>2974</v>
+        <v>4137</v>
       </c>
       <c r="D82" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G82" s="4">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C83" s="4">
-        <v>2831</v>
+        <v>4380</v>
       </c>
       <c r="D83" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>9</v>
@@ -7994,21 +7988,21 @@
         <v>11</v>
       </c>
       <c r="G83" s="4">
-        <v>127</v>
+        <v>270</v>
       </c>
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C84" s="4">
-        <v>4137</v>
+        <v>4566</v>
       </c>
       <c r="D84" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>9</v>
@@ -8017,21 +8011,21 @@
         <v>11</v>
       </c>
       <c r="G84" s="4">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C85" s="4">
-        <v>4380</v>
+        <v>4567</v>
       </c>
       <c r="D85" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>9</v>
@@ -8040,21 +8034,21 @@
         <v>11</v>
       </c>
       <c r="G85" s="4">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C86" s="4">
-        <v>4566</v>
+        <v>4204</v>
       </c>
       <c r="D86" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>9</v>
@@ -8063,7 +8057,7 @@
         <v>11</v>
       </c>
       <c r="G86" s="4">
-        <v>240</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8074,33 +8068,33 @@
         <v>776</v>
       </c>
       <c r="C87" s="4">
-        <v>4567</v>
+        <v>4205</v>
       </c>
       <c r="D87" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4">
-        <v>240</v>
+        <v>310</v>
       </c>
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C88" s="4">
-        <v>4204</v>
+        <v>4225</v>
       </c>
       <c r="D88" s="4">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>9</v>
@@ -8109,7 +8103,7 @@
         <v>11</v>
       </c>
       <c r="G88" s="4">
-        <v>127</v>
+        <v>775</v>
       </c>
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8120,7 +8114,7 @@
         <v>778</v>
       </c>
       <c r="C89" s="4">
-        <v>4205</v>
+        <v>4378</v>
       </c>
       <c r="D89" s="4">
         <v>10</v>
@@ -8132,7 +8126,7 @@
         <v>10</v>
       </c>
       <c r="G89" s="4">
-        <v>310</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8143,19 +8137,19 @@
         <v>778</v>
       </c>
       <c r="C90" s="4">
-        <v>4225</v>
+        <v>4379</v>
       </c>
       <c r="D90" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G90" s="4">
-        <v>775</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8166,19 +8160,19 @@
         <v>780</v>
       </c>
       <c r="C91" s="4">
-        <v>4378</v>
+        <v>3524</v>
       </c>
       <c r="D91" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>10</v>
+        <v>781</v>
       </c>
       <c r="G91" s="4">
-        <v>430</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8189,134 +8183,134 @@
         <v>780</v>
       </c>
       <c r="C92" s="4">
-        <v>4379</v>
+        <v>3523</v>
       </c>
       <c r="D92" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>10</v>
+        <v>781</v>
       </c>
       <c r="G92" s="4">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C93" s="4">
-        <v>3524</v>
+        <v>3521</v>
       </c>
       <c r="D93" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>9</v>
+        <v>784</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>783</v>
+        <v>28</v>
       </c>
       <c r="G93" s="4">
-        <v>350</v>
+        <v>158</v>
       </c>
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C94" s="4">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="D94" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>9</v>
+        <v>424</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>783</v>
+        <v>28</v>
       </c>
       <c r="G94" s="4">
-        <v>72</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C95" s="4">
-        <v>3521</v>
+        <v>64</v>
       </c>
       <c r="D95" s="4">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>786</v>
+        <v>269</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G95" s="4">
-        <v>158</v>
+        <v>132</v>
       </c>
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C96" s="4">
-        <v>3522</v>
+        <v>90</v>
       </c>
       <c r="D96" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>424</v>
+        <v>269</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G96" s="4">
-        <v>216.5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C97" s="4">
-        <v>64</v>
+        <v>3637</v>
       </c>
       <c r="D97" s="4">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G97" s="4">
-        <v>132</v>
+        <v>375</v>
       </c>
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8327,42 +8321,42 @@
         <v>790</v>
       </c>
       <c r="C98" s="4">
-        <v>90</v>
+        <v>2805</v>
       </c>
       <c r="D98" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G98" s="4">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C99" s="4">
-        <v>3637</v>
+        <v>2427</v>
       </c>
       <c r="D99" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G99" s="4">
-        <v>375</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8373,7 +8367,7 @@
         <v>792</v>
       </c>
       <c r="C100" s="4">
-        <v>2805</v>
+        <v>3437</v>
       </c>
       <c r="D100" s="4">
         <v>10</v>
@@ -8385,7 +8379,7 @@
         <v>10</v>
       </c>
       <c r="G100" s="4">
-        <v>150</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8396,10 +8390,10 @@
         <v>792</v>
       </c>
       <c r="C101" s="4">
-        <v>2427</v>
+        <v>3396</v>
       </c>
       <c r="D101" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>9</v>
@@ -8408,7 +8402,7 @@
         <v>11</v>
       </c>
       <c r="G101" s="4">
-        <v>46</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8419,134 +8413,134 @@
         <v>794</v>
       </c>
       <c r="C102" s="4">
-        <v>3437</v>
+        <v>3395</v>
       </c>
       <c r="D102" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>9</v>
+        <v>795</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G102" s="4">
-        <v>350</v>
+        <v>54</v>
       </c>
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C103" s="4">
-        <v>3396</v>
+        <v>3490</v>
       </c>
       <c r="D103" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>9</v>
+        <v>795</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G103" s="4">
-        <v>178.5</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C104" s="4">
-        <v>3395</v>
+        <v>458</v>
       </c>
       <c r="D104" s="4">
         <v>12</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G104" s="4">
-        <v>54</v>
+        <v>269.5</v>
       </c>
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C105" s="4">
-        <v>3490</v>
+        <v>2641</v>
       </c>
       <c r="D105" s="4">
         <v>12</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G105" s="4">
-        <v>169</v>
+        <v>222</v>
       </c>
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C106" s="4">
-        <v>458</v>
+        <v>4293</v>
       </c>
       <c r="D106" s="4">
         <v>12</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G106" s="4">
-        <v>269.5</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C107" s="4">
-        <v>2641</v>
+        <v>2396</v>
       </c>
       <c r="D107" s="4">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>802</v>
+        <v>9</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G107" s="4">
-        <v>222</v>
+        <v>675</v>
       </c>
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8557,19 +8551,19 @@
         <v>806</v>
       </c>
       <c r="C108" s="4">
-        <v>4293</v>
+        <v>2426</v>
       </c>
       <c r="D108" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>802</v>
+        <v>9</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G108" s="4">
-        <v>210</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8580,33 +8574,33 @@
         <v>808</v>
       </c>
       <c r="C109" s="4">
-        <v>2396</v>
+        <v>4335</v>
       </c>
       <c r="D109" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G109" s="4">
-        <v>675</v>
+        <v>510</v>
       </c>
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C110" s="4">
-        <v>2426</v>
+        <v>4477</v>
       </c>
       <c r="D110" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>9</v>
@@ -8615,18 +8609,18 @@
         <v>11</v>
       </c>
       <c r="G110" s="4">
-        <v>137</v>
+        <v>255</v>
       </c>
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C111" s="4">
-        <v>4335</v>
+        <v>4479</v>
       </c>
       <c r="D111" s="4">
         <v>3</v>
@@ -8638,18 +8632,18 @@
         <v>11</v>
       </c>
       <c r="G111" s="4">
-        <v>510</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C112" s="4">
-        <v>4477</v>
+        <v>4478</v>
       </c>
       <c r="D112" s="4">
         <v>3</v>
@@ -8666,25 +8660,25 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C113" s="4">
-        <v>4479</v>
+        <v>2646</v>
       </c>
       <c r="D113" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>9</v>
+        <v>817</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>11</v>
+        <v>272</v>
       </c>
       <c r="G113" s="4">
-        <v>255</v>
+        <v>53</v>
       </c>
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8695,33 +8689,33 @@
         <v>816</v>
       </c>
       <c r="C114" s="4">
-        <v>4478</v>
+        <v>2645</v>
       </c>
       <c r="D114" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>9</v>
+        <v>818</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>11</v>
+        <v>272</v>
       </c>
       <c r="G114" s="4">
-        <v>255</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C115" s="4">
-        <v>2646</v>
+        <v>2638</v>
       </c>
       <c r="D115" s="4">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>819</v>
@@ -8730,121 +8724,75 @@
         <v>272</v>
       </c>
       <c r="G115" s="4">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C116" s="4">
-        <v>2645</v>
+        <v>4294</v>
       </c>
       <c r="D116" s="4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>272</v>
       </c>
       <c r="G116" s="4">
-        <v>81.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="C117" s="4">
-        <v>2638</v>
+        <v>4314</v>
       </c>
       <c r="D117" s="4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>821</v>
+        <v>424</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="G117" s="4">
-        <v>70</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C118" s="4">
-        <v>4294</v>
+        <v>4315</v>
       </c>
       <c r="D118" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="G118" s="4">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="C119" s="4">
-        <v>4314</v>
-      </c>
-      <c r="D119" s="4">
-        <v>15</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G119" s="4">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="120" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="C120" s="4">
-        <v>4315</v>
-      </c>
-      <c r="D120" s="4">
-        <v>15</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G120" s="4">
         <v>450</v>
       </c>
     </row>
@@ -8893,10 +8841,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C2" s="4">
         <v>3402</v>
@@ -8905,7 +8853,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>272</v>
@@ -8916,10 +8864,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C3" s="4">
         <v>3401</v>
@@ -8928,7 +8876,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>272</v>
@@ -8939,10 +8887,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C4" s="4">
         <v>3403</v>
@@ -8951,7 +8899,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>272</v>
@@ -8962,10 +8910,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C5" s="4">
         <v>4032</v>
@@ -8974,7 +8922,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>272</v>
@@ -8985,10 +8933,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C6" s="4">
         <v>4460</v>
@@ -8997,7 +8945,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>272</v>
@@ -9008,10 +8956,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C7" s="4">
         <v>4260</v>
@@ -9020,7 +8968,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>272</v>
@@ -9031,10 +8979,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C8" s="4">
         <v>2551</v>
@@ -9043,7 +8991,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>272</v>
@@ -9054,10 +9002,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C9" s="4">
         <v>2550</v>
@@ -9066,7 +9014,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>272</v>
@@ -9077,10 +9025,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C10" s="4">
         <v>4383</v>
@@ -9089,7 +9037,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>272</v>
@@ -9143,10 +9091,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C2" s="4">
         <v>3644</v>
@@ -9155,7 +9103,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>272</v>
@@ -9166,10 +9114,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C3" s="4">
         <v>3644</v>
@@ -9178,7 +9126,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>272</v>
@@ -9189,10 +9137,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C4" s="4">
         <v>3641</v>
@@ -9201,7 +9149,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>272</v>
@@ -9212,10 +9160,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C5" s="4">
         <v>3645</v>
@@ -9224,7 +9172,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>272</v>
@@ -9235,10 +9183,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C6" s="4">
         <v>3852</v>
@@ -9247,7 +9195,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -9258,10 +9206,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C7" s="4">
         <v>3647</v>
@@ -9270,7 +9218,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>272</v>
@@ -9281,10 +9229,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C8" s="4">
         <v>3648</v>
@@ -9293,7 +9241,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>272</v>
@@ -9347,10 +9295,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C2" s="4">
         <v>3056</v>
@@ -9370,10 +9318,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C3" s="4">
         <v>3083</v>
@@ -9393,10 +9341,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C4" s="4">
         <v>2264</v>
@@ -9416,10 +9364,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C5" s="4">
         <v>2355</v>
@@ -9439,10 +9387,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C6" s="4">
         <v>573</v>
@@ -9462,10 +9410,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C7" s="4">
         <v>572</v>
@@ -9485,10 +9433,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C8" s="4">
         <v>4411</v>
@@ -9508,10 +9456,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C9" s="4">
         <v>4410</v>
@@ -9574,10 +9522,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C2" s="4">
         <v>4044</v>
@@ -9586,7 +9534,7 @@
         <v>500</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -9597,10 +9545,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C3" s="4">
         <v>4672</v>
@@ -9609,7 +9557,7 @@
         <v>500</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -9620,10 +9568,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C4" s="4">
         <v>4043</v>
@@ -9643,10 +9591,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C5" s="4">
         <v>3531</v>
@@ -9666,10 +9614,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C6" s="4">
         <v>3974</v>
@@ -9689,10 +9637,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C7" s="4">
         <v>3530</v>
@@ -9712,10 +9660,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C8" s="4">
         <v>4282</v>
@@ -9735,10 +9683,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C9" s="4">
         <v>3870</v>
@@ -9747,7 +9695,7 @@
         <v>500</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -9758,10 +9706,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C10" s="4">
         <v>3701</v>
@@ -9770,7 +9718,7 @@
         <v>500</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -9781,10 +9729,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C11" s="4">
         <v>3800</v>
@@ -9793,7 +9741,7 @@
         <v>500</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -9804,10 +9752,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C12" s="4">
         <v>3725</v>
@@ -9816,7 +9764,7 @@
         <v>500</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -9827,10 +9775,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C13" s="4">
         <v>3871</v>
@@ -9839,7 +9787,7 @@
         <v>500</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -9850,10 +9798,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C14" s="4">
         <v>2825</v>
@@ -9873,10 +9821,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C15" s="4">
         <v>2828</v>
@@ -9896,10 +9844,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C16" s="4">
         <v>2826</v>
@@ -9919,10 +9867,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C17" s="4">
         <v>3058</v>
@@ -9942,10 +9890,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C18" s="4">
         <v>3059</v>
@@ -9965,10 +9913,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C19" s="4">
         <v>2829</v>
@@ -9988,10 +9936,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C20" s="4">
         <v>4126</v>
@@ -10011,10 +9959,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C21" s="4">
         <v>2827</v>
@@ -10034,10 +9982,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C22" s="4">
         <v>3801</v>
@@ -10046,7 +9994,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -10057,10 +10005,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C23" s="4">
         <v>3833</v>
@@ -10069,7 +10017,7 @@
         <v>500</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -10080,10 +10028,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C24" s="4">
         <v>3897</v>
@@ -10103,10 +10051,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C25" s="4">
         <v>3764</v>
@@ -10215,10 +10163,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C4" s="4">
         <v>3443</v>
@@ -10238,10 +10186,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C5" s="4">
         <v>3019</v>
@@ -10261,10 +10209,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C6" s="4">
         <v>4489</v>
@@ -10284,10 +10232,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C7" s="4">
         <v>4490</v>
@@ -10307,10 +10255,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C8" s="4">
         <v>3476</v>
@@ -10330,10 +10278,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C9" s="4">
         <v>3477</v>
@@ -10353,10 +10301,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C10" s="4">
         <v>4344</v>
@@ -10422,10 +10370,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C13" s="4">
         <v>3719</v>
@@ -10445,10 +10393,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C14" s="4">
         <v>3720</v>
@@ -10468,10 +10416,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C15" s="4">
         <v>3765</v>
@@ -10491,10 +10439,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C16" s="4">
         <v>3766</v>
@@ -10514,10 +10462,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C17" s="4">
         <v>3126</v>
@@ -10537,10 +10485,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C18" s="4">
         <v>3127</v>
@@ -10560,10 +10508,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C19" s="4">
         <v>3435</v>
@@ -10583,10 +10531,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C20" s="4">
         <v>3436</v>
@@ -10606,10 +10554,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C21" s="4">
         <v>3128</v>
@@ -10629,10 +10577,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C22" s="4">
         <v>3129</v>
@@ -10652,10 +10600,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C23" s="4">
         <v>4158</v>
@@ -10675,10 +10623,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C24" s="4">
         <v>4159</v>
@@ -10698,10 +10646,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C25" s="4">
         <v>4561</v>
@@ -10721,10 +10669,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C26" s="4">
         <v>4562</v>
@@ -10836,10 +10784,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C31" s="4">
         <v>4346</v>
@@ -10859,10 +10807,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C32" s="4">
         <v>4345</v>
@@ -10882,10 +10830,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C33" s="4">
         <v>4347</v>
@@ -10905,10 +10853,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C34" s="4">
         <v>4446</v>
@@ -10928,10 +10876,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C35" s="4">
         <v>4476</v>
@@ -10943,7 +10891,7 @@
         <v>9</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G35" s="4">
         <v>33.5</v>
@@ -10951,10 +10899,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C36" s="4">
         <v>4348</v>
@@ -10974,10 +10922,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C37" s="4">
         <v>4456</v>
@@ -10997,10 +10945,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C38" s="4">
         <v>4051</v>
@@ -11020,10 +10968,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C39" s="4">
         <v>4408</v>
@@ -11043,10 +10991,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C40" s="4">
         <v>4341</v>
@@ -11066,10 +11014,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C41" s="4">
         <v>4265</v>
@@ -11089,10 +11037,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C42" s="4">
         <v>4266</v>
@@ -11112,10 +11060,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C43" s="4">
         <v>4269</v>
@@ -11135,10 +11083,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C44" s="4">
         <v>4273</v>
@@ -11158,10 +11106,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C45" s="4">
         <v>4405</v>
@@ -11181,10 +11129,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C46" s="4">
         <v>4406</v>
@@ -11204,10 +11152,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C47" s="4">
         <v>4267</v>
@@ -11227,10 +11175,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C48" s="4">
         <v>4271</v>
@@ -11250,10 +11198,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C49" s="4">
         <v>4276</v>
@@ -11273,10 +11221,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C50" s="4">
         <v>4342</v>
@@ -11296,10 +11244,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C51" s="4">
         <v>2505</v>
@@ -11319,10 +11267,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C52" s="4">
         <v>4398</v>
@@ -11342,10 +11290,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C53" s="4">
         <v>4270</v>
@@ -11365,10 +11313,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C54" s="4">
         <v>4275</v>
@@ -11388,10 +11336,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C55" s="4">
         <v>4274</v>
@@ -11411,10 +11359,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C56" s="4">
         <v>4399</v>
@@ -11434,10 +11382,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C57" s="4">
         <v>4404</v>
@@ -11457,10 +11405,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C58" s="4">
         <v>4262</v>
@@ -11480,10 +11428,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C59" s="4">
         <v>4263</v>
@@ -11503,10 +11451,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C60" s="4">
         <v>4264</v>
@@ -11526,10 +11474,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C61" s="4">
         <v>4407</v>
@@ -11549,10 +11497,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C62" s="4">
         <v>4397</v>
@@ -11572,10 +11520,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C63" s="4">
         <v>4343</v>
@@ -11595,10 +11543,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C64" s="4">
         <v>4268</v>
@@ -11618,10 +11566,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C65" s="4">
         <v>2833</v>
@@ -11641,10 +11589,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C66" s="4">
         <v>3125</v>
@@ -11664,10 +11612,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C67" s="4">
         <v>3752</v>
@@ -11687,10 +11635,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C68" s="4">
         <v>3753</v>
@@ -11710,10 +11658,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C69" s="4">
         <v>2511</v>
@@ -11733,10 +11681,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C70" s="4">
         <v>4311</v>
@@ -11756,10 +11704,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C71" s="4">
         <v>4046</v>
@@ -11779,10 +11727,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C72" s="4">
         <v>4047</v>
@@ -11802,10 +11750,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C73" s="4">
         <v>4312</v>
@@ -11825,10 +11773,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C74" s="4">
         <v>4310</v>
@@ -11848,10 +11796,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C75" s="4">
         <v>4074</v>
@@ -11860,7 +11808,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -11871,10 +11819,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C76" s="4">
         <v>4076</v>
@@ -11883,10 +11831,10 @@
         <v>1</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G76" s="4">
         <v>32.5</v>
@@ -11894,10 +11842,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C77" s="4">
         <v>4133</v>
@@ -11909,7 +11857,7 @@
         <v>424</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G77" s="4">
         <v>72</v>
@@ -11917,10 +11865,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C78" s="4">
         <v>3068</v>
@@ -11940,10 +11888,10 @@
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C79" s="4">
         <v>3087</v>
@@ -11963,10 +11911,10 @@
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C80" s="4">
         <v>4560</v>
@@ -11986,10 +11934,10 @@
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C81" s="4">
         <v>4531</v>
@@ -12009,10 +11957,10 @@
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C82" s="4">
         <v>4532</v>
@@ -12032,10 +11980,10 @@
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C83" s="4">
         <v>4559</v>
@@ -12055,10 +12003,10 @@
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C84" s="4">
         <v>4493</v>
@@ -12078,10 +12026,10 @@
     </row>
     <row r="85" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C85" s="4">
         <v>4102</v>
@@ -12090,7 +12038,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -12101,10 +12049,10 @@
     </row>
     <row r="86" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C86" s="4">
         <v>4103</v>
@@ -12113,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>272</v>
@@ -12124,10 +12072,10 @@
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C87" s="4">
         <v>4547</v>
@@ -12136,7 +12084,7 @@
         <v>10</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>272</v>
@@ -12147,10 +12095,10 @@
     </row>
     <row r="88" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C88" s="4">
         <v>4624</v>
@@ -12159,7 +12107,7 @@
         <v>21</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -12170,10 +12118,10 @@
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C89" s="4">
         <v>4627</v>
@@ -12182,7 +12130,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -12193,10 +12141,10 @@
     </row>
     <row r="90" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C90" s="4">
         <v>4628</v>
@@ -12205,7 +12153,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -12216,10 +12164,10 @@
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C91" s="4">
         <v>4625</v>
@@ -12228,7 +12176,7 @@
         <v>21</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -12239,10 +12187,10 @@
     </row>
     <row r="92" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C92" s="4">
         <v>4626</v>
@@ -12251,7 +12199,7 @@
         <v>21</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -12262,10 +12210,10 @@
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C93" s="4">
         <v>4699</v>
@@ -12274,7 +12222,7 @@
         <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>272</v>
@@ -12285,10 +12233,10 @@
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C94" s="4">
         <v>4643</v>
@@ -12297,10 +12245,10 @@
         <v>6</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G94" s="4">
         <v>97.5</v>
@@ -12308,10 +12256,10 @@
     </row>
     <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C95" s="4">
         <v>4687</v>
@@ -12320,10 +12268,10 @@
         <v>6</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G95" s="4">
         <v>64</v>
@@ -12331,10 +12279,10 @@
     </row>
     <row r="96" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C96" s="4">
         <v>4644</v>
@@ -12343,10 +12291,10 @@
         <v>6</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G96" s="4">
         <v>57</v>
@@ -12354,10 +12302,10 @@
     </row>
     <row r="97" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C97" s="4">
         <v>4104</v>
@@ -12366,7 +12314,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>272</v>
@@ -12377,10 +12325,10 @@
     </row>
     <row r="98" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C98" s="4">
         <v>4101</v>
@@ -12389,7 +12337,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>272</v>
@@ -12400,10 +12348,10 @@
     </row>
     <row r="99" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C99" s="4">
         <v>4105</v>
@@ -12412,7 +12360,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>272</v>
@@ -12423,10 +12371,10 @@
     </row>
     <row r="100" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C100" s="4">
         <v>3705</v>
@@ -12435,7 +12383,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>272</v>
@@ -12446,10 +12394,10 @@
     </row>
     <row r="101" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C101" s="4">
         <v>3823</v>
@@ -12458,7 +12406,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>28</v>
@@ -12469,10 +12417,10 @@
     </row>
     <row r="102" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C102" s="4">
         <v>4641</v>
@@ -12481,7 +12429,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -12492,10 +12440,10 @@
     </row>
     <row r="103" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>1075</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>1077</v>
       </c>
       <c r="C103" s="4">
         <v>4583</v>
@@ -12504,7 +12452,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>272</v>
@@ -12515,10 +12463,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C104" s="4">
         <v>4308</v>
@@ -12527,7 +12475,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -12538,10 +12486,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C105" s="4">
         <v>4309</v>
@@ -12550,10 +12498,10 @@
         <v>10</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G105" s="4">
         <v>68.5</v>
@@ -12561,10 +12509,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C106" s="4">
         <v>4635</v>
@@ -12576,7 +12524,7 @@
         <v>424</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G106" s="4">
         <v>177</v>
@@ -12584,10 +12532,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C107" s="4">
         <v>4412</v>
@@ -12599,7 +12547,7 @@
         <v>9</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G107" s="4">
         <v>75.5</v>
@@ -12607,10 +12555,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C108" s="4">
         <v>4413</v>
@@ -12630,10 +12578,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C109" s="4">
         <v>4414</v>
@@ -12653,10 +12601,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C110" s="4">
         <v>4415</v>
@@ -12676,10 +12624,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C111" s="4">
         <v>4416</v>
@@ -12699,10 +12647,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C112" s="4">
         <v>4475</v>
@@ -12711,7 +12659,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -12722,10 +12670,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C113" s="4">
         <v>4354</v>
@@ -12734,10 +12682,10 @@
         <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G113" s="4">
         <v>79.5</v>
@@ -12745,10 +12693,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C114" s="4">
         <v>4445</v>
@@ -12757,7 +12705,7 @@
         <v>12</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>28</v>
@@ -12768,10 +12716,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C115" s="4">
         <v>4353</v>
@@ -12780,7 +12728,7 @@
         <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>28</v>
@@ -12791,10 +12739,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C116" s="4">
         <v>4350</v>
@@ -12803,7 +12751,7 @@
         <v>12</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>28</v>
@@ -12814,10 +12762,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C117" s="4">
         <v>4352</v>
@@ -12826,7 +12774,7 @@
         <v>12</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>28</v>
@@ -12837,10 +12785,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C118" s="4">
         <v>4349</v>
@@ -12849,7 +12797,7 @@
         <v>12</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>28</v>
@@ -12860,10 +12808,10 @@
     </row>
     <row r="119" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C119" s="4">
         <v>4351</v>
@@ -12872,7 +12820,7 @@
         <v>12</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>28</v>
@@ -12883,10 +12831,10 @@
     </row>
     <row r="120" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C120" s="4">
         <v>4581</v>
@@ -12895,7 +12843,7 @@
         <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>28</v>
@@ -12906,10 +12854,10 @@
     </row>
     <row r="121" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C121" s="4">
         <v>4096</v>
@@ -12929,10 +12877,10 @@
     </row>
     <row r="122" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C122" s="4">
         <v>4582</v>
@@ -12941,7 +12889,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -12952,10 +12900,10 @@
     </row>
     <row r="123" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="C123" s="4">
         <v>4123</v>
@@ -12964,7 +12912,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -12975,10 +12923,10 @@
     </row>
     <row r="124" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="C124" s="4">
         <v>4306</v>
@@ -12987,10 +12935,10 @@
         <v>10</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G124" s="4">
         <v>81</v>
@@ -12998,10 +12946,10 @@
     </row>
     <row r="125" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="C125" s="4">
         <v>4307</v>
@@ -13010,10 +12958,10 @@
         <v>10</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G125" s="4">
         <v>81</v>
@@ -13021,10 +12969,10 @@
     </row>
     <row r="126" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C126" s="4">
         <v>2659</v>
@@ -13033,7 +12981,7 @@
         <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>272</v>
@@ -13044,10 +12992,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C127" s="4">
         <v>2621</v>
@@ -13056,7 +13004,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>272</v>
@@ -13067,10 +13015,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C128" s="4">
         <v>3656</v>
@@ -13079,7 +13027,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>272</v>
@@ -13133,10 +13081,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C2" s="4">
         <v>3459</v>
@@ -13145,7 +13093,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -13156,10 +13104,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C3" s="4">
         <v>3803</v>
@@ -13168,7 +13116,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -13179,10 +13127,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C4" s="4">
         <v>3425</v>
@@ -13191,10 +13139,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G4" s="4">
         <v>29</v>
@@ -13202,10 +13150,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C5" s="4">
         <v>3426</v>
@@ -13214,7 +13162,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>28</v>
@@ -13225,10 +13173,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C6" s="4">
         <v>3427</v>
@@ -13237,10 +13185,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G6" s="4">
         <v>62.5</v>
@@ -13248,10 +13196,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C7" s="4">
         <v>3428</v>
@@ -13260,7 +13208,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>28</v>
@@ -13271,10 +13219,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C8" s="4">
         <v>3429</v>
@@ -13283,10 +13231,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G8" s="4">
         <v>76.5</v>
@@ -13294,10 +13242,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C9" s="4">
         <v>3430</v>
@@ -13306,7 +13254,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>28</v>
@@ -13317,10 +13265,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C10" s="4">
         <v>3913</v>
@@ -13329,10 +13277,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G10" s="4">
         <v>68</v>
@@ -13340,10 +13288,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C11" s="4">
         <v>3872</v>
@@ -13352,7 +13300,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>28</v>
@@ -13363,10 +13311,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C12" s="4">
         <v>3422</v>
@@ -13375,10 +13323,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G12" s="4">
         <v>20</v>
@@ -13386,10 +13334,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C13" s="4">
         <v>3423</v>
@@ -13398,7 +13346,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>28</v>
@@ -13409,10 +13357,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C14" s="4">
         <v>3431</v>
@@ -13421,10 +13369,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G14" s="4">
         <v>115</v>
@@ -13432,10 +13380,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C15" s="4">
         <v>3432</v>
@@ -13444,7 +13392,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>28</v>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3758" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="1142">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -4253,7 +4253,7 @@
         <v>28</v>
       </c>
       <c r="G16" s="4">
-        <v>155</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5211,7 +5211,7 @@
         <v>28</v>
       </c>
       <c r="G24" s="4">
-        <v>340</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5234,7 +5234,7 @@
         <v>28</v>
       </c>
       <c r="G25" s="4">
-        <v>155</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -7643,7 +7643,7 @@
         <v>10</v>
       </c>
       <c r="G68" s="4">
-        <v>900</v>
+        <v>975</v>
       </c>
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7666,7 +7666,7 @@
         <v>11</v>
       </c>
       <c r="G69" s="4">
-        <v>182</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -13409,7 +13409,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -15468,7 +15468,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="90" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>135</v>
       </c>
@@ -15476,65 +15476,65 @@
         <v>136</v>
       </c>
       <c r="C90" s="4">
+        <v>4290</v>
+      </c>
+      <c r="D90" s="4">
+        <v>11</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="4">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C91" s="4">
         <v>2385</v>
       </c>
-      <c r="D90" s="4">
-        <v>5</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="4">
+      <c r="D91" s="4">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="4">
         <v>242</v>
       </c>
     </row>
-    <row r="91" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+    <row r="92" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B92" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C92" s="4">
         <v>4540</v>
       </c>
-      <c r="D91" s="4">
-        <v>10</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G91" s="4">
+      <c r="D92" s="4">
+        <v>10</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="4">
         <v>650</v>
-      </c>
-    </row>
-    <row r="92" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C92" s="4">
-        <v>2384</v>
-      </c>
-      <c r="D92" s="4">
-        <v>25</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G92" s="4">
-        <v>187.5</v>
       </c>
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -15545,19 +15545,19 @@
         <v>140</v>
       </c>
       <c r="C93" s="4">
-        <v>3851</v>
+        <v>2384</v>
       </c>
       <c r="D93" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G93" s="4">
-        <v>75</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -15568,18 +15568,41 @@
         <v>140</v>
       </c>
       <c r="C94" s="4">
+        <v>3851</v>
+      </c>
+      <c r="D94" s="4">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C95" s="4">
         <v>2424</v>
       </c>
-      <c r="D94" s="4">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="4">
+      <c r="D95" s="4">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="4">
         <v>39.5</v>
       </c>
     </row>
@@ -23333,7 +23356,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="4">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3762" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="1142">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -4650,7 +4650,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5191,7 +5191,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>647</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>648</v>
       </c>
       <c r="C24" s="4">
-        <v>2406</v>
+        <v>3111</v>
       </c>
       <c r="D24" s="4">
         <v>10</v>
@@ -5211,21 +5211,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="4">
-        <v>400</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>647</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>30</v>
+        <v>648</v>
       </c>
       <c r="C25" s="4">
-        <v>2229</v>
+        <v>2406</v>
       </c>
       <c r="D25" s="4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>9</v>
@@ -5234,6 +5234,29 @@
         <v>28</v>
       </c>
       <c r="G25" s="4">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2229</v>
+      </c>
+      <c r="D26" s="4">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="4">
         <v>130</v>
       </c>
     </row>
@@ -15476,7 +15499,7 @@
         <v>136</v>
       </c>
       <c r="C90" s="4">
-        <v>4290</v>
+        <v>4179</v>
       </c>
       <c r="D90" s="4">
         <v>11</v>
@@ -25334,7 +25357,7 @@
         <v>10</v>
       </c>
       <c r="G108" s="4">
-        <v>315</v>
+        <v>335</v>
       </c>
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -25357,7 +25380,7 @@
         <v>11</v>
       </c>
       <c r="G109" s="4">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3766" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3768" uniqueCount="1144">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2055,6 +2055,9 @@
     <t>QUINOA EM GRÃOS</t>
   </si>
   <si>
+    <t>323.50</t>
+  </si>
+  <si>
     <t>semente-de-sucupira</t>
   </si>
   <si>
@@ -2401,6 +2404,9 @@
   </si>
   <si>
     <t>PSYLLIUM HUSK</t>
+  </si>
+  <si>
+    <t>262.50</t>
   </si>
   <si>
     <t>tribulus-terrestres-da-folha</t>
@@ -5990,7 +5996,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="4">
-        <v>1850</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6012,8 +6018,8 @@
       <c r="F32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G32" s="4">
-        <v>373.5</v>
+      <c r="G32" s="4" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6064,10 +6070,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C35" s="4">
         <v>3754</v>
@@ -6130,10 +6136,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C2" s="4">
         <v>4336</v>
@@ -6153,10 +6159,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C3" s="4">
         <v>2618</v>
@@ -6176,10 +6182,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C4" s="4">
         <v>2398</v>
@@ -6199,10 +6205,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C5" s="4">
         <v>2297</v>
@@ -6222,10 +6228,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C6" s="4">
         <v>3653</v>
@@ -6245,10 +6251,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C7" s="4">
         <v>2339</v>
@@ -6268,10 +6274,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C8" s="4">
         <v>2223</v>
@@ -6291,10 +6297,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C9" s="4">
         <v>3707</v>
@@ -6314,10 +6320,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C10" s="4">
         <v>4090</v>
@@ -6337,10 +6343,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C11" s="4">
         <v>4279</v>
@@ -6383,10 +6389,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C13" s="4">
         <v>3540</v>
@@ -6406,10 +6412,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C14" s="4">
         <v>3541</v>
@@ -6498,10 +6504,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C18" s="4">
         <v>4639</v>
@@ -6521,10 +6527,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C19" s="4">
         <v>2336</v>
@@ -6544,10 +6550,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C20" s="4">
         <v>2421</v>
@@ -6567,10 +6573,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C21" s="4">
         <v>2568</v>
@@ -6590,10 +6596,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C22" s="4">
         <v>3009</v>
@@ -6613,10 +6619,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C23" s="4">
         <v>2778</v>
@@ -6636,10 +6642,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C24" s="4">
         <v>3106</v>
@@ -6659,10 +6665,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C25" s="4">
         <v>3489</v>
@@ -6682,10 +6688,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C26" s="4">
         <v>3696</v>
@@ -6705,10 +6711,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C27" s="4">
         <v>2783</v>
@@ -6728,10 +6734,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C28" s="4">
         <v>3755</v>
@@ -6751,10 +6757,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C29" s="4">
         <v>3486</v>
@@ -6774,10 +6780,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C30" s="4">
         <v>3487</v>
@@ -6797,10 +6803,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C31" s="4">
         <v>4488</v>
@@ -6820,10 +6826,10 @@
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C32" s="4">
         <v>4333</v>
@@ -6843,10 +6849,10 @@
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C33" s="4">
         <v>4650</v>
@@ -6866,10 +6872,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C34" s="4">
         <v>4388</v>
@@ -6889,10 +6895,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C35" s="4">
         <v>4389</v>
@@ -6912,10 +6918,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C36" s="4">
         <v>3488</v>
@@ -6935,10 +6941,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C37" s="4">
         <v>3400</v>
@@ -6958,10 +6964,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C38" s="4">
         <v>2257</v>
@@ -6981,10 +6987,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C39" s="4">
         <v>565</v>
@@ -7004,10 +7010,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C40" s="4">
         <v>4474</v>
@@ -7027,10 +7033,10 @@
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C41" s="4">
         <v>4473</v>
@@ -7050,10 +7056,10 @@
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C42" s="4">
         <v>2657</v>
@@ -7073,10 +7079,10 @@
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C43" s="4">
         <v>2658</v>
@@ -7119,10 +7125,10 @@
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C45" s="4">
         <v>3537</v>
@@ -7142,10 +7148,10 @@
     </row>
     <row r="46" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C46" s="4">
         <v>2732</v>
@@ -7165,10 +7171,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C47" s="4">
         <v>2733</v>
@@ -7188,10 +7194,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C48" s="4">
         <v>2584</v>
@@ -7211,10 +7217,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C49" s="4">
         <v>2677</v>
@@ -7234,10 +7240,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C50" s="4">
         <v>2495</v>
@@ -7257,10 +7263,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C51" s="4">
         <v>2678</v>
@@ -7280,10 +7286,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C52" s="4">
         <v>4498</v>
@@ -7303,10 +7309,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C53" s="4">
         <v>4253</v>
@@ -7326,10 +7332,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C54" s="4">
         <v>4500</v>
@@ -7349,10 +7355,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C55" s="4">
         <v>4249</v>
@@ -7372,10 +7378,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C56" s="4">
         <v>3724</v>
@@ -7395,10 +7401,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C57" s="4">
         <v>3736</v>
@@ -7418,10 +7424,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C58" s="4">
         <v>4499</v>
@@ -7441,10 +7447,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C59" s="4">
         <v>3536</v>
@@ -7464,10 +7470,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C60" s="4">
         <v>2494</v>
@@ -7487,10 +7493,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C61" s="4">
         <v>2679</v>
@@ -7510,10 +7516,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C62" s="4">
         <v>4497</v>
@@ -7533,10 +7539,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C63" s="4">
         <v>2493</v>
@@ -7556,10 +7562,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C64" s="4">
         <v>3535</v>
@@ -7579,10 +7585,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C65" s="4">
         <v>2498</v>
@@ -7602,10 +7608,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C66" s="4">
         <v>2806</v>
@@ -7625,10 +7631,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C67" s="4">
         <v>2807</v>
@@ -7648,10 +7654,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C68" s="4">
         <v>4556</v>
@@ -7671,10 +7677,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C69" s="4">
         <v>4557</v>
@@ -7694,10 +7700,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C70" s="4">
         <v>4018</v>
@@ -7717,10 +7723,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C71" s="4">
         <v>2652</v>
@@ -7740,10 +7746,10 @@
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C72" s="4">
         <v>4049</v>
@@ -7763,10 +7769,10 @@
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C73" s="4">
         <v>3737</v>
@@ -7786,10 +7792,10 @@
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C74" s="4">
         <v>4301</v>
@@ -7809,10 +7815,10 @@
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C75" s="4">
         <v>4334</v>
@@ -7832,10 +7838,10 @@
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C76" s="4">
         <v>195</v>
@@ -7855,10 +7861,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C77" s="4">
         <v>54</v>
@@ -7878,10 +7884,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C78" s="4">
         <v>63</v>
@@ -7901,10 +7907,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C79" s="4">
         <v>2483</v>
@@ -7924,10 +7930,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C80" s="4">
         <v>2974</v>
@@ -7947,10 +7953,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C81" s="4">
         <v>2831</v>
@@ -7970,10 +7976,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C82" s="4">
         <v>4137</v>
@@ -7993,10 +7999,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C83" s="4">
         <v>4380</v>
@@ -8016,10 +8022,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C84" s="4">
         <v>4566</v>
@@ -8039,10 +8045,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C85" s="4">
         <v>4567</v>
@@ -8062,10 +8068,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C86" s="4">
         <v>4204</v>
@@ -8085,10 +8091,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C87" s="4">
         <v>4205</v>
@@ -8108,10 +8114,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C88" s="4">
         <v>4225</v>
@@ -8131,10 +8137,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C89" s="4">
         <v>4378</v>
@@ -8154,10 +8160,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C90" s="4">
         <v>4379</v>
@@ -8177,10 +8183,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C91" s="4">
         <v>3524</v>
@@ -8192,7 +8198,7 @@
         <v>9</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G91" s="4">
         <v>350</v>
@@ -8200,10 +8206,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C92" s="4">
         <v>3523</v>
@@ -8215,7 +8221,7 @@
         <v>9</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G92" s="4">
         <v>72</v>
@@ -8223,10 +8229,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C93" s="4">
         <v>3521</v>
@@ -8235,7 +8241,7 @@
         <v>16</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>28</v>
@@ -8246,10 +8252,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C94" s="4">
         <v>3522</v>
@@ -8269,10 +8275,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C95" s="4">
         <v>64</v>
@@ -8292,10 +8298,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C96" s="4">
         <v>90</v>
@@ -8315,10 +8321,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C97" s="4">
         <v>3637</v>
@@ -8332,16 +8338,16 @@
       <c r="F97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G97" s="4">
-        <v>375</v>
+      <c r="G97" s="4" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C98" s="4">
         <v>2805</v>
@@ -8356,15 +8362,15 @@
         <v>10</v>
       </c>
       <c r="G98" s="4">
-        <v>150</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C99" s="4">
         <v>2427</v>
@@ -8379,15 +8385,15 @@
         <v>11</v>
       </c>
       <c r="G99" s="4">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C100" s="4">
         <v>3437</v>
@@ -8407,10 +8413,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C101" s="4">
         <v>3396</v>
@@ -8430,10 +8436,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C102" s="4">
         <v>3395</v>
@@ -8442,7 +8448,7 @@
         <v>12</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>28</v>
@@ -8453,10 +8459,10 @@
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C103" s="4">
         <v>3490</v>
@@ -8465,7 +8471,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>28</v>
@@ -8476,10 +8482,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C104" s="4">
         <v>458</v>
@@ -8488,7 +8494,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>28</v>
@@ -8499,10 +8505,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C105" s="4">
         <v>2641</v>
@@ -8511,7 +8517,7 @@
         <v>12</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>28</v>
@@ -8522,10 +8528,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C106" s="4">
         <v>4293</v>
@@ -8534,7 +8540,7 @@
         <v>12</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>28</v>
@@ -8545,10 +8551,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C107" s="4">
         <v>2396</v>
@@ -8568,10 +8574,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C108" s="4">
         <v>2426</v>
@@ -8591,10 +8597,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C109" s="4">
         <v>4335</v>
@@ -8614,10 +8620,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C110" s="4">
         <v>4477</v>
@@ -8637,10 +8643,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C111" s="4">
         <v>4479</v>
@@ -8660,10 +8666,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C112" s="4">
         <v>4478</v>
@@ -8683,10 +8689,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C113" s="4">
         <v>2646</v>
@@ -8695,7 +8701,7 @@
         <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>272</v>
@@ -8706,10 +8712,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C114" s="4">
         <v>2645</v>
@@ -8718,7 +8724,7 @@
         <v>6</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>272</v>
@@ -8729,10 +8735,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C115" s="4">
         <v>2638</v>
@@ -8741,7 +8747,7 @@
         <v>9</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>272</v>
@@ -8752,10 +8758,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C116" s="4">
         <v>4294</v>
@@ -8764,7 +8770,7 @@
         <v>18</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>272</v>
@@ -8775,10 +8781,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C117" s="4">
         <v>4314</v>
@@ -8798,10 +8804,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C118" s="4">
         <v>4315</v>
@@ -8810,7 +8816,7 @@
         <v>15</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>28</v>
@@ -8864,10 +8870,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C2" s="4">
         <v>3402</v>
@@ -8876,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>272</v>
@@ -8887,10 +8893,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C3" s="4">
         <v>3401</v>
@@ -8899,7 +8905,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>272</v>
@@ -8910,10 +8916,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C4" s="4">
         <v>3403</v>
@@ -8922,7 +8928,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>272</v>
@@ -8933,10 +8939,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C5" s="4">
         <v>4032</v>
@@ -8945,7 +8951,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>272</v>
@@ -8956,10 +8962,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C6" s="4">
         <v>4460</v>
@@ -8968,7 +8974,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>272</v>
@@ -8979,10 +8985,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C7" s="4">
         <v>4260</v>
@@ -8991,7 +8997,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>272</v>
@@ -9002,10 +9008,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C8" s="4">
         <v>2551</v>
@@ -9014,7 +9020,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>272</v>
@@ -9025,10 +9031,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C9" s="4">
         <v>2550</v>
@@ -9037,7 +9043,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>272</v>
@@ -9048,10 +9054,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C10" s="4">
         <v>4383</v>
@@ -9060,7 +9066,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>272</v>
@@ -9114,10 +9120,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C2" s="4">
         <v>3644</v>
@@ -9126,7 +9132,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>272</v>
@@ -9137,10 +9143,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C3" s="4">
         <v>3644</v>
@@ -9149,7 +9155,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>272</v>
@@ -9160,10 +9166,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C4" s="4">
         <v>3641</v>
@@ -9172,7 +9178,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>272</v>
@@ -9183,10 +9189,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C5" s="4">
         <v>3645</v>
@@ -9195,7 +9201,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>272</v>
@@ -9206,10 +9212,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C6" s="4">
         <v>3852</v>
@@ -9218,7 +9224,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -9229,10 +9235,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C7" s="4">
         <v>3647</v>
@@ -9241,7 +9247,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>272</v>
@@ -9252,10 +9258,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C8" s="4">
         <v>3648</v>
@@ -9264,7 +9270,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>272</v>
@@ -9318,10 +9324,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C2" s="4">
         <v>3056</v>
@@ -9341,10 +9347,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C3" s="4">
         <v>3083</v>
@@ -9364,10 +9370,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C4" s="4">
         <v>2264</v>
@@ -9387,10 +9393,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C5" s="4">
         <v>2355</v>
@@ -9410,10 +9416,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C6" s="4">
         <v>573</v>
@@ -9433,10 +9439,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C7" s="4">
         <v>572</v>
@@ -9456,10 +9462,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C8" s="4">
         <v>4411</v>
@@ -9479,10 +9485,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C9" s="4">
         <v>4410</v>
@@ -9545,10 +9551,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C2" s="4">
         <v>4044</v>
@@ -9557,7 +9563,7 @@
         <v>500</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -9568,10 +9574,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C3" s="4">
         <v>4672</v>
@@ -9580,7 +9586,7 @@
         <v>500</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -9591,10 +9597,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C4" s="4">
         <v>4043</v>
@@ -9614,10 +9620,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C5" s="4">
         <v>3531</v>
@@ -9637,10 +9643,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C6" s="4">
         <v>3974</v>
@@ -9660,10 +9666,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C7" s="4">
         <v>3530</v>
@@ -9683,10 +9689,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C8" s="4">
         <v>4282</v>
@@ -9706,10 +9712,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C9" s="4">
         <v>3870</v>
@@ -9718,7 +9724,7 @@
         <v>500</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -9729,10 +9735,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C10" s="4">
         <v>3701</v>
@@ -9741,7 +9747,7 @@
         <v>500</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -9752,10 +9758,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C11" s="4">
         <v>3800</v>
@@ -9764,7 +9770,7 @@
         <v>500</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -9775,10 +9781,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="C12" s="4">
         <v>3725</v>
@@ -9787,7 +9793,7 @@
         <v>500</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -9798,10 +9804,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C13" s="4">
         <v>3871</v>
@@ -9810,7 +9816,7 @@
         <v>500</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -9821,10 +9827,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C14" s="4">
         <v>2825</v>
@@ -9844,10 +9850,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C15" s="4">
         <v>2828</v>
@@ -9867,10 +9873,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C16" s="4">
         <v>2826</v>
@@ -9890,10 +9896,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C17" s="4">
         <v>3058</v>
@@ -9913,10 +9919,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C18" s="4">
         <v>3059</v>
@@ -9936,10 +9942,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C19" s="4">
         <v>2829</v>
@@ -9959,10 +9965,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C20" s="4">
         <v>4126</v>
@@ -9982,10 +9988,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C21" s="4">
         <v>2827</v>
@@ -10005,10 +10011,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C22" s="4">
         <v>3801</v>
@@ -10017,7 +10023,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -10028,10 +10034,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C23" s="4">
         <v>3833</v>
@@ -10040,7 +10046,7 @@
         <v>500</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -10051,10 +10057,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="C24" s="4">
         <v>3897</v>
@@ -10074,10 +10080,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C25" s="4">
         <v>3764</v>
@@ -10186,10 +10192,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C4" s="4">
         <v>3443</v>
@@ -10209,10 +10215,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C5" s="4">
         <v>3019</v>
@@ -10232,10 +10238,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C6" s="4">
         <v>4489</v>
@@ -10255,10 +10261,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C7" s="4">
         <v>4490</v>
@@ -10278,10 +10284,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C8" s="4">
         <v>3476</v>
@@ -10301,10 +10307,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C9" s="4">
         <v>3477</v>
@@ -10324,10 +10330,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C10" s="4">
         <v>4344</v>
@@ -10393,10 +10399,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C13" s="4">
         <v>3719</v>
@@ -10416,10 +10422,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C14" s="4">
         <v>3720</v>
@@ -10439,10 +10445,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C15" s="4">
         <v>3765</v>
@@ -10462,10 +10468,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C16" s="4">
         <v>3766</v>
@@ -10485,10 +10491,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C17" s="4">
         <v>3126</v>
@@ -10508,10 +10514,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C18" s="4">
         <v>3127</v>
@@ -10531,10 +10537,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C19" s="4">
         <v>3435</v>
@@ -10554,10 +10560,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C20" s="4">
         <v>3436</v>
@@ -10577,10 +10583,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C21" s="4">
         <v>3128</v>
@@ -10600,10 +10606,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C22" s="4">
         <v>3129</v>
@@ -10623,10 +10629,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C23" s="4">
         <v>4158</v>
@@ -10646,10 +10652,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C24" s="4">
         <v>4159</v>
@@ -10669,10 +10675,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C25" s="4">
         <v>4561</v>
@@ -10692,10 +10698,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C26" s="4">
         <v>4562</v>
@@ -10807,10 +10813,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C31" s="4">
         <v>4346</v>
@@ -10830,10 +10836,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="C32" s="4">
         <v>4345</v>
@@ -10853,10 +10859,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C33" s="4">
         <v>4347</v>
@@ -10876,10 +10882,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C34" s="4">
         <v>4446</v>
@@ -10899,10 +10905,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C35" s="4">
         <v>4476</v>
@@ -10914,7 +10920,7 @@
         <v>9</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G35" s="4">
         <v>33.5</v>
@@ -10922,10 +10928,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C36" s="4">
         <v>4348</v>
@@ -10945,10 +10951,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C37" s="4">
         <v>4456</v>
@@ -10968,10 +10974,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C38" s="4">
         <v>4051</v>
@@ -10991,10 +10997,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C39" s="4">
         <v>4408</v>
@@ -11014,10 +11020,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="C40" s="4">
         <v>4341</v>
@@ -11037,10 +11043,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C41" s="4">
         <v>4265</v>
@@ -11060,10 +11066,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C42" s="4">
         <v>4266</v>
@@ -11083,10 +11089,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="C43" s="4">
         <v>4269</v>
@@ -11106,10 +11112,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C44" s="4">
         <v>4273</v>
@@ -11129,10 +11135,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="C45" s="4">
         <v>4405</v>
@@ -11152,10 +11158,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C46" s="4">
         <v>4406</v>
@@ -11175,10 +11181,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="C47" s="4">
         <v>4267</v>
@@ -11198,10 +11204,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C48" s="4">
         <v>4271</v>
@@ -11221,10 +11227,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C49" s="4">
         <v>4276</v>
@@ -11244,10 +11250,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C50" s="4">
         <v>4342</v>
@@ -11267,10 +11273,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C51" s="4">
         <v>2505</v>
@@ -11290,10 +11296,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C52" s="4">
         <v>4398</v>
@@ -11313,10 +11319,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C53" s="4">
         <v>4270</v>
@@ -11336,10 +11342,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C54" s="4">
         <v>4275</v>
@@ -11359,10 +11365,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C55" s="4">
         <v>4274</v>
@@ -11382,10 +11388,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C56" s="4">
         <v>4399</v>
@@ -11405,10 +11411,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C57" s="4">
         <v>4404</v>
@@ -11428,10 +11434,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C58" s="4">
         <v>4262</v>
@@ -11451,10 +11457,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C59" s="4">
         <v>4263</v>
@@ -11474,10 +11480,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C60" s="4">
         <v>4264</v>
@@ -11497,10 +11503,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C61" s="4">
         <v>4407</v>
@@ -11520,10 +11526,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C62" s="4">
         <v>4397</v>
@@ -11543,10 +11549,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C63" s="4">
         <v>4343</v>
@@ -11566,10 +11572,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C64" s="4">
         <v>4268</v>
@@ -11589,10 +11595,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C65" s="4">
         <v>2833</v>
@@ -11612,10 +11618,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C66" s="4">
         <v>3125</v>
@@ -11635,10 +11641,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C67" s="4">
         <v>3752</v>
@@ -11658,10 +11664,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C68" s="4">
         <v>3753</v>
@@ -11681,10 +11687,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C69" s="4">
         <v>2511</v>
@@ -11704,10 +11710,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C70" s="4">
         <v>4311</v>
@@ -11727,10 +11733,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C71" s="4">
         <v>4046</v>
@@ -11750,10 +11756,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C72" s="4">
         <v>4047</v>
@@ -11773,10 +11779,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C73" s="4">
         <v>4312</v>
@@ -11796,10 +11802,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C74" s="4">
         <v>4310</v>
@@ -11819,10 +11825,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C75" s="4">
         <v>4074</v>
@@ -11831,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -11842,10 +11848,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C76" s="4">
         <v>4076</v>
@@ -11854,10 +11860,10 @@
         <v>1</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G76" s="4">
         <v>32.5</v>
@@ -11865,10 +11871,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C77" s="4">
         <v>4133</v>
@@ -11880,7 +11886,7 @@
         <v>424</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G77" s="4">
         <v>72</v>
@@ -11888,10 +11894,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C78" s="4">
         <v>3068</v>
@@ -11911,10 +11917,10 @@
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C79" s="4">
         <v>3087</v>
@@ -11934,10 +11940,10 @@
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C80" s="4">
         <v>4560</v>
@@ -11957,10 +11963,10 @@
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C81" s="4">
         <v>4531</v>
@@ -11980,10 +11986,10 @@
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C82" s="4">
         <v>4532</v>
@@ -12003,10 +12009,10 @@
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C83" s="4">
         <v>4559</v>
@@ -12026,10 +12032,10 @@
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C84" s="4">
         <v>4493</v>
@@ -12049,10 +12055,10 @@
     </row>
     <row r="85" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C85" s="4">
         <v>4102</v>
@@ -12061,7 +12067,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -12072,10 +12078,10 @@
     </row>
     <row r="86" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="C86" s="4">
         <v>4103</v>
@@ -12084,7 +12090,7 @@
         <v>10</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>272</v>
@@ -12095,10 +12101,10 @@
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="C87" s="4">
         <v>4547</v>
@@ -12107,7 +12113,7 @@
         <v>10</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>272</v>
@@ -12118,10 +12124,10 @@
     </row>
     <row r="88" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C88" s="4">
         <v>4624</v>
@@ -12130,7 +12136,7 @@
         <v>21</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -12141,10 +12147,10 @@
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C89" s="4">
         <v>4627</v>
@@ -12153,7 +12159,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -12164,10 +12170,10 @@
     </row>
     <row r="90" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C90" s="4">
         <v>4628</v>
@@ -12176,7 +12182,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -12187,10 +12193,10 @@
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C91" s="4">
         <v>4625</v>
@@ -12199,7 +12205,7 @@
         <v>21</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -12210,10 +12216,10 @@
     </row>
     <row r="92" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C92" s="4">
         <v>4626</v>
@@ -12222,7 +12228,7 @@
         <v>21</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -12233,10 +12239,10 @@
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C93" s="4">
         <v>4699</v>
@@ -12245,7 +12251,7 @@
         <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>272</v>
@@ -12256,10 +12262,10 @@
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C94" s="4">
         <v>4643</v>
@@ -12268,10 +12274,10 @@
         <v>6</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G94" s="4">
         <v>97.5</v>
@@ -12279,10 +12285,10 @@
     </row>
     <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C95" s="4">
         <v>4687</v>
@@ -12291,10 +12297,10 @@
         <v>6</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G95" s="4">
         <v>64</v>
@@ -12302,10 +12308,10 @@
     </row>
     <row r="96" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C96" s="4">
         <v>4644</v>
@@ -12314,10 +12320,10 @@
         <v>6</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G96" s="4">
         <v>57</v>
@@ -12325,10 +12331,10 @@
     </row>
     <row r="97" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C97" s="4">
         <v>4104</v>
@@ -12337,7 +12343,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>272</v>
@@ -12348,10 +12354,10 @@
     </row>
     <row r="98" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C98" s="4">
         <v>4101</v>
@@ -12360,7 +12366,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>272</v>
@@ -12371,10 +12377,10 @@
     </row>
     <row r="99" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C99" s="4">
         <v>4105</v>
@@ -12383,7 +12389,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>272</v>
@@ -12394,10 +12400,10 @@
     </row>
     <row r="100" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C100" s="4">
         <v>3705</v>
@@ -12406,7 +12412,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>272</v>
@@ -12417,10 +12423,10 @@
     </row>
     <row r="101" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C101" s="4">
         <v>3823</v>
@@ -12429,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>28</v>
@@ -12440,10 +12446,10 @@
     </row>
     <row r="102" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C102" s="4">
         <v>4641</v>
@@ -12452,7 +12458,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -12463,10 +12469,10 @@
     </row>
     <row r="103" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C103" s="4">
         <v>4583</v>
@@ -12475,7 +12481,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>272</v>
@@ -12486,10 +12492,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C104" s="4">
         <v>4308</v>
@@ -12498,7 +12504,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -12509,10 +12515,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C105" s="4">
         <v>4309</v>
@@ -12521,10 +12527,10 @@
         <v>10</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G105" s="4">
         <v>68.5</v>
@@ -12532,10 +12538,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C106" s="4">
         <v>4635</v>
@@ -12547,7 +12553,7 @@
         <v>424</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G106" s="4">
         <v>177</v>
@@ -12555,10 +12561,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C107" s="4">
         <v>4412</v>
@@ -12570,7 +12576,7 @@
         <v>9</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G107" s="4">
         <v>75.5</v>
@@ -12578,10 +12584,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C108" s="4">
         <v>4413</v>
@@ -12601,10 +12607,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C109" s="4">
         <v>4414</v>
@@ -12624,10 +12630,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C110" s="4">
         <v>4415</v>
@@ -12647,10 +12653,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C111" s="4">
         <v>4416</v>
@@ -12670,10 +12676,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C112" s="4">
         <v>4475</v>
@@ -12682,7 +12688,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -12693,10 +12699,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C113" s="4">
         <v>4354</v>
@@ -12705,10 +12711,10 @@
         <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G113" s="4">
         <v>79.5</v>
@@ -12716,10 +12722,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C114" s="4">
         <v>4445</v>
@@ -12728,7 +12734,7 @@
         <v>12</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>28</v>
@@ -12739,10 +12745,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C115" s="4">
         <v>4353</v>
@@ -12751,7 +12757,7 @@
         <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>28</v>
@@ -12762,10 +12768,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C116" s="4">
         <v>4350</v>
@@ -12774,7 +12780,7 @@
         <v>12</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>28</v>
@@ -12785,10 +12791,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C117" s="4">
         <v>4352</v>
@@ -12797,7 +12803,7 @@
         <v>12</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>28</v>
@@ -12808,10 +12814,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="C118" s="4">
         <v>4349</v>
@@ -12820,7 +12826,7 @@
         <v>12</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>28</v>
@@ -12831,10 +12837,10 @@
     </row>
     <row r="119" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C119" s="4">
         <v>4351</v>
@@ -12843,7 +12849,7 @@
         <v>12</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>28</v>
@@ -12854,10 +12860,10 @@
     </row>
     <row r="120" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="C120" s="4">
         <v>4581</v>
@@ -12866,7 +12872,7 @@
         <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>28</v>
@@ -12877,10 +12883,10 @@
     </row>
     <row r="121" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C121" s="4">
         <v>4096</v>
@@ -12900,10 +12906,10 @@
     </row>
     <row r="122" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C122" s="4">
         <v>4582</v>
@@ -12912,7 +12918,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -12923,10 +12929,10 @@
     </row>
     <row r="123" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C123" s="4">
         <v>4123</v>
@@ -12935,7 +12941,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -12946,10 +12952,10 @@
     </row>
     <row r="124" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C124" s="4">
         <v>4306</v>
@@ -12958,10 +12964,10 @@
         <v>10</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G124" s="4">
         <v>81</v>
@@ -12969,10 +12975,10 @@
     </row>
     <row r="125" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C125" s="4">
         <v>4307</v>
@@ -12981,10 +12987,10 @@
         <v>10</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G125" s="4">
         <v>81</v>
@@ -12992,10 +12998,10 @@
     </row>
     <row r="126" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C126" s="4">
         <v>2659</v>
@@ -13004,7 +13010,7 @@
         <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>272</v>
@@ -13015,10 +13021,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C127" s="4">
         <v>2621</v>
@@ -13027,7 +13033,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>272</v>
@@ -13038,10 +13044,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C128" s="4">
         <v>3656</v>
@@ -13050,7 +13056,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>272</v>
@@ -13104,10 +13110,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C2" s="4">
         <v>3459</v>
@@ -13116,7 +13122,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -13127,10 +13133,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C3" s="4">
         <v>3803</v>
@@ -13139,7 +13145,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -13150,10 +13156,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C4" s="4">
         <v>3425</v>
@@ -13162,10 +13168,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G4" s="4">
         <v>29</v>
@@ -13173,10 +13179,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C5" s="4">
         <v>3426</v>
@@ -13185,7 +13191,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>28</v>
@@ -13196,10 +13202,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C6" s="4">
         <v>3427</v>
@@ -13208,10 +13214,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G6" s="4">
         <v>62.5</v>
@@ -13219,10 +13225,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C7" s="4">
         <v>3428</v>
@@ -13231,7 +13237,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>28</v>
@@ -13242,10 +13248,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C8" s="4">
         <v>3429</v>
@@ -13254,10 +13260,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G8" s="4">
         <v>76.5</v>
@@ -13265,10 +13271,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C9" s="4">
         <v>3430</v>
@@ -13277,7 +13283,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>28</v>
@@ -13288,10 +13294,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C10" s="4">
         <v>3913</v>
@@ -13300,10 +13306,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G10" s="4">
         <v>68</v>
@@ -13311,10 +13317,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C11" s="4">
         <v>3872</v>
@@ -13323,7 +13329,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>28</v>
@@ -13334,10 +13340,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C12" s="4">
         <v>3422</v>
@@ -13346,10 +13352,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G12" s="4">
         <v>20</v>
@@ -13357,10 +13363,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C13" s="4">
         <v>3423</v>
@@ -13369,7 +13375,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>28</v>
@@ -13380,10 +13386,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C14" s="4">
         <v>3431</v>
@@ -13392,10 +13398,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G14" s="4">
         <v>115</v>
@@ -13403,10 +13409,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C15" s="4">
         <v>3432</v>
@@ -13415,7 +13421,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>28</v>
@@ -15922,7 +15928,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="4">
-        <v>650</v>
+        <v>675</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -15945,7 +15951,7 @@
         <v>11</v>
       </c>
       <c r="G13" s="4">
-        <v>133.5</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -23103,7 +23109,7 @@
         <v>272</v>
       </c>
       <c r="G10" s="4">
-        <v>290</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -16644,7 +16644,7 @@
         <v>11</v>
       </c>
       <c r="G16" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -16667,7 +16667,7 @@
         <v>11</v>
       </c>
       <c r="G17" s="4">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3771" uniqueCount="1147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="1148">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2044,6 +2044,9 @@
   </si>
   <si>
     <t>PAINÇO</t>
+  </si>
+  <si>
+    <t>27.50</t>
   </si>
   <si>
     <t>pepita-de-girassol</t>
@@ -5797,16 +5800,16 @@
       <c r="F22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="4">
-        <v>23</v>
+      <c r="G22" s="4" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C23" s="4">
         <v>3417</v>
@@ -5826,10 +5829,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C24" s="4">
         <v>2716</v>
@@ -5849,10 +5852,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C25" s="4">
         <v>2478</v>
@@ -5872,10 +5875,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C26" s="4">
         <v>2606</v>
@@ -5895,10 +5898,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C27" s="4">
         <v>2338</v>
@@ -5918,10 +5921,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C28" s="4">
         <v>2425</v>
@@ -5941,10 +5944,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C29" s="4">
         <v>2579</v>
@@ -5964,10 +5967,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C30" s="4">
         <v>2243</v>
@@ -6028,7 +6031,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6079,10 +6082,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C35" s="4">
         <v>3754</v>
@@ -6145,10 +6148,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C2" s="4">
         <v>4336</v>
@@ -6168,10 +6171,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C3" s="4">
         <v>2618</v>
@@ -6191,10 +6194,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C4" s="4">
         <v>2398</v>
@@ -6214,10 +6217,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C5" s="4">
         <v>2297</v>
@@ -6237,10 +6240,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C6" s="4">
         <v>3653</v>
@@ -6260,10 +6263,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C7" s="4">
         <v>2339</v>
@@ -6283,10 +6286,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C8" s="4">
         <v>2223</v>
@@ -6306,10 +6309,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C9" s="4">
         <v>3707</v>
@@ -6329,10 +6332,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C10" s="4">
         <v>4090</v>
@@ -6352,10 +6355,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C11" s="4">
         <v>4279</v>
@@ -6398,10 +6401,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C13" s="4">
         <v>3540</v>
@@ -6421,10 +6424,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C14" s="4">
         <v>3541</v>
@@ -6513,10 +6516,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C18" s="4">
         <v>4639</v>
@@ -6536,10 +6539,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C19" s="4">
         <v>2336</v>
@@ -6559,10 +6562,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C20" s="4">
         <v>2421</v>
@@ -6582,10 +6585,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C21" s="4">
         <v>2568</v>
@@ -6605,10 +6608,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C22" s="4">
         <v>3009</v>
@@ -6628,10 +6631,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C23" s="4">
         <v>2778</v>
@@ -6651,10 +6654,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C24" s="4">
         <v>3106</v>
@@ -6674,10 +6677,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C25" s="4">
         <v>3489</v>
@@ -6697,10 +6700,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C26" s="4">
         <v>3696</v>
@@ -6720,10 +6723,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C27" s="4">
         <v>2783</v>
@@ -6743,10 +6746,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C28" s="4">
         <v>3755</v>
@@ -6766,10 +6769,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C29" s="4">
         <v>3486</v>
@@ -6789,10 +6792,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C30" s="4">
         <v>3487</v>
@@ -6812,10 +6815,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C31" s="4">
         <v>4488</v>
@@ -6835,10 +6838,10 @@
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C32" s="4">
         <v>4333</v>
@@ -6858,10 +6861,10 @@
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C33" s="4">
         <v>4650</v>
@@ -6881,10 +6884,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C34" s="4">
         <v>4388</v>
@@ -6904,10 +6907,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C35" s="4">
         <v>4389</v>
@@ -6927,10 +6930,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C36" s="4">
         <v>3488</v>
@@ -6950,10 +6953,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C37" s="4">
         <v>3400</v>
@@ -6973,10 +6976,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C38" s="4">
         <v>2257</v>
@@ -6996,10 +6999,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C39" s="4">
         <v>565</v>
@@ -7019,10 +7022,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C40" s="4">
         <v>4474</v>
@@ -7042,10 +7045,10 @@
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C41" s="4">
         <v>4473</v>
@@ -7065,10 +7068,10 @@
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C42" s="4">
         <v>2657</v>
@@ -7088,10 +7091,10 @@
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C43" s="4">
         <v>2658</v>
@@ -7134,10 +7137,10 @@
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C45" s="4">
         <v>3537</v>
@@ -7157,10 +7160,10 @@
     </row>
     <row r="46" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C46" s="4">
         <v>2732</v>
@@ -7180,10 +7183,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C47" s="4">
         <v>2733</v>
@@ -7203,10 +7206,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C48" s="4">
         <v>2584</v>
@@ -7226,10 +7229,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C49" s="4">
         <v>2677</v>
@@ -7249,10 +7252,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C50" s="4">
         <v>2495</v>
@@ -7272,10 +7275,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C51" s="4">
         <v>2678</v>
@@ -7295,10 +7298,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C52" s="4">
         <v>4498</v>
@@ -7318,10 +7321,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C53" s="4">
         <v>4253</v>
@@ -7341,10 +7344,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C54" s="4">
         <v>4500</v>
@@ -7364,10 +7367,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C55" s="4">
         <v>4249</v>
@@ -7387,10 +7390,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C56" s="4">
         <v>3724</v>
@@ -7410,10 +7413,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C57" s="4">
         <v>3736</v>
@@ -7433,10 +7436,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C58" s="4">
         <v>4499</v>
@@ -7456,10 +7459,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C59" s="4">
         <v>3536</v>
@@ -7479,10 +7482,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C60" s="4">
         <v>2494</v>
@@ -7502,10 +7505,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C61" s="4">
         <v>2679</v>
@@ -7525,10 +7528,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C62" s="4">
         <v>4497</v>
@@ -7548,10 +7551,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C63" s="4">
         <v>2493</v>
@@ -7571,10 +7574,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C64" s="4">
         <v>3535</v>
@@ -7594,10 +7597,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C65" s="4">
         <v>2498</v>
@@ -7617,10 +7620,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C66" s="4">
         <v>2806</v>
@@ -7640,10 +7643,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C67" s="4">
         <v>2807</v>
@@ -7663,10 +7666,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C68" s="4">
         <v>4556</v>
@@ -7686,10 +7689,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C69" s="4">
         <v>4557</v>
@@ -7709,10 +7712,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C70" s="4">
         <v>4018</v>
@@ -7732,10 +7735,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C71" s="4">
         <v>2652</v>
@@ -7755,10 +7758,10 @@
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C72" s="4">
         <v>4049</v>
@@ -7778,10 +7781,10 @@
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C73" s="4">
         <v>3737</v>
@@ -7801,10 +7804,10 @@
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C74" s="4">
         <v>4301</v>
@@ -7824,10 +7827,10 @@
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C75" s="4">
         <v>4334</v>
@@ -7847,10 +7850,10 @@
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C76" s="4">
         <v>195</v>
@@ -7870,10 +7873,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C77" s="4">
         <v>54</v>
@@ -7893,10 +7896,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C78" s="4">
         <v>63</v>
@@ -7916,10 +7919,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C79" s="4">
         <v>2483</v>
@@ -7939,10 +7942,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C80" s="4">
         <v>2974</v>
@@ -7962,10 +7965,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C81" s="4">
         <v>2831</v>
@@ -7985,10 +7988,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C82" s="4">
         <v>4137</v>
@@ -8008,10 +8011,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C83" s="4">
         <v>4380</v>
@@ -8031,10 +8034,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C84" s="4">
         <v>4566</v>
@@ -8054,10 +8057,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C85" s="4">
         <v>4567</v>
@@ -8077,10 +8080,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C86" s="4">
         <v>4204</v>
@@ -8100,10 +8103,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C87" s="4">
         <v>4205</v>
@@ -8123,10 +8126,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C88" s="4">
         <v>4378</v>
@@ -8146,10 +8149,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C89" s="4">
         <v>4379</v>
@@ -8169,10 +8172,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C90" s="4">
         <v>3524</v>
@@ -8184,7 +8187,7 @@
         <v>9</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G90" s="4">
         <v>350</v>
@@ -8192,10 +8195,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C91" s="4">
         <v>3523</v>
@@ -8207,7 +8210,7 @@
         <v>9</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G91" s="4">
         <v>72</v>
@@ -8215,10 +8218,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C92" s="4">
         <v>3521</v>
@@ -8227,7 +8230,7 @@
         <v>16</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>28</v>
@@ -8238,10 +8241,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C93" s="4">
         <v>3522</v>
@@ -8261,10 +8264,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C94" s="4">
         <v>64</v>
@@ -8284,10 +8287,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C95" s="4">
         <v>90</v>
@@ -8307,10 +8310,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C96" s="4">
         <v>3637</v>
@@ -8325,15 +8328,15 @@
         <v>10</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C97" s="4">
         <v>2805</v>
@@ -8353,10 +8356,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C98" s="4">
         <v>2427</v>
@@ -8376,10 +8379,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C99" s="4">
         <v>3437</v>
@@ -8399,10 +8402,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C100" s="4">
         <v>3396</v>
@@ -8422,10 +8425,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C101" s="4">
         <v>3395</v>
@@ -8434,7 +8437,7 @@
         <v>12</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>28</v>
@@ -8445,10 +8448,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C102" s="4">
         <v>3490</v>
@@ -8457,7 +8460,7 @@
         <v>12</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>28</v>
@@ -8468,10 +8471,10 @@
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C103" s="4">
         <v>458</v>
@@ -8480,7 +8483,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>28</v>
@@ -8491,10 +8494,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C104" s="4">
         <v>2641</v>
@@ -8503,7 +8506,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>28</v>
@@ -8514,10 +8517,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C105" s="4">
         <v>4293</v>
@@ -8526,7 +8529,7 @@
         <v>12</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>28</v>
@@ -8537,10 +8540,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C106" s="4">
         <v>2396</v>
@@ -8560,10 +8563,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C107" s="4">
         <v>2426</v>
@@ -8583,10 +8586,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C108" s="4">
         <v>4335</v>
@@ -8606,10 +8609,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C109" s="4">
         <v>4477</v>
@@ -8629,10 +8632,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C110" s="4">
         <v>4479</v>
@@ -8652,10 +8655,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C111" s="4">
         <v>4478</v>
@@ -8675,10 +8678,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C112" s="4">
         <v>2646</v>
@@ -8687,7 +8690,7 @@
         <v>12</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>273</v>
@@ -8698,10 +8701,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C113" s="4">
         <v>2645</v>
@@ -8710,7 +8713,7 @@
         <v>6</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>273</v>
@@ -8721,10 +8724,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C114" s="4">
         <v>2638</v>
@@ -8733,7 +8736,7 @@
         <v>9</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>273</v>
@@ -8744,10 +8747,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C115" s="4">
         <v>4294</v>
@@ -8756,7 +8759,7 @@
         <v>18</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>273</v>
@@ -8767,10 +8770,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C116" s="4">
         <v>4314</v>
@@ -8790,10 +8793,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C117" s="4">
         <v>4315</v>
@@ -8802,7 +8805,7 @@
         <v>15</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>28</v>
@@ -8856,10 +8859,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C2" s="4">
         <v>3402</v>
@@ -8868,7 +8871,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>273</v>
@@ -8879,10 +8882,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C3" s="4">
         <v>3401</v>
@@ -8891,7 +8894,7 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>273</v>
@@ -8902,10 +8905,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C4" s="4">
         <v>3403</v>
@@ -8914,7 +8917,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>273</v>
@@ -8925,10 +8928,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C5" s="4">
         <v>4032</v>
@@ -8937,7 +8940,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>273</v>
@@ -8948,10 +8951,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C6" s="4">
         <v>4460</v>
@@ -8960,7 +8963,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>273</v>
@@ -8971,10 +8974,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C7" s="4">
         <v>4260</v>
@@ -8983,7 +8986,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>273</v>
@@ -8994,10 +8997,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C8" s="4">
         <v>2551</v>
@@ -9006,7 +9009,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>273</v>
@@ -9017,10 +9020,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C9" s="4">
         <v>2550</v>
@@ -9029,7 +9032,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>273</v>
@@ -9040,10 +9043,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C10" s="4">
         <v>4383</v>
@@ -9052,7 +9055,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>273</v>
@@ -9106,10 +9109,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C2" s="4">
         <v>3644</v>
@@ -9118,7 +9121,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>273</v>
@@ -9129,10 +9132,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C3" s="4">
         <v>3644</v>
@@ -9141,7 +9144,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>273</v>
@@ -9152,10 +9155,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C4" s="4">
         <v>3641</v>
@@ -9164,7 +9167,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>273</v>
@@ -9175,10 +9178,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C5" s="4">
         <v>3645</v>
@@ -9187,7 +9190,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>273</v>
@@ -9198,10 +9201,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C6" s="4">
         <v>3852</v>
@@ -9210,7 +9213,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -9221,10 +9224,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C7" s="4">
         <v>3647</v>
@@ -9233,7 +9236,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>273</v>
@@ -9244,10 +9247,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C8" s="4">
         <v>3648</v>
@@ -9256,7 +9259,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>273</v>
@@ -9310,10 +9313,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C2" s="4">
         <v>3056</v>
@@ -9328,15 +9331,15 @@
         <v>273</v>
       </c>
       <c r="G2" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C3" s="4">
         <v>3083</v>
@@ -9351,15 +9354,15 @@
         <v>273</v>
       </c>
       <c r="G3" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C4" s="4">
         <v>2264</v>
@@ -9374,15 +9377,15 @@
         <v>28</v>
       </c>
       <c r="G4" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C5" s="4">
         <v>2355</v>
@@ -9397,15 +9400,15 @@
         <v>28</v>
       </c>
       <c r="G5" s="4">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C6" s="4">
         <v>573</v>
@@ -9425,10 +9428,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C7" s="4">
         <v>572</v>
@@ -9448,10 +9451,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C8" s="4">
         <v>4411</v>
@@ -9471,10 +9474,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C9" s="4">
         <v>4410</v>
@@ -9537,10 +9540,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C2" s="4">
         <v>4044</v>
@@ -9549,7 +9552,7 @@
         <v>500</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -9560,10 +9563,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C3" s="4">
         <v>4672</v>
@@ -9572,7 +9575,7 @@
         <v>500</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -9583,10 +9586,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C4" s="4">
         <v>4043</v>
@@ -9606,10 +9609,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C5" s="4">
         <v>3531</v>
@@ -9629,10 +9632,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C6" s="4">
         <v>3974</v>
@@ -9652,10 +9655,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C7" s="4">
         <v>3530</v>
@@ -9675,10 +9678,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C8" s="4">
         <v>4282</v>
@@ -9698,10 +9701,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C9" s="4">
         <v>3870</v>
@@ -9710,7 +9713,7 @@
         <v>500</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -9721,10 +9724,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C10" s="4">
         <v>3701</v>
@@ -9733,7 +9736,7 @@
         <v>500</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -9744,10 +9747,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C11" s="4">
         <v>3800</v>
@@ -9756,7 +9759,7 @@
         <v>500</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -9767,10 +9770,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C12" s="4">
         <v>3725</v>
@@ -9779,7 +9782,7 @@
         <v>500</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -9790,10 +9793,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C13" s="4">
         <v>3871</v>
@@ -9802,7 +9805,7 @@
         <v>500</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -9813,10 +9816,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C14" s="4">
         <v>2825</v>
@@ -9836,10 +9839,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C15" s="4">
         <v>2828</v>
@@ -9859,10 +9862,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C16" s="4">
         <v>2826</v>
@@ -9882,10 +9885,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C17" s="4">
         <v>3058</v>
@@ -9905,10 +9908,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C18" s="4">
         <v>3059</v>
@@ -9928,10 +9931,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C19" s="4">
         <v>2829</v>
@@ -9951,10 +9954,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C20" s="4">
         <v>4126</v>
@@ -9974,10 +9977,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C21" s="4">
         <v>2827</v>
@@ -9997,10 +10000,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C22" s="4">
         <v>3801</v>
@@ -10009,7 +10012,7 @@
         <v>500</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -10020,10 +10023,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C23" s="4">
         <v>3833</v>
@@ -10032,7 +10035,7 @@
         <v>500</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -10043,10 +10046,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C24" s="4">
         <v>3897</v>
@@ -10066,10 +10069,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C25" s="4">
         <v>3764</v>
@@ -10178,10 +10181,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C4" s="4">
         <v>3443</v>
@@ -10201,10 +10204,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C5" s="4">
         <v>3019</v>
@@ -10224,10 +10227,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C6" s="4">
         <v>4489</v>
@@ -10247,10 +10250,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C7" s="4">
         <v>4490</v>
@@ -10270,10 +10273,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C8" s="4">
         <v>3476</v>
@@ -10293,10 +10296,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C9" s="4">
         <v>3477</v>
@@ -10316,10 +10319,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C10" s="4">
         <v>4344</v>
@@ -10385,10 +10388,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C13" s="4">
         <v>3719</v>
@@ -10408,10 +10411,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C14" s="4">
         <v>3720</v>
@@ -10431,10 +10434,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C15" s="4">
         <v>3765</v>
@@ -10454,10 +10457,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C16" s="4">
         <v>3766</v>
@@ -10477,10 +10480,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C17" s="4">
         <v>3126</v>
@@ -10500,10 +10503,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C18" s="4">
         <v>3127</v>
@@ -10523,10 +10526,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C19" s="4">
         <v>3435</v>
@@ -10546,10 +10549,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C20" s="4">
         <v>3436</v>
@@ -10569,10 +10572,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C21" s="4">
         <v>3128</v>
@@ -10592,10 +10595,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C22" s="4">
         <v>3129</v>
@@ -10615,10 +10618,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C23" s="4">
         <v>4158</v>
@@ -10638,10 +10641,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C24" s="4">
         <v>4159</v>
@@ -10661,10 +10664,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C25" s="4">
         <v>4561</v>
@@ -10684,10 +10687,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C26" s="4">
         <v>4562</v>
@@ -10799,10 +10802,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C31" s="4">
         <v>4346</v>
@@ -10822,10 +10825,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C32" s="4">
         <v>4345</v>
@@ -10845,10 +10848,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C33" s="4">
         <v>4347</v>
@@ -10868,10 +10871,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C34" s="4">
         <v>4446</v>
@@ -10891,10 +10894,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C35" s="4">
         <v>4476</v>
@@ -10906,7 +10909,7 @@
         <v>9</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G35" s="4">
         <v>33.5</v>
@@ -10914,10 +10917,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C36" s="4">
         <v>4348</v>
@@ -10937,10 +10940,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C37" s="4">
         <v>4456</v>
@@ -10960,10 +10963,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C38" s="4">
         <v>4051</v>
@@ -10983,10 +10986,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C39" s="4">
         <v>4408</v>
@@ -11006,10 +11009,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C40" s="4">
         <v>4341</v>
@@ -11029,10 +11032,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C41" s="4">
         <v>4265</v>
@@ -11052,10 +11055,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C42" s="4">
         <v>4266</v>
@@ -11075,10 +11078,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C43" s="4">
         <v>4269</v>
@@ -11098,10 +11101,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C44" s="4">
         <v>4273</v>
@@ -11121,10 +11124,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C45" s="4">
         <v>4405</v>
@@ -11144,10 +11147,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C46" s="4">
         <v>4406</v>
@@ -11167,10 +11170,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C47" s="4">
         <v>4267</v>
@@ -11190,10 +11193,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C48" s="4">
         <v>4271</v>
@@ -11213,10 +11216,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C49" s="4">
         <v>4276</v>
@@ -11236,10 +11239,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C50" s="4">
         <v>4342</v>
@@ -11259,10 +11262,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C51" s="4">
         <v>2505</v>
@@ -11282,10 +11285,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C52" s="4">
         <v>4398</v>
@@ -11305,10 +11308,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C53" s="4">
         <v>4270</v>
@@ -11328,10 +11331,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C54" s="4">
         <v>4275</v>
@@ -11351,10 +11354,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C55" s="4">
         <v>4274</v>
@@ -11374,10 +11377,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C56" s="4">
         <v>4399</v>
@@ -11397,10 +11400,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C57" s="4">
         <v>4404</v>
@@ -11420,10 +11423,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C58" s="4">
         <v>4262</v>
@@ -11443,10 +11446,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C59" s="4">
         <v>4263</v>
@@ -11466,10 +11469,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C60" s="4">
         <v>4264</v>
@@ -11489,10 +11492,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C61" s="4">
         <v>4407</v>
@@ -11512,10 +11515,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C62" s="4">
         <v>4397</v>
@@ -11535,10 +11538,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C63" s="4">
         <v>4343</v>
@@ -11558,10 +11561,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C64" s="4">
         <v>4268</v>
@@ -11581,10 +11584,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C65" s="4">
         <v>2833</v>
@@ -11604,10 +11607,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C66" s="4">
         <v>3125</v>
@@ -11627,10 +11630,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C67" s="4">
         <v>3752</v>
@@ -11650,10 +11653,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C68" s="4">
         <v>3753</v>
@@ -11673,10 +11676,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C69" s="4">
         <v>2511</v>
@@ -11696,10 +11699,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C70" s="4">
         <v>4311</v>
@@ -11719,10 +11722,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C71" s="4">
         <v>4046</v>
@@ -11742,10 +11745,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C72" s="4">
         <v>4047</v>
@@ -11765,10 +11768,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C73" s="4">
         <v>4312</v>
@@ -11788,10 +11791,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C74" s="4">
         <v>4310</v>
@@ -11811,10 +11814,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C75" s="4">
         <v>4074</v>
@@ -11823,7 +11826,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -11834,10 +11837,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C76" s="4">
         <v>4076</v>
@@ -11846,10 +11849,10 @@
         <v>1</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G76" s="4">
         <v>32.5</v>
@@ -11857,10 +11860,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C77" s="4">
         <v>4133</v>
@@ -11872,7 +11875,7 @@
         <v>426</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G77" s="4">
         <v>72</v>
@@ -11880,10 +11883,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C78" s="4">
         <v>3068</v>
@@ -11903,10 +11906,10 @@
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C79" s="4">
         <v>3087</v>
@@ -11926,10 +11929,10 @@
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C80" s="4">
         <v>4560</v>
@@ -11949,10 +11952,10 @@
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C81" s="4">
         <v>4531</v>
@@ -11972,10 +11975,10 @@
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C82" s="4">
         <v>4532</v>
@@ -11995,10 +11998,10 @@
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C83" s="4">
         <v>4559</v>
@@ -12018,10 +12021,10 @@
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C84" s="4">
         <v>4493</v>
@@ -12041,10 +12044,10 @@
     </row>
     <row r="85" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C85" s="4">
         <v>4102</v>
@@ -12053,7 +12056,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -12064,10 +12067,10 @@
     </row>
     <row r="86" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C86" s="4">
         <v>4103</v>
@@ -12076,7 +12079,7 @@
         <v>10</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>273</v>
@@ -12087,10 +12090,10 @@
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C87" s="4">
         <v>4547</v>
@@ -12099,7 +12102,7 @@
         <v>10</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>273</v>
@@ -12110,10 +12113,10 @@
     </row>
     <row r="88" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C88" s="4">
         <v>4624</v>
@@ -12122,7 +12125,7 @@
         <v>21</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -12133,10 +12136,10 @@
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C89" s="4">
         <v>4627</v>
@@ -12145,7 +12148,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -12156,10 +12159,10 @@
     </row>
     <row r="90" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C90" s="4">
         <v>4628</v>
@@ -12168,7 +12171,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -12179,10 +12182,10 @@
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C91" s="4">
         <v>4625</v>
@@ -12191,7 +12194,7 @@
         <v>21</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -12202,10 +12205,10 @@
     </row>
     <row r="92" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C92" s="4">
         <v>4626</v>
@@ -12214,7 +12217,7 @@
         <v>21</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -12225,10 +12228,10 @@
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C93" s="4">
         <v>4699</v>
@@ -12237,7 +12240,7 @@
         <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>273</v>
@@ -12248,10 +12251,10 @@
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C94" s="4">
         <v>4643</v>
@@ -12260,10 +12263,10 @@
         <v>6</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G94" s="4">
         <v>97.5</v>
@@ -12271,10 +12274,10 @@
     </row>
     <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C95" s="4">
         <v>4687</v>
@@ -12283,10 +12286,10 @@
         <v>6</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G95" s="4">
         <v>64</v>
@@ -12294,10 +12297,10 @@
     </row>
     <row r="96" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C96" s="4">
         <v>4644</v>
@@ -12306,10 +12309,10 @@
         <v>6</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G96" s="4">
         <v>57</v>
@@ -12317,10 +12320,10 @@
     </row>
     <row r="97" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C97" s="4">
         <v>4104</v>
@@ -12329,7 +12332,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>273</v>
@@ -12340,10 +12343,10 @@
     </row>
     <row r="98" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C98" s="4">
         <v>4101</v>
@@ -12352,7 +12355,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>273</v>
@@ -12363,10 +12366,10 @@
     </row>
     <row r="99" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C99" s="4">
         <v>4105</v>
@@ -12375,7 +12378,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>273</v>
@@ -12386,10 +12389,10 @@
     </row>
     <row r="100" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C100" s="4">
         <v>3705</v>
@@ -12398,7 +12401,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>273</v>
@@ -12409,10 +12412,10 @@
     </row>
     <row r="101" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C101" s="4">
         <v>3823</v>
@@ -12421,7 +12424,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>28</v>
@@ -12432,10 +12435,10 @@
     </row>
     <row r="102" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C102" s="4">
         <v>4641</v>
@@ -12444,7 +12447,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -12455,10 +12458,10 @@
     </row>
     <row r="103" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C103" s="4">
         <v>4583</v>
@@ -12467,7 +12470,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>273</v>
@@ -12478,10 +12481,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C104" s="4">
         <v>4308</v>
@@ -12490,7 +12493,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -12501,10 +12504,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C105" s="4">
         <v>4309</v>
@@ -12513,10 +12516,10 @@
         <v>10</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G105" s="4">
         <v>68.5</v>
@@ -12524,10 +12527,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C106" s="4">
         <v>4635</v>
@@ -12539,7 +12542,7 @@
         <v>426</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G106" s="4">
         <v>177</v>
@@ -12547,10 +12550,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C107" s="4">
         <v>4412</v>
@@ -12562,7 +12565,7 @@
         <v>9</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G107" s="4">
         <v>75.5</v>
@@ -12570,10 +12573,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C108" s="4">
         <v>4413</v>
@@ -12593,10 +12596,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C109" s="4">
         <v>4414</v>
@@ -12616,10 +12619,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C110" s="4">
         <v>4415</v>
@@ -12639,10 +12642,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C111" s="4">
         <v>4416</v>
@@ -12662,10 +12665,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C112" s="4">
         <v>4475</v>
@@ -12674,7 +12677,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -12685,10 +12688,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C113" s="4">
         <v>4354</v>
@@ -12697,10 +12700,10 @@
         <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G113" s="4">
         <v>79.5</v>
@@ -12708,10 +12711,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C114" s="4">
         <v>4445</v>
@@ -12720,7 +12723,7 @@
         <v>12</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>28</v>
@@ -12731,10 +12734,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C115" s="4">
         <v>4353</v>
@@ -12743,7 +12746,7 @@
         <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>28</v>
@@ -12754,10 +12757,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C116" s="4">
         <v>4350</v>
@@ -12766,7 +12769,7 @@
         <v>12</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>28</v>
@@ -12777,10 +12780,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C117" s="4">
         <v>4352</v>
@@ -12789,7 +12792,7 @@
         <v>12</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>28</v>
@@ -12800,10 +12803,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C118" s="4">
         <v>4349</v>
@@ -12812,7 +12815,7 @@
         <v>12</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>28</v>
@@ -12823,10 +12826,10 @@
     </row>
     <row r="119" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C119" s="4">
         <v>4351</v>
@@ -12835,7 +12838,7 @@
         <v>12</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>28</v>
@@ -12846,10 +12849,10 @@
     </row>
     <row r="120" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C120" s="4">
         <v>4581</v>
@@ -12858,7 +12861,7 @@
         <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>28</v>
@@ -12869,10 +12872,10 @@
     </row>
     <row r="121" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C121" s="4">
         <v>4096</v>
@@ -12892,10 +12895,10 @@
     </row>
     <row r="122" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C122" s="4">
         <v>4582</v>
@@ -12904,7 +12907,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -12915,10 +12918,10 @@
     </row>
     <row r="123" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C123" s="4">
         <v>4123</v>
@@ -12927,7 +12930,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -12938,10 +12941,10 @@
     </row>
     <row r="124" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C124" s="4">
         <v>4306</v>
@@ -12950,10 +12953,10 @@
         <v>10</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G124" s="4">
         <v>81</v>
@@ -12961,10 +12964,10 @@
     </row>
     <row r="125" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C125" s="4">
         <v>4307</v>
@@ -12973,10 +12976,10 @@
         <v>10</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="G125" s="4">
         <v>81</v>
@@ -12984,10 +12987,10 @@
     </row>
     <row r="126" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C126" s="4">
         <v>2659</v>
@@ -12996,7 +12999,7 @@
         <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>273</v>
@@ -13007,10 +13010,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C127" s="4">
         <v>2621</v>
@@ -13019,7 +13022,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>273</v>
@@ -13030,10 +13033,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C128" s="4">
         <v>3656</v>
@@ -13042,7 +13045,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>273</v>
@@ -13096,10 +13099,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C2" s="4">
         <v>3459</v>
@@ -13108,7 +13111,7 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -13119,10 +13122,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C3" s="4">
         <v>3803</v>
@@ -13131,7 +13134,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -13142,10 +13145,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C4" s="4">
         <v>3425</v>
@@ -13154,10 +13157,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G4" s="4">
         <v>29</v>
@@ -13165,10 +13168,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C5" s="4">
         <v>3426</v>
@@ -13177,7 +13180,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>28</v>
@@ -13188,10 +13191,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C6" s="4">
         <v>3427</v>
@@ -13200,10 +13203,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G6" s="4">
         <v>62.5</v>
@@ -13211,10 +13214,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C7" s="4">
         <v>3428</v>
@@ -13223,7 +13226,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>28</v>
@@ -13234,10 +13237,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C8" s="4">
         <v>3429</v>
@@ -13246,10 +13249,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G8" s="4">
         <v>76.5</v>
@@ -13257,10 +13260,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C9" s="4">
         <v>3430</v>
@@ -13269,7 +13272,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>28</v>
@@ -13280,10 +13283,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C10" s="4">
         <v>3913</v>
@@ -13292,10 +13295,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G10" s="4">
         <v>68</v>
@@ -13303,10 +13306,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C11" s="4">
         <v>3872</v>
@@ -13315,7 +13318,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>28</v>
@@ -13326,10 +13329,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C12" s="4">
         <v>3422</v>
@@ -13338,10 +13341,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G12" s="4">
         <v>20</v>
@@ -13349,10 +13352,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C13" s="4">
         <v>3423</v>
@@ -13361,7 +13364,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>28</v>
@@ -13372,10 +13375,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C14" s="4">
         <v>3431</v>
@@ -13384,10 +13387,10 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G14" s="4">
         <v>115</v>
@@ -13395,10 +13398,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C15" s="4">
         <v>3432</v>
@@ -13407,7 +13410,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>28</v>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4792,7 +4792,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="4">
-        <v>450</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7868,7 +7868,7 @@
         <v>10</v>
       </c>
       <c r="G76" s="4">
-        <v>300</v>
+        <v>312.5</v>
       </c>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7891,7 +7891,7 @@
         <v>11</v>
       </c>
       <c r="G77" s="4">
-        <v>63</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21793,7 +21793,7 @@
         <v>10</v>
       </c>
       <c r="G88" s="4">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="1151">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2695,6 +2695,15 @@
   </si>
   <si>
     <t>BATATA FRITA SALSA MEXICANA</t>
+  </si>
+  <si>
+    <t>biscoito-polvilho</t>
+  </si>
+  <si>
+    <t>BISCOITO DE POLVILHO C/QUEIJO</t>
+  </si>
+  <si>
+    <t>X180G</t>
   </si>
   <si>
     <t>mix-batata-doce-chips</t>
@@ -9503,7 +9512,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -9768,7 +9777,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>887</v>
       </c>
@@ -9791,7 +9800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>889</v>
       </c>
@@ -9799,53 +9808,53 @@
         <v>890</v>
       </c>
       <c r="C13" s="4">
-        <v>3871</v>
+        <v>4244</v>
       </c>
       <c r="D13" s="4">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" s="4">
-        <v>27</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C14" s="4">
+        <v>3871</v>
+      </c>
+      <c r="D14" s="4">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="C15" s="4">
         <v>2825</v>
-      </c>
-      <c r="D14" s="4">
-        <v>2</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="4">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="C15" s="4">
-        <v>2828</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
@@ -9862,13 +9871,13 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C16" s="4">
-        <v>2826</v>
+        <v>2828</v>
       </c>
       <c r="D16" s="4">
         <v>2</v>
@@ -9885,13 +9894,13 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C17" s="4">
-        <v>3058</v>
+        <v>2826</v>
       </c>
       <c r="D17" s="4">
         <v>2</v>
@@ -9908,13 +9917,13 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C18" s="4">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D18" s="4">
         <v>2</v>
@@ -9931,13 +9940,13 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C19" s="4">
-        <v>2829</v>
+        <v>3059</v>
       </c>
       <c r="D19" s="4">
         <v>2</v>
@@ -9954,13 +9963,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C20" s="4">
-        <v>4126</v>
+        <v>2829</v>
       </c>
       <c r="D20" s="4">
         <v>2</v>
@@ -9977,13 +9986,13 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C21" s="4">
-        <v>2827</v>
+        <v>4126</v>
       </c>
       <c r="D21" s="4">
         <v>2</v>
@@ -10000,19 +10009,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C22" s="4">
-        <v>3801</v>
+        <v>2827</v>
       </c>
       <c r="D22" s="4">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>868</v>
+        <v>9</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -10023,13 +10032,13 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C23" s="4">
-        <v>3833</v>
+        <v>3801</v>
       </c>
       <c r="D23" s="4">
         <v>500</v>
@@ -10046,36 +10055,36 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C24" s="4">
-        <v>3897</v>
+        <v>3833</v>
       </c>
       <c r="D24" s="4">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>9</v>
+        <v>868</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G24" s="4">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C25" s="4">
-        <v>3764</v>
+        <v>3897</v>
       </c>
       <c r="D25" s="4">
         <v>2</v>
@@ -10084,9 +10093,32 @@
         <v>9</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G25" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3764</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="4">
         <v>81</v>
       </c>
     </row>
@@ -10181,10 +10213,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C4" s="4">
         <v>3443</v>
@@ -10204,10 +10236,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C5" s="4">
         <v>3019</v>
@@ -10227,10 +10259,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C6" s="4">
         <v>4489</v>
@@ -10250,10 +10282,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C7" s="4">
         <v>4490</v>
@@ -10273,10 +10305,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C8" s="4">
         <v>3476</v>
@@ -10296,10 +10328,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C9" s="4">
         <v>3477</v>
@@ -10319,10 +10351,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C10" s="4">
         <v>4344</v>
@@ -10388,10 +10420,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C13" s="4">
         <v>3719</v>
@@ -10411,10 +10443,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C14" s="4">
         <v>3720</v>
@@ -10434,10 +10466,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C15" s="4">
         <v>3765</v>
@@ -10457,10 +10489,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C16" s="4">
         <v>3766</v>
@@ -10480,10 +10512,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C17" s="4">
         <v>3126</v>
@@ -10503,10 +10535,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C18" s="4">
         <v>3127</v>
@@ -10526,10 +10558,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C19" s="4">
         <v>3435</v>
@@ -10549,10 +10581,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C20" s="4">
         <v>3436</v>
@@ -10572,10 +10604,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C21" s="4">
         <v>3128</v>
@@ -10595,10 +10627,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C22" s="4">
         <v>3129</v>
@@ -10618,10 +10650,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C23" s="4">
         <v>4158</v>
@@ -10641,10 +10673,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C24" s="4">
         <v>4159</v>
@@ -10664,10 +10696,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C25" s="4">
         <v>4561</v>
@@ -10687,10 +10719,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C26" s="4">
         <v>4562</v>
@@ -10802,10 +10834,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C31" s="4">
         <v>4346</v>
@@ -10825,10 +10857,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C32" s="4">
         <v>4345</v>
@@ -10848,10 +10880,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C33" s="4">
         <v>4347</v>
@@ -10871,10 +10903,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C34" s="4">
         <v>4446</v>
@@ -10894,10 +10926,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="C35" s="4">
         <v>4476</v>
@@ -10917,10 +10949,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C36" s="4">
         <v>4348</v>
@@ -10940,10 +10972,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="C37" s="4">
         <v>4456</v>
@@ -10963,10 +10995,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="C38" s="4">
         <v>4051</v>
@@ -10986,10 +11018,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C39" s="4">
         <v>4408</v>
@@ -11009,10 +11041,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C40" s="4">
         <v>4341</v>
@@ -11032,10 +11064,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="C41" s="4">
         <v>4265</v>
@@ -11055,10 +11087,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C42" s="4">
         <v>4266</v>
@@ -11078,10 +11110,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C43" s="4">
         <v>4269</v>
@@ -11101,10 +11133,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="C44" s="4">
         <v>4273</v>
@@ -11124,10 +11156,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C45" s="4">
         <v>4405</v>
@@ -11147,10 +11179,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="C46" s="4">
         <v>4406</v>
@@ -11170,10 +11202,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C47" s="4">
         <v>4267</v>
@@ -11193,10 +11225,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C48" s="4">
         <v>4271</v>
@@ -11216,10 +11248,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C49" s="4">
         <v>4276</v>
@@ -11239,10 +11271,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="C50" s="4">
         <v>4342</v>
@@ -11262,10 +11294,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C51" s="4">
         <v>2505</v>
@@ -11285,10 +11317,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C52" s="4">
         <v>4398</v>
@@ -11308,10 +11340,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C53" s="4">
         <v>4270</v>
@@ -11331,10 +11363,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C54" s="4">
         <v>4275</v>
@@ -11354,10 +11386,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C55" s="4">
         <v>4274</v>
@@ -11377,10 +11409,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C56" s="4">
         <v>4399</v>
@@ -11400,10 +11432,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C57" s="4">
         <v>4404</v>
@@ -11423,10 +11455,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C58" s="4">
         <v>4262</v>
@@ -11446,10 +11478,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C59" s="4">
         <v>4263</v>
@@ -11469,10 +11501,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C60" s="4">
         <v>4264</v>
@@ -11492,10 +11524,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="C61" s="4">
         <v>4407</v>
@@ -11515,10 +11547,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C62" s="4">
         <v>4397</v>
@@ -11538,10 +11570,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C63" s="4">
         <v>4343</v>
@@ -11561,10 +11593,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C64" s="4">
         <v>4268</v>
@@ -11584,10 +11616,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C65" s="4">
         <v>2833</v>
@@ -11607,10 +11639,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C66" s="4">
         <v>3125</v>
@@ -11630,10 +11662,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C67" s="4">
         <v>3752</v>
@@ -11653,10 +11685,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C68" s="4">
         <v>3753</v>
@@ -11676,10 +11708,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C69" s="4">
         <v>2511</v>
@@ -11699,10 +11731,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C70" s="4">
         <v>4311</v>
@@ -11722,10 +11754,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C71" s="4">
         <v>4046</v>
@@ -11745,10 +11777,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C72" s="4">
         <v>4047</v>
@@ -11768,10 +11800,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C73" s="4">
         <v>4312</v>
@@ -11791,10 +11823,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C74" s="4">
         <v>4310</v>
@@ -11814,10 +11846,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C75" s="4">
         <v>4074</v>
@@ -11826,7 +11858,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -11837,10 +11869,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C76" s="4">
         <v>4076</v>
@@ -11849,10 +11881,10 @@
         <v>1</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G76" s="4">
         <v>32.5</v>
@@ -11860,10 +11892,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C77" s="4">
         <v>4133</v>
@@ -11875,7 +11907,7 @@
         <v>426</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G77" s="4">
         <v>72</v>
@@ -11883,10 +11915,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C78" s="4">
         <v>3068</v>
@@ -11906,10 +11938,10 @@
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C79" s="4">
         <v>3087</v>
@@ -11929,10 +11961,10 @@
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="C80" s="4">
         <v>4560</v>
@@ -11952,10 +11984,10 @@
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C81" s="4">
         <v>4531</v>
@@ -11975,10 +12007,10 @@
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C82" s="4">
         <v>4532</v>
@@ -11998,10 +12030,10 @@
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C83" s="4">
         <v>4559</v>
@@ -12021,10 +12053,10 @@
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="C84" s="4">
         <v>4493</v>
@@ -12044,10 +12076,10 @@
     </row>
     <row r="85" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C85" s="4">
         <v>4102</v>
@@ -12056,7 +12088,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -12067,10 +12099,10 @@
     </row>
     <row r="86" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C86" s="4">
         <v>4103</v>
@@ -12079,7 +12111,7 @@
         <v>10</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>273</v>
@@ -12090,10 +12122,10 @@
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="C87" s="4">
         <v>4547</v>
@@ -12102,7 +12134,7 @@
         <v>10</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>273</v>
@@ -12113,10 +12145,10 @@
     </row>
     <row r="88" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="C88" s="4">
         <v>4624</v>
@@ -12125,7 +12157,7 @@
         <v>21</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -12136,10 +12168,10 @@
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C89" s="4">
         <v>4627</v>
@@ -12148,7 +12180,7 @@
         <v>25</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -12159,10 +12191,10 @@
     </row>
     <row r="90" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="C90" s="4">
         <v>4628</v>
@@ -12171,7 +12203,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -12182,10 +12214,10 @@
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="C91" s="4">
         <v>4625</v>
@@ -12194,7 +12226,7 @@
         <v>21</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -12205,10 +12237,10 @@
     </row>
     <row r="92" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C92" s="4">
         <v>4626</v>
@@ -12217,7 +12249,7 @@
         <v>21</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -12228,10 +12260,10 @@
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="C93" s="4">
         <v>4699</v>
@@ -12240,7 +12272,7 @@
         <v>50</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>273</v>
@@ -12251,10 +12283,10 @@
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="C94" s="4">
         <v>4643</v>
@@ -12263,10 +12295,10 @@
         <v>6</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="G94" s="4">
         <v>97.5</v>
@@ -12274,10 +12306,10 @@
     </row>
     <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="C95" s="4">
         <v>4687</v>
@@ -12286,10 +12318,10 @@
         <v>6</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G95" s="4">
         <v>64</v>
@@ -12297,10 +12329,10 @@
     </row>
     <row r="96" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="C96" s="4">
         <v>4644</v>
@@ -12309,10 +12341,10 @@
         <v>6</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G96" s="4">
         <v>57</v>
@@ -12320,10 +12352,10 @@
     </row>
     <row r="97" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C97" s="4">
         <v>4104</v>
@@ -12332,7 +12364,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>273</v>
@@ -12343,10 +12375,10 @@
     </row>
     <row r="98" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="C98" s="4">
         <v>4101</v>
@@ -12355,7 +12387,7 @@
         <v>10</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>273</v>
@@ -12366,10 +12398,10 @@
     </row>
     <row r="99" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="C99" s="4">
         <v>4105</v>
@@ -12378,7 +12410,7 @@
         <v>10</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>273</v>
@@ -12389,10 +12421,10 @@
     </row>
     <row r="100" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="C100" s="4">
         <v>3705</v>
@@ -12401,7 +12433,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>273</v>
@@ -12412,10 +12444,10 @@
     </row>
     <row r="101" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="C101" s="4">
         <v>3823</v>
@@ -12424,7 +12456,7 @@
         <v>10</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>28</v>
@@ -12435,10 +12467,10 @@
     </row>
     <row r="102" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C102" s="4">
         <v>4641</v>
@@ -12447,7 +12479,7 @@
         <v>6</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -12458,10 +12490,10 @@
     </row>
     <row r="103" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="C103" s="4">
         <v>4583</v>
@@ -12470,7 +12502,7 @@
         <v>12</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>273</v>
@@ -12481,10 +12513,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C104" s="4">
         <v>4308</v>
@@ -12493,7 +12525,7 @@
         <v>10</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -12504,10 +12536,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C105" s="4">
         <v>4309</v>
@@ -12516,10 +12548,10 @@
         <v>10</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G105" s="4">
         <v>68.5</v>
@@ -12527,10 +12559,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C106" s="4">
         <v>4635</v>
@@ -12542,7 +12574,7 @@
         <v>426</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G106" s="4">
         <v>177</v>
@@ -12550,10 +12582,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C107" s="4">
         <v>4412</v>
@@ -12565,7 +12597,7 @@
         <v>9</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G107" s="4">
         <v>75.5</v>
@@ -12573,10 +12605,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C108" s="4">
         <v>4413</v>
@@ -12596,10 +12628,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C109" s="4">
         <v>4414</v>
@@ -12619,10 +12651,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C110" s="4">
         <v>4415</v>
@@ -12642,10 +12674,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C111" s="4">
         <v>4416</v>
@@ -12665,10 +12697,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="C112" s="4">
         <v>4475</v>
@@ -12677,7 +12709,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -12688,10 +12720,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="C113" s="4">
         <v>4354</v>
@@ -12700,7 +12732,7 @@
         <v>12</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>786</v>
@@ -12711,10 +12743,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="C114" s="4">
         <v>4445</v>
@@ -12723,7 +12755,7 @@
         <v>12</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>28</v>
@@ -12734,10 +12766,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="C115" s="4">
         <v>4353</v>
@@ -12746,7 +12778,7 @@
         <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>28</v>
@@ -12757,10 +12789,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="C116" s="4">
         <v>4350</v>
@@ -12769,7 +12801,7 @@
         <v>12</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>28</v>
@@ -12780,10 +12812,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C117" s="4">
         <v>4352</v>
@@ -12792,7 +12824,7 @@
         <v>12</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>28</v>
@@ -12803,10 +12835,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="C118" s="4">
         <v>4349</v>
@@ -12815,7 +12847,7 @@
         <v>12</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>28</v>
@@ -12826,10 +12858,10 @@
     </row>
     <row r="119" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="C119" s="4">
         <v>4351</v>
@@ -12838,7 +12870,7 @@
         <v>12</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>28</v>
@@ -12849,10 +12881,10 @@
     </row>
     <row r="120" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C120" s="4">
         <v>4581</v>
@@ -12861,7 +12893,7 @@
         <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>28</v>
@@ -12872,10 +12904,10 @@
     </row>
     <row r="121" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="C121" s="4">
         <v>4096</v>
@@ -12895,10 +12927,10 @@
     </row>
     <row r="122" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C122" s="4">
         <v>4582</v>
@@ -12907,7 +12939,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -12918,10 +12950,10 @@
     </row>
     <row r="123" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="C123" s="4">
         <v>4123</v>
@@ -12930,7 +12962,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -12941,10 +12973,10 @@
     </row>
     <row r="124" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C124" s="4">
         <v>4306</v>
@@ -12953,10 +12985,10 @@
         <v>10</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G124" s="4">
         <v>81</v>
@@ -12964,10 +12996,10 @@
     </row>
     <row r="125" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C125" s="4">
         <v>4307</v>
@@ -12976,10 +13008,10 @@
         <v>10</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="G125" s="4">
         <v>81</v>
@@ -12987,10 +13019,10 @@
     </row>
     <row r="126" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C126" s="4">
         <v>2659</v>
@@ -12999,7 +13031,7 @@
         <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>273</v>
@@ -13010,10 +13042,10 @@
     </row>
     <row r="127" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C127" s="4">
         <v>2621</v>
@@ -13022,7 +13054,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>273</v>
@@ -13033,10 +13065,10 @@
     </row>
     <row r="128" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="C128" s="4">
         <v>3656</v>
@@ -13045,7 +13077,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>273</v>
@@ -13099,10 +13131,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="C2" s="4">
         <v>3459</v>
@@ -13122,10 +13154,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="C3" s="4">
         <v>3803</v>
@@ -13145,10 +13177,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="C4" s="4">
         <v>3425</v>
@@ -13168,10 +13200,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="C5" s="4">
         <v>3426</v>
@@ -13191,10 +13223,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C6" s="4">
         <v>3427</v>
@@ -13214,10 +13246,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="C7" s="4">
         <v>3428</v>
@@ -13237,10 +13269,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="C8" s="4">
         <v>3429</v>
@@ -13260,10 +13292,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="C9" s="4">
         <v>3430</v>
@@ -13283,10 +13315,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C10" s="4">
         <v>3913</v>
@@ -13306,10 +13338,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="C11" s="4">
         <v>3872</v>
@@ -13329,10 +13361,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="C12" s="4">
         <v>3422</v>
@@ -13352,10 +13384,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="C13" s="4">
         <v>3423</v>
@@ -13364,7 +13396,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>28</v>
@@ -13375,10 +13407,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="C14" s="4">
         <v>3431</v>
@@ -13398,10 +13430,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="C15" s="4">
         <v>3432</v>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -4801,7 +4801,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="4">
-        <v>415</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7647,7 +7647,7 @@
         <v>273</v>
       </c>
       <c r="G66" s="4">
-        <v>472.5</v>
+        <v>405</v>
       </c>
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7670,7 +7670,7 @@
         <v>28</v>
       </c>
       <c r="G67" s="4">
-        <v>159.5</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7969,7 +7969,7 @@
         <v>10</v>
       </c>
       <c r="G80" s="4">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7992,7 +7992,7 @@
         <v>11</v>
       </c>
       <c r="G81" s="4">
-        <v>127</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8061,7 +8061,7 @@
         <v>11</v>
       </c>
       <c r="G84" s="4">
-        <v>240</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8084,7 +8084,7 @@
         <v>11</v>
       </c>
       <c r="G85" s="4">
-        <v>240</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="1151">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -129,6 +129,9 @@
     <t>SEMENTE DE ABOBORA</t>
   </si>
   <si>
+    <t>323.50</t>
+  </si>
+  <si>
     <t>semente-de-chia</t>
   </si>
   <si>
@@ -2065,9 +2068,6 @@
   </si>
   <si>
     <t>QUINOA EM GRÃOS</t>
-  </si>
-  <si>
-    <t>323.50</t>
   </si>
   <si>
     <t>semente-de-sucupira</t>
@@ -4004,7 +4004,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="4">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4303,7 +4303,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="4">
-        <v>1850</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4325,16 +4325,16 @@
       <c r="F18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="4">
-        <v>373.5</v>
+      <c r="G18" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4">
         <v>571</v>
@@ -4354,10 +4354,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="4">
         <v>2245</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="4">
         <v>2259</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="4">
         <v>2422</v>
@@ -4423,10 +4423,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4">
         <v>569</v>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" s="4">
         <v>282</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4">
         <v>3123</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4">
         <v>2674</v>
@@ -4515,10 +4515,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="4">
         <v>3124</v>
@@ -4538,10 +4538,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" s="4">
         <v>2824</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4">
         <v>3130</v>
@@ -4584,10 +4584,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4">
         <v>3131</v>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" s="4">
         <v>3438</v>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C32" s="4">
         <v>3434</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C2" s="4">
         <v>3051</v>
@@ -4737,10 +4737,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C3" s="4">
         <v>2675</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C4" s="4">
         <v>2791</v>
@@ -4783,10 +4783,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C5" s="4">
         <v>3090</v>
@@ -4806,10 +4806,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C6" s="4">
         <v>2414</v>
@@ -4829,10 +4829,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C7" s="4">
         <v>2418</v>
@@ -4852,10 +4852,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C8" s="4">
         <v>2272</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C9" s="4">
         <v>3651</v>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C10" s="4">
         <v>4206</v>
@@ -4921,10 +4921,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C11" s="4">
         <v>3652</v>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C12" s="4">
         <v>4136</v>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C13" s="4">
         <v>4585</v>
@@ -4979,7 +4979,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>28</v>
@@ -4990,10 +4990,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C14" s="4">
         <v>4584</v>
@@ -5013,10 +5013,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C15" s="4">
         <v>2756</v>
@@ -5025,7 +5025,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -5036,10 +5036,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C16" s="4">
         <v>2757</v>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C17" s="4">
         <v>4491</v>
@@ -5071,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>28</v>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C18" s="4">
         <v>4492</v>
@@ -5100,15 +5100,15 @@
         <v>11</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C19" s="4">
         <v>4700</v>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C21" s="4">
         <v>4674</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C22" s="4">
         <v>2362</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C23" s="4">
         <v>4403</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C24" s="4">
         <v>3111</v>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C25" s="4">
         <v>2406</v>
@@ -5295,7 +5295,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5332,10 +5332,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C2" s="4">
         <v>189</v>
@@ -5355,10 +5355,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C3" s="4">
         <v>9</v>
@@ -5378,10 +5378,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C4" s="4">
         <v>2553</v>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C5" s="4">
         <v>521</v>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C6" s="4">
         <v>99</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C7" s="4">
         <v>2613</v>
@@ -5470,10 +5470,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C8" s="4">
         <v>3365</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C9" s="4">
         <v>2556</v>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C10" s="4">
         <v>2555</v>
@@ -5539,10 +5539,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C11" s="4">
         <v>4045</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C12" s="4">
         <v>3669</v>
@@ -5585,154 +5585,154 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C13" s="4">
         <v>38</v>
       </c>
       <c r="D13" s="4">
+        <v>22.68</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C14" s="4">
+        <v>3473</v>
+      </c>
+      <c r="D14" s="4">
         <v>20</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="4">
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4">
         <v>136.5</v>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2479</v>
-      </c>
-      <c r="D14" s="4">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="4">
-        <v>22</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>665</v>
-      </c>
       <c r="C15" s="4">
-        <v>105</v>
+        <v>2479</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="4">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C16" s="4">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="D16" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" s="4">
-        <v>201</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>667</v>
-      </c>
       <c r="C17" s="4">
-        <v>2848</v>
+        <v>212</v>
       </c>
       <c r="D17" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="4">
-        <v>615</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C18" s="4">
-        <v>2851</v>
+        <v>2848</v>
       </c>
       <c r="D18" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="4">
-        <v>125</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>669</v>
-      </c>
       <c r="C19" s="4">
-        <v>4202</v>
+        <v>2851</v>
       </c>
       <c r="D19" s="4">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>9</v>
@@ -5741,113 +5741,113 @@
         <v>11</v>
       </c>
       <c r="G19" s="4">
-        <v>147.5</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C20" s="4">
-        <v>4201</v>
+        <v>4202</v>
       </c>
       <c r="D20" s="4">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>637</v>
+        <v>9</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G20" s="4">
-        <v>295</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>671</v>
-      </c>
       <c r="C21" s="4">
-        <v>653</v>
+        <v>4201</v>
       </c>
       <c r="D21" s="4">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>9</v>
+        <v>638</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G21" s="4">
-        <v>122.5</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C22" s="4">
-        <v>2484</v>
+        <v>653</v>
       </c>
       <c r="D22" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>672</v>
+        <v>10</v>
+      </c>
+      <c r="G22" s="4">
+        <v>122.5</v>
       </c>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2484</v>
+      </c>
+      <c r="D23" s="4">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>673</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="C23" s="4">
-        <v>3417</v>
-      </c>
-      <c r="D23" s="4">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="4">
-        <v>320</v>
       </c>
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C24" s="4">
-        <v>2716</v>
+        <v>3417</v>
       </c>
       <c r="D24" s="4">
-        <v>22.68</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>9</v>
@@ -5856,67 +5856,67 @@
         <v>10</v>
       </c>
       <c r="G24" s="4">
-        <v>290.5</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C25" s="4">
-        <v>2478</v>
+        <v>2716</v>
       </c>
       <c r="D25" s="4">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" s="4">
-        <v>82</v>
+        <v>290.5</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>676</v>
-      </c>
       <c r="C26" s="4">
-        <v>2606</v>
+        <v>2478</v>
       </c>
       <c r="D26" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="4">
-        <v>450</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C27" s="4">
-        <v>2338</v>
+        <v>2606</v>
       </c>
       <c r="D27" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>9</v>
@@ -5925,67 +5925,67 @@
         <v>10</v>
       </c>
       <c r="G27" s="4">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C28" s="4">
-        <v>2425</v>
+        <v>2338</v>
       </c>
       <c r="D28" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="4">
-        <v>91</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>678</v>
-      </c>
       <c r="C29" s="4">
-        <v>2579</v>
+        <v>2425</v>
       </c>
       <c r="D29" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" s="4">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C30" s="4">
-        <v>2243</v>
+        <v>2579</v>
       </c>
       <c r="D30" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>9</v>
@@ -5994,18 +5994,18 @@
         <v>10</v>
       </c>
       <c r="G30" s="4">
-        <v>425</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>31</v>
+        <v>678</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>679</v>
       </c>
       <c r="C31" s="4">
-        <v>4400</v>
+        <v>2243</v>
       </c>
       <c r="D31" s="4">
         <v>25</v>
@@ -6017,7 +6017,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="4">
-        <v>1600</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6028,10 +6028,10 @@
         <v>32</v>
       </c>
       <c r="C32" s="4">
-        <v>2676</v>
+        <v>4400</v>
       </c>
       <c r="D32" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>9</v>
@@ -6039,76 +6039,99 @@
       <c r="F32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>679</v>
+      <c r="G32" s="4">
+        <v>1600</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="4">
+        <v>2676</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="4">
-        <v>571</v>
-      </c>
-      <c r="D33" s="4">
-        <v>25</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="4">
-        <v>275</v>
       </c>
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C34" s="4">
-        <v>2245</v>
+        <v>571</v>
       </c>
       <c r="D34" s="4">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G34" s="4">
-        <v>58</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="4">
+        <v>2245</v>
+      </c>
+      <c r="D35" s="4">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C36" s="4">
         <v>3754</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D36" s="4">
         <v>3</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="4">
+      <c r="E36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="4">
         <v>450</v>
       </c>
     </row>
@@ -6238,10 +6261,10 @@
         <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G5" s="4">
         <v>77.5</v>
@@ -6284,10 +6307,10 @@
         <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" s="4">
         <v>180</v>
@@ -6307,10 +6330,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G8" s="4">
         <v>62</v>
@@ -6330,10 +6353,10 @@
         <v>20</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G9" s="4">
         <v>69.5</v>
@@ -6356,7 +6379,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G10" s="4">
         <v>153.5</v>
@@ -6379,7 +6402,7 @@
         <v>9</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G11" s="4">
         <v>298.5</v>
@@ -6387,10 +6410,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4">
         <v>2259</v>
@@ -6456,10 +6479,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4">
         <v>2422</v>
@@ -6479,10 +6502,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4">
         <v>569</v>
@@ -6502,10 +6525,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4">
         <v>282</v>
@@ -6704,7 +6727,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="4">
-        <v>700</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6750,7 +6773,7 @@
         <v>11</v>
       </c>
       <c r="G27" s="4">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -6796,7 +6819,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="4">
-        <v>595</v>
+        <v>627.5</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7003,7 +7026,7 @@
         <v>11</v>
       </c>
       <c r="G38" s="4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7037,7 +7060,7 @@
         <v>721</v>
       </c>
       <c r="C40" s="4">
-        <v>4474</v>
+        <v>4473</v>
       </c>
       <c r="D40" s="4">
         <v>3</v>
@@ -7060,7 +7083,7 @@
         <v>723</v>
       </c>
       <c r="C41" s="4">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="D41" s="4">
         <v>3</v>
@@ -7123,10 +7146,10 @@
     </row>
     <row r="44" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C44" s="4">
         <v>4640</v>
@@ -7135,7 +7158,7 @@
         <v>6</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -7158,7 +7181,7 @@
         <v>12</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>28</v>
@@ -7319,10 +7342,10 @@
         <v>10</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G52" s="4">
         <v>240</v>
@@ -7345,7 +7368,7 @@
         <v>9</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G53" s="4">
         <v>112</v>
@@ -7368,7 +7391,7 @@
         <v>9</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G54" s="4">
         <v>224</v>
@@ -7388,10 +7411,10 @@
         <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G55" s="4">
         <v>230</v>
@@ -7411,10 +7434,10 @@
         <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G56" s="4">
         <v>224</v>
@@ -7434,7 +7457,7 @@
         <v>12</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>28</v>
@@ -7457,10 +7480,10 @@
         <v>10</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G58" s="4">
         <v>240</v>
@@ -7480,7 +7503,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>28</v>
@@ -7549,10 +7572,10 @@
         <v>10</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G62" s="4">
         <v>240</v>
@@ -7595,7 +7618,7 @@
         <v>12</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>28</v>
@@ -7644,7 +7667,7 @@
         <v>9</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G66" s="4">
         <v>405</v>
@@ -8262,7 +8285,7 @@
         <v>12</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>28</v>
@@ -8285,7 +8308,7 @@
         <v>8</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>28</v>
@@ -8308,7 +8331,7 @@
         <v>8</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>28</v>
@@ -8702,7 +8725,7 @@
         <v>823</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G112" s="4">
         <v>53</v>
@@ -8725,7 +8748,7 @@
         <v>824</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G113" s="4">
         <v>81.5</v>
@@ -8748,7 +8771,7 @@
         <v>825</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G114" s="4">
         <v>70</v>
@@ -8771,7 +8794,7 @@
         <v>828</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G115" s="4">
         <v>150</v>
@@ -8791,7 +8814,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>28</v>
@@ -8883,7 +8906,7 @@
         <v>836</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G2" s="4">
         <v>46.5</v>
@@ -8906,7 +8929,7 @@
         <v>837</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G3" s="4">
         <v>66.5</v>
@@ -8929,7 +8952,7 @@
         <v>838</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G4" s="4">
         <v>38.5</v>
@@ -8952,7 +8975,7 @@
         <v>841</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G5" s="4">
         <v>57.5</v>
@@ -8975,7 +8998,7 @@
         <v>841</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G6" s="4">
         <v>57.5</v>
@@ -8998,7 +9021,7 @@
         <v>846</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" s="4">
         <v>58</v>
@@ -9021,7 +9044,7 @@
         <v>836</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G8" s="4">
         <v>86</v>
@@ -9044,7 +9067,7 @@
         <v>851</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G9" s="4">
         <v>26.5</v>
@@ -9067,7 +9090,7 @@
         <v>841</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G10" s="4">
         <v>53</v>
@@ -9124,7 +9147,7 @@
         <v>855</v>
       </c>
       <c r="C2" s="4">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="D2" s="4">
         <v>12</v>
@@ -9133,7 +9156,7 @@
         <v>836</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G2" s="4">
         <v>171.5</v>
@@ -9156,7 +9179,7 @@
         <v>806</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G3" s="4">
         <v>86.5</v>
@@ -9179,7 +9202,7 @@
         <v>838</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G4" s="4">
         <v>89</v>
@@ -9202,7 +9225,7 @@
         <v>856</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G5" s="4">
         <v>171.5</v>
@@ -9248,7 +9271,7 @@
         <v>838</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" s="4">
         <v>33</v>
@@ -9271,7 +9294,7 @@
         <v>859</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G8" s="4">
         <v>35.5</v>
@@ -9334,10 +9357,10 @@
         <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G2" s="4">
         <v>56</v>
@@ -9357,10 +9380,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G3" s="4">
         <v>57</v>
@@ -9380,7 +9403,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>28</v>
@@ -9403,7 +9426,7 @@
         <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>28</v>
@@ -9426,10 +9449,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G6" s="4">
         <v>59</v>
@@ -9449,10 +9472,10 @@
         <v>20</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G7" s="4">
         <v>60</v>
@@ -9472,7 +9495,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>28</v>
@@ -9495,7 +9518,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>28</v>
@@ -10167,10 +10190,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="4">
         <v>3438</v>
@@ -10190,10 +10213,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4">
         <v>3434</v>
@@ -10363,7 +10386,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>28</v>
@@ -10374,10 +10397,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4">
         <v>3123</v>
@@ -10397,10 +10420,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4">
         <v>2674</v>
@@ -10596,7 +10619,7 @@
         <v>9</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G20" s="4">
         <v>60.5</v>
@@ -10742,10 +10765,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="4">
         <v>3124</v>
@@ -10765,10 +10788,10 @@
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C28" s="4">
         <v>2824</v>
@@ -10788,10 +10811,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29" s="4">
         <v>3130</v>
@@ -10811,10 +10834,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="4">
         <v>3131</v>
@@ -10846,7 +10869,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>28</v>
@@ -10869,7 +10892,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>28</v>
@@ -10892,7 +10915,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>28</v>
@@ -10915,7 +10938,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>28</v>
@@ -10961,7 +10984,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>28</v>
@@ -10984,10 +11007,10 @@
         <v>10</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G37" s="4">
         <v>69</v>
@@ -11904,7 +11927,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>1028</v>
@@ -11996,7 +12019,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>10</v>
@@ -12042,7 +12065,7 @@
         <v>12</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>11</v>
@@ -12114,7 +12137,7 @@
         <v>1043</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G86" s="4">
         <v>77</v>
@@ -12137,7 +12160,7 @@
         <v>1043</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G87" s="4">
         <v>77</v>
@@ -12200,7 +12223,7 @@
         <v>4628</v>
       </c>
       <c r="D90" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>1056</v>
@@ -12209,7 +12232,7 @@
         <v>11</v>
       </c>
       <c r="G90" s="4">
-        <v>28</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -12275,7 +12298,7 @@
         <v>1063</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G93" s="4">
         <v>30</v>
@@ -12367,7 +12390,7 @@
         <v>1043</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G97" s="4">
         <v>77</v>
@@ -12390,7 +12413,7 @@
         <v>1043</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G98" s="4">
         <v>77</v>
@@ -12413,7 +12436,7 @@
         <v>1043</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G99" s="4">
         <v>77</v>
@@ -12436,7 +12459,7 @@
         <v>1079</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G100" s="4">
         <v>123.5</v>
@@ -12505,7 +12528,7 @@
         <v>1043</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G103" s="4">
         <v>144</v>
@@ -12571,7 +12594,7 @@
         <v>10</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>1028</v>
@@ -13034,7 +13057,7 @@
         <v>1130</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G126" s="4">
         <v>30</v>
@@ -13057,7 +13080,7 @@
         <v>1131</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G127" s="4">
         <v>25.5</v>
@@ -13080,7 +13103,7 @@
         <v>1043</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G128" s="4">
         <v>27</v>
@@ -13310,7 +13333,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="4">
-        <v>714.5</v>
+        <v>714</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -13496,10 +13519,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="4">
         <v>585</v>
@@ -13519,10 +13542,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="4">
         <v>467</v>
@@ -13542,10 +13565,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="4">
         <v>4685</v>
@@ -13565,10 +13588,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4">
         <v>4686</v>
@@ -13588,10 +13611,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="4">
         <v>3391</v>
@@ -13611,10 +13634,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4">
         <v>3399</v>
@@ -13634,10 +13657,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4">
         <v>2405</v>
@@ -13657,10 +13680,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4">
         <v>3655</v>
@@ -13680,10 +13703,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4">
         <v>2444</v>
@@ -13703,10 +13726,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4">
         <v>3390</v>
@@ -13726,10 +13749,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4">
         <v>3404</v>
@@ -13749,10 +13772,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="4">
         <v>3105</v>
@@ -13772,10 +13795,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="4">
         <v>2445</v>
@@ -13795,10 +13818,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="4">
         <v>2446</v>
@@ -13818,10 +13841,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="4">
         <v>2781</v>
@@ -13841,10 +13864,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" s="4">
         <v>3463</v>
@@ -13864,10 +13887,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="4">
         <v>4259</v>
@@ -13887,10 +13910,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="4">
         <v>3367</v>
@@ -13910,10 +13933,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4">
         <v>3464</v>
@@ -13933,10 +13956,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="4">
         <v>4256</v>
@@ -13956,10 +13979,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" s="4">
         <v>3368</v>
@@ -13979,10 +14002,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="4">
         <v>3465</v>
@@ -14002,10 +14025,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="4">
         <v>3372</v>
@@ -14025,10 +14048,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="4">
         <v>3466</v>
@@ -14048,10 +14071,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="4">
         <v>3380</v>
@@ -14117,10 +14140,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="4">
         <v>465</v>
@@ -14140,10 +14163,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="4">
         <v>2643</v>
@@ -14163,10 +14186,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" s="4">
         <v>2644</v>
@@ -14186,10 +14209,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C32" s="4">
         <v>2570</v>
@@ -14209,10 +14232,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="4">
         <v>3021</v>
@@ -14278,10 +14301,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="4">
         <v>3505</v>
@@ -14301,10 +14324,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="4">
         <v>2443</v>
@@ -14324,10 +14347,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38" s="4">
         <v>2283</v>
@@ -14347,10 +14370,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39" s="4">
         <v>4255</v>
@@ -14370,10 +14393,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="4">
         <v>103</v>
@@ -14393,10 +14416,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" s="4">
         <v>2629</v>
@@ -14416,10 +14439,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" s="4">
         <v>2452</v>
@@ -14439,10 +14462,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43" s="4">
         <v>150</v>
@@ -14462,10 +14485,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C44" s="4">
         <v>2453</v>
@@ -14485,10 +14508,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C45" s="4">
         <v>2450</v>
@@ -14508,10 +14531,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C46" s="4">
         <v>7</v>
@@ -14531,10 +14554,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" s="4">
         <v>2451</v>
@@ -14554,10 +14577,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4">
         <v>468</v>
@@ -14577,10 +14600,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" s="4">
         <v>4138</v>
@@ -14600,10 +14623,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C50" s="4">
         <v>2508</v>
@@ -14623,10 +14646,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C51" s="4">
         <v>4691</v>
@@ -14646,10 +14669,10 @@
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52" s="4">
         <v>4692</v>
@@ -14669,10 +14692,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C53" s="4">
         <v>2442</v>
@@ -14692,10 +14715,10 @@
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="4">
         <v>2524</v>
@@ -14715,10 +14738,10 @@
     </row>
     <row r="55" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C55" s="4">
         <v>3441</v>
@@ -14738,10 +14761,10 @@
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C56" s="4">
         <v>2523</v>
@@ -14761,10 +14784,10 @@
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C57" s="4">
         <v>3408</v>
@@ -14779,15 +14802,15 @@
         <v>28</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C58" s="4">
         <v>2273</v>
@@ -14807,10 +14830,10 @@
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="4">
         <v>2271</v>
@@ -14830,10 +14853,10 @@
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C60" s="4">
         <v>3409</v>
@@ -14853,10 +14876,10 @@
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C61" s="4">
         <v>459</v>
@@ -14876,10 +14899,10 @@
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" s="4">
         <v>285</v>
@@ -14899,10 +14922,10 @@
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C63" s="4">
         <v>2252</v>
@@ -14922,10 +14945,10 @@
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" s="4">
         <v>2291</v>
@@ -14945,10 +14968,10 @@
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C65" s="4">
         <v>3534</v>
@@ -14968,10 +14991,10 @@
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" s="4">
         <v>2250</v>
@@ -14991,10 +15014,10 @@
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C67" s="4">
         <v>2340</v>
@@ -15014,10 +15037,10 @@
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" s="4">
         <v>3533</v>
@@ -15037,10 +15060,10 @@
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" s="4">
         <v>3532</v>
@@ -15060,10 +15083,10 @@
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C70" s="4">
         <v>2251</v>
@@ -15083,10 +15106,10 @@
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C71" s="4">
         <v>3081</v>
@@ -15106,10 +15129,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C72" s="4">
         <v>3818</v>
@@ -15129,10 +15152,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C73" s="4">
         <v>2534</v>
@@ -15152,10 +15175,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C74" s="4">
         <v>2234</v>
@@ -15175,10 +15198,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C75" s="4">
         <v>2238</v>
@@ -15198,10 +15221,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C76" s="4">
         <v>2535</v>
@@ -15221,10 +15244,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C77" s="4">
         <v>2512</v>
@@ -15244,10 +15267,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C78" s="4">
         <v>2537</v>
@@ -15267,10 +15290,10 @@
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C79" s="4">
         <v>2236</v>
@@ -15290,10 +15313,10 @@
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C80" s="4">
         <v>2546</v>
@@ -15313,10 +15336,10 @@
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C81" s="4">
         <v>2232</v>
@@ -15336,10 +15359,10 @@
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C82" s="4">
         <v>2536</v>
@@ -15359,10 +15382,10 @@
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C83" s="4">
         <v>4021</v>
@@ -15382,10 +15405,10 @@
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C84" s="4">
         <v>4135</v>
@@ -15394,7 +15417,7 @@
         <v>12</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>28</v>
@@ -15405,10 +15428,10 @@
     </row>
     <row r="85" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C85" s="4">
         <v>2852</v>
@@ -15428,10 +15451,10 @@
     </row>
     <row r="86" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C86" s="4">
         <v>3601</v>
@@ -15451,10 +15474,10 @@
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C87" s="4">
         <v>263</v>
@@ -15474,10 +15497,10 @@
     </row>
     <row r="88" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C88" s="4">
         <v>2632</v>
@@ -15497,10 +15520,10 @@
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C89" s="4">
         <v>2330</v>
@@ -15520,10 +15543,10 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C90" s="4">
         <v>4179</v>
@@ -15543,10 +15566,10 @@
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C91" s="4">
         <v>2385</v>
@@ -15566,10 +15589,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C92" s="4">
         <v>4540</v>
@@ -15589,10 +15612,10 @@
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C93" s="4">
         <v>2384</v>
@@ -15612,10 +15635,10 @@
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C94" s="4">
         <v>3851</v>
@@ -15635,10 +15658,10 @@
     </row>
     <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C95" s="4">
         <v>2424</v>
@@ -15701,10 +15724,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C2" s="4">
         <v>85</v>
@@ -15724,10 +15747,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="4">
         <v>2447</v>
@@ -15747,10 +15770,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4">
         <v>551</v>
@@ -15770,10 +15793,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4">
         <v>2448</v>
@@ -15793,10 +15816,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="4">
         <v>3559</v>
@@ -15816,10 +15839,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4">
         <v>3560</v>
@@ -15839,10 +15862,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4">
         <v>255</v>
@@ -15862,10 +15885,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="4">
         <v>2456</v>
@@ -15885,10 +15908,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="4">
         <v>80</v>
@@ -15908,10 +15931,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="4">
         <v>2457</v>
@@ -15931,10 +15954,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="4">
         <v>94</v>
@@ -15954,10 +15977,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="4">
         <v>2458</v>
@@ -15977,10 +16000,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4">
         <v>2454</v>
@@ -16000,10 +16023,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C15" s="4">
         <v>2455</v>
@@ -16023,10 +16046,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" s="4">
         <v>450</v>
@@ -16046,10 +16069,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C17" s="4">
         <v>2459</v>
@@ -16112,10 +16135,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="4">
         <v>2314</v>
@@ -16135,10 +16158,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C3" s="4">
         <v>2313</v>
@@ -16158,10 +16181,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4">
         <v>2316</v>
@@ -16181,10 +16204,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" s="4">
         <v>2312</v>
@@ -16204,10 +16227,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C6" s="4">
         <v>3513</v>
@@ -16227,10 +16250,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C7" s="4">
         <v>2315</v>
@@ -16250,10 +16273,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" s="4">
         <v>3512</v>
@@ -16273,10 +16296,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" s="4">
         <v>2311</v>
@@ -16339,10 +16362,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C2" s="4">
         <v>3440</v>
@@ -16362,10 +16385,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C3" s="4">
         <v>2832</v>
@@ -16385,10 +16408,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C4" s="4">
         <v>4337</v>
@@ -16408,10 +16431,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4">
         <v>4668</v>
@@ -16431,10 +16454,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="4">
         <v>4667</v>
@@ -16454,10 +16477,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" s="4">
         <v>3045</v>
@@ -16477,10 +16500,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C8" s="4">
         <v>4376</v>
@@ -16500,10 +16523,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C9" s="4">
         <v>2625</v>
@@ -16523,10 +16546,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C10" s="4">
         <v>2717</v>
@@ -16546,10 +16569,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C11" s="4">
         <v>2573</v>
@@ -16569,10 +16592,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C12" s="4">
         <v>2504</v>
@@ -16592,10 +16615,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4">
         <v>2505</v>
@@ -16615,10 +16638,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C14" s="4">
         <v>3043</v>
@@ -16638,10 +16661,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C15" s="4">
         <v>2557</v>
@@ -16661,10 +16684,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="4">
         <v>2540</v>
@@ -16684,10 +16707,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C17" s="4">
         <v>3503</v>
@@ -16707,10 +16730,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C18" s="4">
         <v>2691</v>
@@ -16730,10 +16753,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C19" s="4">
         <v>2692</v>
@@ -16753,10 +16776,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" s="4">
         <v>3484</v>
@@ -16776,10 +16799,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" s="4">
         <v>3485</v>
@@ -16799,10 +16822,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C22" s="4">
         <v>3976</v>
@@ -16822,10 +16845,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="4">
         <v>2780</v>
@@ -16845,10 +16868,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C24" s="4">
         <v>3406</v>
@@ -16868,10 +16891,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" s="4">
         <v>3040</v>
@@ -16891,10 +16914,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C26" s="4">
         <v>3041</v>
@@ -16914,10 +16937,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C27" s="4">
         <v>2741</v>
@@ -16937,10 +16960,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="4">
         <v>2559</v>
@@ -16960,10 +16983,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" s="4">
         <v>2526</v>
@@ -16983,10 +17006,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C30" s="4">
         <v>2527</v>
@@ -17006,10 +17029,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C31" s="4">
         <v>3063</v>
@@ -17029,10 +17052,10 @@
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C32" s="4">
         <v>4251</v>
@@ -17052,10 +17075,10 @@
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C33" s="4">
         <v>4250</v>
@@ -17075,10 +17098,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" s="4">
         <v>2739</v>
@@ -17098,10 +17121,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C35" s="4">
         <v>2560</v>
@@ -17121,10 +17144,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C36" s="4">
         <v>2742</v>
@@ -17144,10 +17167,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="4">
         <v>2744</v>
@@ -17167,10 +17190,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C38" s="4">
         <v>4072</v>
@@ -17190,10 +17213,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C39" s="4">
         <v>4071</v>
@@ -17213,10 +17236,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C40" s="4">
         <v>2696</v>
@@ -17236,10 +17259,10 @@
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C41" s="4">
         <v>2697</v>
@@ -17259,10 +17282,10 @@
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C42" s="4">
         <v>3044</v>
@@ -17282,10 +17305,10 @@
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C43" s="4">
         <v>2746</v>
@@ -17305,10 +17328,10 @@
     </row>
     <row r="44" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C44" s="4">
         <v>2713</v>
@@ -17328,10 +17351,10 @@
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C45" s="4">
         <v>3037</v>
@@ -17351,10 +17374,10 @@
     </row>
     <row r="46" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C46" s="4">
         <v>3038</v>
@@ -17374,10 +17397,10 @@
     </row>
     <row r="47" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C47" s="4">
         <v>2248</v>
@@ -17397,10 +17420,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" s="4">
         <v>3869</v>
@@ -17420,10 +17443,10 @@
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C49" s="4">
         <v>2436</v>
@@ -17443,13 +17466,13 @@
     </row>
     <row r="50" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C50" s="4">
-        <v>2466</v>
+        <v>4623</v>
       </c>
       <c r="D50" s="4">
         <v>25</v>
@@ -17466,13 +17489,13 @@
     </row>
     <row r="51" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" s="4">
-        <v>2465</v>
+        <v>4622</v>
       </c>
       <c r="D51" s="4">
         <v>2</v>
@@ -17489,10 +17512,10 @@
     </row>
     <row r="52" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="4">
         <v>4318</v>
@@ -17512,10 +17535,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C53" s="4">
         <v>4319</v>
@@ -17535,10 +17558,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C54" s="4">
         <v>4254</v>
@@ -17558,10 +17581,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C55" s="4">
         <v>2563</v>
@@ -17581,10 +17604,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C56" s="4">
         <v>4689</v>
@@ -17604,10 +17627,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C57" s="4">
         <v>2725</v>
@@ -17627,10 +17650,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C58" s="4">
         <v>2562</v>
@@ -17650,10 +17673,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C59" s="4">
         <v>2782</v>
@@ -17673,10 +17696,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C60" s="4">
         <v>2745</v>
@@ -17696,10 +17719,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C61" s="4">
         <v>4207</v>
@@ -17719,10 +17742,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C62" s="4">
         <v>3769</v>
@@ -17742,10 +17765,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C63" s="4">
         <v>3034</v>
@@ -17765,10 +17788,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C64" s="4">
         <v>3039</v>
@@ -17788,10 +17811,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C65" s="4">
         <v>3421</v>
@@ -17811,10 +17834,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C66" s="4">
         <v>2748</v>
@@ -17834,10 +17857,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C67" s="4">
         <v>2576</v>
@@ -17857,10 +17880,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C68" s="4">
         <v>3032</v>
@@ -17880,10 +17903,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C69" s="4">
         <v>2740</v>
@@ -17903,10 +17926,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C70" s="4">
         <v>3098</v>
@@ -17926,10 +17949,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C71" s="4">
         <v>2743</v>
@@ -17949,10 +17972,10 @@
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C72" s="4">
         <v>3360</v>
@@ -17972,10 +17995,10 @@
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C73" s="4">
         <v>2611</v>
@@ -17995,10 +18018,10 @@
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C74" s="4">
         <v>2558</v>
@@ -18018,10 +18041,10 @@
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C75" s="4">
         <v>3042</v>
@@ -18041,10 +18064,10 @@
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C76" s="4">
         <v>2561</v>
@@ -18064,10 +18087,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C77" s="4">
         <v>4226</v>
@@ -18087,10 +18110,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C78" s="4">
         <v>4227</v>
@@ -18153,10 +18176,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C2" s="4">
         <v>4295</v>
@@ -18176,10 +18199,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C3" s="4">
         <v>203</v>
@@ -18199,10 +18222,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C4" s="4">
         <v>2490</v>
@@ -18222,10 +18245,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C5" s="4">
         <v>4552</v>
@@ -18245,10 +18268,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C6" s="4">
         <v>3893</v>
@@ -18268,10 +18291,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C7" s="4">
         <v>2242</v>
@@ -18291,10 +18314,10 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C8" s="4">
         <v>2518</v>
@@ -18314,10 +18337,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C9" s="4">
         <v>845</v>
@@ -18337,10 +18360,10 @@
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C10" s="4">
         <v>2517</v>
@@ -18360,10 +18383,10 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C11" s="4">
         <v>2631</v>
@@ -18383,10 +18406,10 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C12" s="4">
         <v>3088</v>
@@ -18406,10 +18429,10 @@
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C13" s="4">
         <v>3850</v>
@@ -18429,10 +18452,10 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C14" s="4">
         <v>2489</v>
@@ -18452,10 +18475,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C15" s="4">
         <v>2437</v>
@@ -18475,10 +18498,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C16" s="4">
         <v>582</v>
@@ -18498,10 +18521,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C17" s="4">
         <v>3415</v>
@@ -18510,7 +18533,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -18521,10 +18544,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C18" s="4">
         <v>2485</v>
@@ -18544,10 +18567,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C19" s="4">
         <v>583</v>
@@ -18567,10 +18590,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C20" s="4">
         <v>3416</v>
@@ -18579,10 +18602,10 @@
         <v>10</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G20" s="4">
         <v>60.5</v>
@@ -18636,10 +18659,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C23" s="4">
         <v>3398</v>
@@ -18659,10 +18682,10 @@
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C24" s="4">
         <v>4025</v>
@@ -18682,10 +18705,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C25" s="4">
         <v>4162</v>
@@ -18705,10 +18728,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="4">
         <v>3424</v>
@@ -18723,15 +18746,15 @@
         <v>11</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C27" s="4">
         <v>4161</v>
@@ -18751,10 +18774,10 @@
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C28" s="4">
         <v>3718</v>
@@ -18774,10 +18797,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C29" s="4">
         <v>4277</v>
@@ -18797,10 +18820,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="4">
         <v>4676</v>
@@ -18820,10 +18843,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C31" s="4">
         <v>4163</v>
@@ -18843,10 +18866,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="4">
         <v>4117</v>
@@ -18866,10 +18889,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" s="4">
         <v>3738</v>
@@ -18889,10 +18912,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" s="4">
         <v>4317</v>
@@ -18912,10 +18935,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C35" s="4">
         <v>2924</v>
@@ -18935,10 +18958,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="4">
         <v>3078</v>
@@ -18958,10 +18981,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C37" s="4">
         <v>2348</v>
@@ -18981,10 +19004,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C38" s="4">
         <v>2538</v>
@@ -19004,10 +19027,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C39" s="4">
         <v>2811</v>
@@ -19027,10 +19050,10 @@
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C40" s="4">
         <v>2820</v>
@@ -19050,10 +19073,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C41" s="4">
         <v>3722</v>
@@ -19073,10 +19096,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C42" s="4">
         <v>4050</v>
@@ -19096,10 +19119,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C43" s="4">
         <v>415</v>
@@ -19119,10 +19142,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C44" s="4">
         <v>93</v>
@@ -19234,10 +19257,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C49" s="4">
         <v>18</v>
@@ -19257,10 +19280,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C50" s="4">
         <v>2477</v>
@@ -19280,10 +19303,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C51" s="4">
         <v>4164</v>
@@ -19303,10 +19326,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C52" s="4">
         <v>3706</v>
@@ -19326,10 +19349,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C53" s="4">
         <v>19</v>
@@ -19349,10 +19372,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C54" s="4">
         <v>2246</v>
@@ -19361,10 +19384,10 @@
         <v>4</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G54" s="4">
         <v>192</v>
@@ -19372,10 +19395,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C55" s="4">
         <v>575</v>
@@ -19395,10 +19418,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C56" s="4">
         <v>221</v>
@@ -19418,10 +19441,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C57" s="4">
         <v>258</v>
@@ -19430,10 +19453,10 @@
         <v>4</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G57" s="4">
         <v>324</v>
@@ -19441,10 +19464,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C58" s="4">
         <v>20</v>
@@ -19464,10 +19487,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C59" s="4">
         <v>2520</v>
@@ -19487,10 +19510,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C60" s="4">
         <v>4089</v>
@@ -19510,10 +19533,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C61" s="4">
         <v>21</v>
@@ -19533,10 +19556,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C62" s="4">
         <v>262</v>
@@ -19556,10 +19579,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C63" s="4">
         <v>2513</v>
@@ -19579,10 +19602,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C64" s="4">
         <v>16</v>
@@ -19602,10 +19625,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C65" s="4">
         <v>3114</v>
@@ -19625,10 +19648,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C66" s="4">
         <v>4086</v>
@@ -19637,10 +19660,10 @@
         <v>10</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G66" s="4">
         <v>170</v>
@@ -19648,10 +19671,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C67" s="4">
         <v>15</v>
@@ -19671,10 +19694,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C68" s="4">
         <v>3115</v>
@@ -19694,10 +19717,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C69" s="4">
         <v>4165</v>
@@ -19717,10 +19740,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C70" s="4">
         <v>4100</v>
@@ -19740,10 +19763,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C71" s="4">
         <v>4280</v>
@@ -19763,10 +19786,10 @@
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C72" s="4">
         <v>4281</v>
@@ -19829,10 +19852,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C2" s="4">
         <v>11</v>
@@ -19852,10 +19875,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C3" s="4">
         <v>2471</v>
@@ -19875,10 +19898,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C4" s="4">
         <v>3472</v>
@@ -19893,15 +19916,15 @@
         <v>10</v>
       </c>
       <c r="G4" s="4">
-        <v>170</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C5" s="4">
         <v>2472</v>
@@ -19916,15 +19939,15 @@
         <v>11</v>
       </c>
       <c r="G5" s="4">
-        <v>31.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C6" s="4">
         <v>133</v>
@@ -19944,10 +19967,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C7" s="4">
         <v>127</v>
@@ -19967,10 +19990,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C8" s="4">
         <v>2637</v>
@@ -19990,10 +20013,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C9" s="4">
         <v>12</v>
@@ -20013,10 +20036,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C10" s="4">
         <v>2501</v>
@@ -20036,10 +20059,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C11" s="4">
         <v>24</v>
@@ -20059,10 +20082,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C12" s="4">
         <v>2726</v>
@@ -20082,10 +20105,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C13" s="4">
         <v>4221</v>
@@ -20105,10 +20128,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C14" s="4">
         <v>4222</v>
@@ -20128,10 +20151,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C15" s="4">
         <v>2580</v>
@@ -20151,10 +20174,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C16" s="4">
         <v>123</v>
@@ -20174,10 +20197,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C17" s="4">
         <v>4016</v>
@@ -20197,10 +20220,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C18" s="4">
         <v>4017</v>
@@ -20220,10 +20243,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C19" s="4">
         <v>210</v>
@@ -20243,10 +20266,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C20" s="4">
         <v>4545</v>
@@ -20266,10 +20289,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C21" s="4">
         <v>3363</v>
@@ -20289,10 +20312,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C22" s="4">
         <v>2482</v>
@@ -20312,10 +20335,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C23" s="4">
         <v>34</v>
@@ -20335,10 +20358,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C24" s="4">
         <v>89</v>
@@ -20358,10 +20381,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C25" s="4">
         <v>114</v>
@@ -20381,10 +20404,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C26" s="4">
         <v>2486</v>
@@ -20404,10 +20427,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C27" s="4">
         <v>2241</v>
@@ -20427,10 +20450,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C28" s="4">
         <v>2487</v>
@@ -20450,10 +20473,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C29" s="4">
         <v>23</v>
@@ -20473,10 +20496,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C30" s="4">
         <v>2260</v>
@@ -20496,10 +20519,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C31" s="4">
         <v>214</v>
@@ -20519,10 +20542,10 @@
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C32" s="4">
         <v>4664</v>
@@ -20542,10 +20565,10 @@
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C33" s="4">
         <v>4665</v>
@@ -20565,10 +20588,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C34" s="4">
         <v>28</v>
@@ -20588,10 +20611,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C35" s="4">
         <v>68</v>
@@ -20611,10 +20634,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C36" s="4">
         <v>2302</v>
@@ -20634,10 +20657,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C37" s="4">
         <v>320</v>
@@ -20657,10 +20680,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C38" s="4">
         <v>3479</v>
@@ -20680,10 +20703,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C39" s="4">
         <v>130</v>
@@ -20703,10 +20726,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C40" s="4">
         <v>2464</v>
@@ -20726,10 +20749,10 @@
     </row>
     <row r="41" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C41" s="4">
         <v>101</v>
@@ -20749,10 +20772,10 @@
     </row>
     <row r="42" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C42" s="4">
         <v>2465</v>
@@ -20772,10 +20795,10 @@
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C43" s="4">
         <v>65</v>
@@ -20795,10 +20818,10 @@
     </row>
     <row r="44" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C44" s="4">
         <v>2624</v>
@@ -20818,10 +20841,10 @@
     </row>
     <row r="45" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C45" s="4">
         <v>119</v>
@@ -20841,10 +20864,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C46" s="4">
         <v>2834</v>
@@ -20864,13 +20887,13 @@
     </row>
     <row r="47" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="4">
-        <v>3621</v>
+        <v>3519</v>
       </c>
       <c r="D47" s="4">
         <v>25</v>
@@ -20887,10 +20910,10 @@
     </row>
     <row r="48" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C48" s="4">
         <v>141</v>
@@ -20910,10 +20933,10 @@
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C49" s="4">
         <v>3025</v>
@@ -20933,10 +20956,10 @@
     </row>
     <row r="50" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C50" s="4">
         <v>2543</v>
@@ -20956,10 +20979,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C51" s="4">
         <v>98</v>
@@ -20979,10 +21002,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C52" s="4">
         <v>35</v>
@@ -21002,10 +21025,10 @@
     </row>
     <row r="53" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C53" s="4">
         <v>2353</v>
@@ -21025,10 +21048,10 @@
     </row>
     <row r="54" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C54" s="4">
         <v>2466</v>
@@ -21048,10 +21071,10 @@
     </row>
     <row r="55" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C55" s="4">
         <v>3089</v>
@@ -21071,10 +21094,10 @@
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C56" s="4">
         <v>2666</v>
@@ -21094,10 +21117,10 @@
     </row>
     <row r="57" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C57" s="4">
         <v>2667</v>
@@ -21117,10 +21140,10 @@
     </row>
     <row r="58" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C58" s="4">
         <v>3478</v>
@@ -21140,10 +21163,10 @@
     </row>
     <row r="59" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C59" s="4">
         <v>190</v>
@@ -21163,10 +21186,10 @@
     </row>
     <row r="60" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C60" s="4">
         <v>2335</v>
@@ -21186,10 +21209,10 @@
     </row>
     <row r="61" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C61" s="4">
         <v>3446</v>
@@ -21209,10 +21232,10 @@
     </row>
     <row r="62" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C62" s="4">
         <v>3447</v>
@@ -21232,10 +21255,10 @@
     </row>
     <row r="63" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C63" s="4">
         <v>100</v>
@@ -21255,10 +21278,10 @@
     </row>
     <row r="64" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C64" s="4">
         <v>136</v>
@@ -21278,10 +21301,10 @@
     </row>
     <row r="65" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C65" s="4">
         <v>259</v>
@@ -21301,10 +21324,10 @@
     </row>
     <row r="66" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C66" s="4">
         <v>2319</v>
@@ -21324,10 +21347,10 @@
     </row>
     <row r="67" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C67" s="4">
         <v>125</v>
@@ -21347,10 +21370,10 @@
     </row>
     <row r="68" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C68" s="4">
         <v>2468</v>
@@ -21370,10 +21393,10 @@
     </row>
     <row r="69" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C69" s="4">
         <v>3740</v>
@@ -21393,10 +21416,10 @@
     </row>
     <row r="70" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C70" s="4">
         <v>2469</v>
@@ -21416,10 +21439,10 @@
     </row>
     <row r="71" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C71" s="4">
         <v>3006</v>
@@ -21439,10 +21462,10 @@
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C72" s="4">
         <v>3007</v>
@@ -21462,10 +21485,10 @@
     </row>
     <row r="73" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C73" s="4">
         <v>117</v>
@@ -21485,10 +21508,10 @@
     </row>
     <row r="74" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C74" s="4">
         <v>2320</v>
@@ -21508,10 +21531,10 @@
     </row>
     <row r="75" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C75" s="4">
         <v>60</v>
@@ -21531,10 +21554,10 @@
     </row>
     <row r="76" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C76" s="4">
         <v>2321</v>
@@ -21554,10 +21577,10 @@
     </row>
     <row r="77" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C77" s="4">
         <v>211</v>
@@ -21577,10 +21600,10 @@
     </row>
     <row r="78" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C78" s="4">
         <v>41</v>
@@ -21600,10 +21623,10 @@
     </row>
     <row r="79" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C79" s="4">
         <v>2322</v>
@@ -21623,10 +21646,10 @@
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C80" s="4">
         <v>67</v>
@@ -21646,10 +21669,10 @@
     </row>
     <row r="81" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C81" s="4">
         <v>2244</v>
@@ -21669,10 +21692,10 @@
     </row>
     <row r="82" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C82" s="4">
         <v>2488</v>
@@ -21692,10 +21715,10 @@
     </row>
     <row r="83" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C83" s="4">
         <v>520</v>
@@ -21715,10 +21738,10 @@
     </row>
     <row r="84" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C84" s="4">
         <v>4546</v>
@@ -21738,10 +21761,10 @@
     </row>
     <row r="85" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C85" s="4">
         <v>3695</v>
@@ -21761,10 +21784,10 @@
     </row>
     <row r="86" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C86" s="4">
         <v>3097</v>
@@ -21784,10 +21807,10 @@
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C87" s="4">
         <v>2460</v>
@@ -21830,10 +21853,10 @@
     </row>
     <row r="89" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C89" s="4">
         <v>135</v>
@@ -21853,10 +21876,10 @@
     </row>
     <row r="90" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C90" s="4">
         <v>2463</v>
@@ -21876,10 +21899,10 @@
     </row>
     <row r="91" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C91" s="4">
         <v>55</v>
@@ -21899,10 +21922,10 @@
     </row>
     <row r="92" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C92" s="4">
         <v>51</v>
@@ -21922,10 +21945,10 @@
     </row>
     <row r="93" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C93" s="4">
         <v>201</v>
@@ -21945,10 +21968,10 @@
     </row>
     <row r="94" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C94" s="4">
         <v>4223</v>
@@ -21968,10 +21991,10 @@
     </row>
     <row r="95" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C95" s="4">
         <v>4224</v>
@@ -22034,10 +22057,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C2" s="4">
         <v>8</v>
@@ -22057,10 +22080,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C3" s="4">
         <v>2391</v>
@@ -22080,10 +22103,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C4" s="4">
         <v>2529</v>
@@ -22149,10 +22172,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C7" s="4">
         <v>3649</v>
@@ -22172,10 +22195,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C8" s="4">
         <v>3650</v>
@@ -22195,10 +22218,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C9" s="4">
         <v>3386</v>
@@ -22218,10 +22241,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C10" s="4">
         <v>3385</v>
@@ -22241,10 +22264,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C11" s="4">
         <v>460</v>
@@ -22264,10 +22287,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C12" s="4">
         <v>2473</v>
@@ -22287,10 +22310,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C13" s="4">
         <v>128</v>
@@ -22310,10 +22333,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C14" s="4">
         <v>2474</v>
@@ -22333,10 +22356,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C15" s="4">
         <v>3085</v>
@@ -22356,10 +22379,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C16" s="4">
         <v>3086</v>
@@ -22379,10 +22402,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C17" s="4">
         <v>4558</v>
@@ -22391,10 +22414,10 @@
         <v>10</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G17" s="4">
         <v>45</v>
@@ -22402,10 +22425,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C18" s="4">
         <v>4697</v>
@@ -22425,10 +22448,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C19" s="4">
         <v>4048</v>
@@ -22437,10 +22460,10 @@
         <v>20</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G19" s="4">
         <v>55</v>
@@ -22448,10 +22471,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C20" s="4">
         <v>2519</v>
@@ -22471,10 +22494,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C21" s="4">
         <v>2525</v>
@@ -22494,10 +22517,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C22" s="4">
         <v>3433</v>
@@ -22517,10 +22540,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C23" s="4">
         <v>3394</v>
@@ -22540,10 +22563,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C24" s="4">
         <v>47</v>
@@ -22563,10 +22586,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C25" s="4">
         <v>46</v>
@@ -22586,10 +22609,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C26" s="4">
         <v>3100</v>
@@ -22609,10 +22632,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C27" s="4">
         <v>3746</v>
@@ -22632,10 +22655,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C28" s="4">
         <v>3639</v>
@@ -22655,10 +22678,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C29" s="4">
         <v>2415</v>
@@ -22678,10 +22701,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C30" s="4">
         <v>3747</v>
@@ -22701,10 +22724,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C31" s="4">
         <v>3640</v>
@@ -22724,10 +22747,10 @@
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C32" s="4">
         <v>2416</v>
@@ -22747,10 +22770,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C33" s="4">
         <v>50</v>
@@ -22770,10 +22793,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C34" s="4">
         <v>2533</v>
@@ -22793,10 +22816,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C35" s="4">
         <v>52</v>
@@ -22816,10 +22839,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C36" s="4">
         <v>2470</v>
@@ -22839,10 +22862,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C37" s="4">
         <v>4671</v>
@@ -22862,10 +22885,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C38" s="4">
         <v>53</v>
@@ -22885,10 +22908,10 @@
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C39" s="4">
         <v>2435</v>
@@ -22951,10 +22974,10 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C2" s="4">
         <v>4139</v>
@@ -22974,10 +22997,10 @@
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C3" s="4">
         <v>3383</v>
@@ -22997,10 +23020,10 @@
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C4" s="4">
         <v>4520</v>
@@ -23020,10 +23043,10 @@
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C5" s="4">
         <v>3381</v>
@@ -23043,10 +23066,10 @@
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C6" s="4">
         <v>3498</v>
@@ -23066,10 +23089,10 @@
     </row>
     <row r="7" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C7" s="4">
         <v>4112</v>
@@ -23089,10 +23112,10 @@
     </row>
     <row r="8" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C8" s="4">
         <v>4116</v>
@@ -23112,10 +23135,10 @@
     </row>
     <row r="9" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C9" s="4">
         <v>4107</v>
@@ -23135,10 +23158,10 @@
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C10" s="4">
         <v>4657</v>
@@ -23147,10 +23170,10 @@
         <v>20</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G10" s="4">
         <v>250</v>
@@ -23158,10 +23181,10 @@
     </row>
     <row r="11" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C11" s="4">
         <v>2222</v>
@@ -23181,10 +23204,10 @@
     </row>
     <row r="12" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C12" s="4">
         <v>3572</v>
@@ -23204,10 +23227,10 @@
     </row>
     <row r="13" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C13" s="4">
         <v>4669</v>
@@ -23227,10 +23250,10 @@
     </row>
     <row r="14" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C14" s="4">
         <v>2522</v>
@@ -23250,10 +23273,10 @@
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C15" s="4">
         <v>2521</v>
@@ -23273,10 +23296,10 @@
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C16" s="4">
         <v>2571</v>
@@ -23296,10 +23319,10 @@
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C17" s="4">
         <v>4108</v>
@@ -23319,10 +23342,10 @@
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C18" s="4">
         <v>4111</v>
@@ -23342,10 +23365,10 @@
     </row>
     <row r="19" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C19" s="4">
         <v>3499</v>
@@ -23365,10 +23388,10 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C20" s="4">
         <v>2616</v>
@@ -23388,10 +23411,10 @@
     </row>
     <row r="21" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C21" s="4">
         <v>2615</v>
@@ -23411,10 +23434,10 @@
     </row>
     <row r="22" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C22" s="4">
         <v>4283</v>
@@ -23434,10 +23457,10 @@
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C23" s="4">
         <v>4114</v>
@@ -23457,10 +23480,10 @@
     </row>
     <row r="24" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C24" s="4">
         <v>3493</v>
@@ -23480,10 +23503,10 @@
     </row>
     <row r="25" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C25" s="4">
         <v>4395</v>
@@ -23503,10 +23526,10 @@
     </row>
     <row r="26" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C26" s="4">
         <v>4394</v>
@@ -23526,10 +23549,10 @@
     </row>
     <row r="27" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C27" s="4">
         <v>4115</v>
@@ -23549,10 +23572,10 @@
     </row>
     <row r="28" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C28" s="4">
         <v>3497</v>
@@ -23572,10 +23595,10 @@
     </row>
     <row r="29" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C29" s="4">
         <v>2492</v>
@@ -23595,10 +23618,10 @@
     </row>
     <row r="30" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C30" s="4">
         <v>2499</v>
@@ -23618,10 +23641,10 @@
     </row>
     <row r="31" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C31" s="4">
         <v>3101</v>
@@ -23636,15 +23659,15 @@
         <v>10</v>
       </c>
       <c r="G31" s="4">
-        <v>73</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C32" s="4">
         <v>580</v>
@@ -23659,15 +23682,15 @@
         <v>10</v>
       </c>
       <c r="G32" s="4">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C33" s="4">
         <v>581</v>
@@ -23687,10 +23710,10 @@
     </row>
     <row r="34" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C34" s="4">
         <v>4029</v>
@@ -23699,7 +23722,7 @@
         <v>20</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>28</v>
@@ -23710,10 +23733,10 @@
     </row>
     <row r="35" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C35" s="4">
         <v>4203</v>
@@ -23722,10 +23745,10 @@
         <v>20</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G35" s="4">
         <v>86</v>
@@ -23733,10 +23756,10 @@
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C36" s="4">
         <v>3936</v>
@@ -23745,7 +23768,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>28</v>
@@ -23756,10 +23779,10 @@
     </row>
     <row r="37" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C37" s="4">
         <v>4302</v>
@@ -23768,7 +23791,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>28</v>
@@ -23779,10 +23802,10 @@
     </row>
     <row r="38" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C38" s="4">
         <v>3027</v>
@@ -23802,10 +23825,10 @@
     </row>
     <row r="39" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C39" s="4">
         <v>3026</v>
@@ -23814,10 +23837,10 @@
         <v>30</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G39" s="4">
         <v>44</v>
@@ -23825,10 +23848,10 @@
     </row>
     <row r="40" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C40" s="4">
         <v>3514</v>
@@ -23848,10 +23871,10 @@
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C41" s="4">
         <v>3515</v>
@@ -23860,10 +23883,10 @@
         <v>30</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G41" s="4">
         <v>46</v>
@@ -23871,10 +23894,10 @@
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C42" s="4">
         <v>3139</v>
@@ -23894,10 +23917,10 @@
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C43" s="4">
         <v>3138</v>
@@ -23917,10 +23940,10 @@
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C44" s="4">
         <v>2592</v>
@@ -23940,10 +23963,10 @@
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C45" s="4">
         <v>2591</v>
@@ -23963,10 +23986,10 @@
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C46" s="4">
         <v>2597</v>
@@ -23986,10 +24009,10 @@
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C47" s="4">
         <v>4174</v>
@@ -24009,10 +24032,10 @@
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C48" s="4">
         <v>4176</v>
@@ -24032,10 +24055,10 @@
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C49" s="4">
         <v>2686</v>
@@ -24055,10 +24078,10 @@
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C50" s="4">
         <v>2687</v>
@@ -24078,10 +24101,10 @@
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C51" s="4">
         <v>4496</v>
@@ -24101,10 +24124,10 @@
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C52" s="4">
         <v>4061</v>
@@ -24124,10 +24147,10 @@
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C53" s="4">
         <v>4166</v>
@@ -24147,10 +24170,10 @@
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C54" s="4">
         <v>2681</v>
@@ -24170,10 +24193,10 @@
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C55" s="4">
         <v>2682</v>
@@ -24193,10 +24216,10 @@
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C56" s="4">
         <v>2683</v>
@@ -24216,10 +24239,10 @@
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C57" s="4">
         <v>2600</v>
@@ -24239,10 +24262,10 @@
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C58" s="4">
         <v>4167</v>
@@ -24262,10 +24285,10 @@
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C59" s="4">
         <v>2595</v>
@@ -24285,10 +24308,10 @@
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C60" s="4">
         <v>4062</v>
@@ -24308,10 +24331,10 @@
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C61" s="4">
         <v>2707</v>
@@ -24331,10 +24354,10 @@
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C62" s="4">
         <v>3605</v>
@@ -24354,10 +24377,10 @@
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C63" s="4">
         <v>3606</v>
@@ -24377,10 +24400,10 @@
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C64" s="4">
         <v>4402</v>
@@ -24400,10 +24423,10 @@
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C65" s="4">
         <v>4401</v>
@@ -24423,10 +24446,10 @@
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C66" s="4">
         <v>2684</v>
@@ -24446,10 +24469,10 @@
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C67" s="4">
         <v>2723</v>
@@ -24469,10 +24492,10 @@
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C68" s="4">
         <v>2734</v>
@@ -24481,7 +24504,7 @@
         <v>6</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -24492,10 +24515,10 @@
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C69" s="4">
         <v>4168</v>
@@ -24515,10 +24538,10 @@
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C70" s="4">
         <v>2718</v>
@@ -24538,10 +24561,10 @@
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C71" s="4">
         <v>2719</v>
@@ -24556,15 +24579,15 @@
         <v>11</v>
       </c>
       <c r="G71" s="4">
-        <v>172.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C72" s="4">
         <v>3094</v>
@@ -24584,10 +24607,10 @@
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C73" s="4">
         <v>4169</v>
@@ -24607,10 +24630,10 @@
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C74" s="4">
         <v>2685</v>
@@ -24630,10 +24653,10 @@
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C75" s="4">
         <v>4113</v>
@@ -24653,10 +24676,10 @@
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C76" s="4">
         <v>4106</v>
@@ -24676,10 +24699,10 @@
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C77" s="4">
         <v>2596</v>
@@ -24699,10 +24722,10 @@
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C78" s="4">
         <v>4457</v>
@@ -24722,10 +24745,10 @@
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C79" s="4">
         <v>4458</v>
@@ -24745,10 +24768,10 @@
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C80" s="4">
         <v>2602</v>
@@ -24768,10 +24791,10 @@
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C81" s="4">
         <v>2605</v>
@@ -24791,10 +24814,10 @@
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C82" s="4">
         <v>3894</v>
@@ -24814,10 +24837,10 @@
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C83" s="4">
         <v>4109</v>
@@ -24837,10 +24860,10 @@
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C84" s="4">
         <v>4110</v>
@@ -24860,10 +24883,10 @@
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C85" s="4">
         <v>4171</v>
@@ -24883,10 +24906,10 @@
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C86" s="4">
         <v>2653</v>
@@ -24906,10 +24929,10 @@
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C87" s="4">
         <v>3675</v>
@@ -24929,10 +24952,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C88" s="4">
         <v>2417</v>
@@ -24952,10 +24975,10 @@
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C89" s="4">
         <v>3109</v>
@@ -24975,10 +24998,10 @@
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C90" s="4">
         <v>2777</v>
@@ -24998,10 +25021,10 @@
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C91" s="4">
         <v>2776</v>
@@ -25021,10 +25044,10 @@
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C92" s="4">
         <v>4173</v>
@@ -25044,10 +25067,10 @@
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C93" s="4">
         <v>2689</v>
@@ -25067,10 +25090,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C94" s="4">
         <v>4170</v>
@@ -25090,10 +25113,10 @@
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C95" s="4">
         <v>4494</v>
@@ -25113,10 +25136,10 @@
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C96" s="4">
         <v>4495</v>
@@ -25136,10 +25159,10 @@
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C97" s="4">
         <v>2785</v>
@@ -25159,10 +25182,10 @@
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C98" s="4">
         <v>2784</v>
@@ -25182,10 +25205,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C99" s="4">
         <v>2788</v>
@@ -25205,10 +25228,10 @@
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C100" s="4">
         <v>2789</v>
@@ -25228,10 +25251,10 @@
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C101" s="4">
         <v>4539</v>
@@ -25251,10 +25274,10 @@
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C102" s="4">
         <v>3495</v>
@@ -25274,10 +25297,10 @@
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C103" s="4">
         <v>2786</v>
@@ -25297,10 +25320,10 @@
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C104" s="4">
         <v>2787</v>
@@ -25320,10 +25343,10 @@
     </row>
     <row r="105" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C105" s="4">
         <v>2598</v>
@@ -25343,10 +25366,10 @@
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C106" s="4">
         <v>4060</v>
@@ -25366,10 +25389,10 @@
     </row>
     <row r="107" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C107" s="4">
         <v>2690</v>
@@ -25389,10 +25412,10 @@
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C108" s="4">
         <v>3355</v>
@@ -25412,10 +25435,10 @@
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C109" s="4">
         <v>3066</v>
@@ -25435,10 +25458,10 @@
     </row>
     <row r="110" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C110" s="4">
         <v>4702</v>
@@ -25458,10 +25481,10 @@
     </row>
     <row r="111" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C111" s="4">
         <v>4701</v>
@@ -25481,10 +25504,10 @@
     </row>
     <row r="112" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C112" s="4">
         <v>1515</v>
@@ -25504,10 +25527,10 @@
     </row>
     <row r="113" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C113" s="4">
         <v>2552</v>
@@ -25527,10 +25550,10 @@
     </row>
     <row r="114" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C114" s="4">
         <v>3092</v>
@@ -25550,10 +25573,10 @@
     </row>
     <row r="115" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C115" s="4">
         <v>2589</v>
@@ -25573,10 +25596,10 @@
     </row>
     <row r="116" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C116" s="4">
         <v>2588</v>
@@ -25596,10 +25619,10 @@
     </row>
     <row r="117" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C117" s="4">
         <v>2688</v>
@@ -25619,10 +25642,10 @@
     </row>
     <row r="118" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C118" s="4">
         <v>2599</v>

--- a/data/ProdutosFomatodos.xlsx
+++ b/data/ProdutosFomatodos.xlsx
@@ -1779,7 +1779,7 @@
     <t>tempero-glutamato</t>
   </si>
   <si>
-    <t>TEMPERO GLUTAMATO</t>
+    <t>GLUTAMATO</t>
   </si>
   <si>
     <t>tempero-lemon-pepper</t>
@@ -11323,7 +11323,7 @@
         <v>981</v>
       </c>
       <c r="C51" s="4">
-        <v>2505</v>
+        <v>4662</v>
       </c>
       <c r="D51" s="4">
         <v>2.5</v>
